--- a/Compatibility.xlsx
+++ b/Compatibility.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R7268085a16544fb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compatibility" sheetId="2" r:id="R5ce9474d72ac4c4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Profiles" sheetId="3" r:id="Rcce1c7915fa34c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" r:id="Ra9220ee976864f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R65bd90097b774f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compatibility" sheetId="2" r:id="Rc59a4346584d4cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Profiles" sheetId="3" r:id="R371959962c914bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" r:id="R3f1efb73afd54a10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -56,6 +56,11 @@
         <x:fgColor rgb="FFECEFF1"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF455A64"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -64,7 +69,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -126,11 +131,13 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="7">
+  <x:dxfs count="8">
     <x:dxf>
       <x:fill>
         <x:patternFill>
@@ -180,6 +187,13 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF8D7DA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
@@ -214,7 +228,7 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard'!$A$11:$A$19</c:f>
+              <c:f>'Dashboard'!$A$11:$A$20</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -222,7 +236,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard'!$B$11:$B$19</c:f>
+              <c:f>'Dashboard'!$B$11:$B$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="0"/>
@@ -308,7 +322,7 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -322,7 +336,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfa405e0536d9477e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9b28a2836ac14bd9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -713,7 +727,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>Crash</x:v>
+        <x:v>White screen</x:v>
       </x:c>
       <x:c r="B8" t="str"/>
       <x:c r="C8" t="str"/>
@@ -723,7 +737,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>Needs assets</x:v>
+        <x:v>Crash</x:v>
       </x:c>
       <x:c r="B9" t="str"/>
       <x:c r="C9" t="str"/>
@@ -733,13 +747,18 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Needs assets</x:v>
       </x:c>
       <x:c r="B10" t="str"/>
       <x:c r="C10" t="str"/>
       <x:c r="D10" t="str"/>
       <x:c r="E10" t="str"/>
       <x:c r="F10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Untested</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -841,7 +860,7 @@
         <x:v>Playable</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
         <x:v>Custom profile</x:v>
@@ -874,14 +893,14 @@
         <x:v>the-fancy-pants-adventure-1.profile</x:v>
       </x:c>
       <x:c r="O2" s="14" t="str">
-        <x:v>0.7.7</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P2" s="14" t="str"/>
       <x:c r="Q2" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
       <x:c r="R2" s="14" t="str">
-        <x:v>Working controls reported; community retest requested.</x:v>
+        <x:v>Runs well on the tested RK3326/EmuELEC setup. Custom handheld profile in use.</x:v>
       </x:c>
       <x:c r="S2" s="14" t="str"/>
     </x:row>
@@ -896,7 +915,7 @@
         <x:v>Playable</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
         <x:v>Custom profile</x:v>
@@ -929,14 +948,14 @@
         <x:v>the-world-hardest-game.profile</x:v>
       </x:c>
       <x:c r="O3" s="14" t="str">
-        <x:v>0.7.7</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P3" s="14" t="str"/>
       <x:c r="Q3" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
       <x:c r="R3" s="14" t="str">
-        <x:v>Working movement/click reported; community retest requested.</x:v>
+        <x:v>Runs well on the tested RK3326/EmuELEC setup. Movement and click controls working.</x:v>
       </x:c>
       <x:c r="S3" s="14" t="str"/>
     </x:row>
@@ -951,7 +970,7 @@
         <x:v>Playable</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
         <x:v>Custom profile</x:v>
@@ -984,14 +1003,14 @@
         <x:v>dad-n-me.profile</x:v>
       </x:c>
       <x:c r="O4" s="14" t="str">
-        <x:v>0.7.7</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P4" s="14" t="str"/>
       <x:c r="Q4" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
       <x:c r="R4" s="14" t="str">
-        <x:v>Light/heavy attacks and click reported working; more device reports wanted.</x:v>
+        <x:v>Playable with medium performance on the tested RK3326/EmuELEC setup.</x:v>
       </x:c>
       <x:c r="S4" s="14" t="str"/>
     </x:row>
@@ -1006,7 +1025,7 @@
         <x:v>Playable</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
         <x:v>Mouse-only</x:v>
@@ -1039,14 +1058,14 @@
         <x:v>papas-pizzeria.profile</x:v>
       </x:c>
       <x:c r="O5" s="14" t="str">
-        <x:v>0.7.7</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P5" s="14" t="str"/>
       <x:c r="Q5" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
       <x:c r="R5" s="14" t="str">
-        <x:v>Later build reported working; additional verification wanted.</x:v>
+        <x:v>Runs well on the tested RK3326/EmuELEC setup. Mouse controls working.</x:v>
       </x:c>
       <x:c r="S5" s="14" t="str"/>
     </x:row>
@@ -1061,7 +1080,7 @@
         <x:v>Playable</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
         <x:v>Mouse-only</x:v>
@@ -1094,14 +1113,14 @@
         <x:v>henry-stickmin-breaking-the-bank.profile</x:v>
       </x:c>
       <x:c r="O6" s="14" t="str">
-        <x:v>0.7.7</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P6" s="14" t="str"/>
       <x:c r="Q6" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
       <x:c r="R6" s="14" t="str">
-        <x:v>Mouse-only profile reported working.</x:v>
+        <x:v>Runs well on the tested RK3326/EmuELEC setup. Mouse controls working.</x:v>
       </x:c>
       <x:c r="S6" s="14" t="str"/>
     </x:row>
@@ -1114,7 +1133,7 @@
         <x:v>Playable</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
         <x:v>Custom profile</x:v>
@@ -1147,14 +1166,14 @@
         <x:v>garfield-s-scary-scavenger-hunt.profile</x:v>
       </x:c>
       <x:c r="O7" s="14" t="str">
-        <x:v>0.7.7</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P7" s="14" t="str"/>
       <x:c r="Q7" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
       <x:c r="R7" s="14" t="str">
-        <x:v>Known multi-file test case; exact package varies.</x:v>
+        <x:v>Multi-file test case. Playable with medium performance on the tested RK3326/EmuELEC setup.</x:v>
       </x:c>
       <x:c r="S7" s="14" t="str"/>
     </x:row>
@@ -1164,10 +1183,10 @@
       </x:c>
       <x:c r="B8" s="14" t="str"/>
       <x:c r="C8" s="14" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Playable</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
         <x:v>Custom profile</x:v>
@@ -1181,9 +1200,15 @@
       <x:c r="H8" s="14" t="str">
         <x:v>Native</x:v>
       </x:c>
-      <x:c r="I8" s="14" t="str"/>
-      <x:c r="J8" s="14" t="str"/>
-      <x:c r="K8" s="14" t="str"/>
+      <x:c r="I8" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
       <x:c r="L8" s="14" t="str">
         <x:v>aarch64</x:v>
       </x:c>
@@ -1194,12 +1219,14 @@
         <x:v>super-mario-63.profile</x:v>
       </x:c>
       <x:c r="O8" s="14" t="str">
-        <x:v>0.8.0</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P8" s="14" t="str"/>
-      <x:c r="Q8" s="14" t="str"/>
+      <x:c r="Q8" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
       <x:c r="R8" s="14" t="str">
-        <x:v>Needs a clean community retest on current release.</x:v>
+        <x:v>Opens and is playable, but performance is low on the tested RK3326/EmuELEC setup.</x:v>
       </x:c>
       <x:c r="S8" s="14" t="str"/>
     </x:row>
@@ -1209,10 +1236,10 @@
       </x:c>
       <x:c r="B9" s="14" t="str"/>
       <x:c r="C9" s="14" t="str">
-        <x:v>Untested</x:v>
+        <x:v>White screen</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
         <x:v>Custom profile</x:v>
@@ -1226,9 +1253,15 @@
       <x:c r="H9" s="14" t="str">
         <x:v>Native</x:v>
       </x:c>
-      <x:c r="I9" s="14" t="str"/>
-      <x:c r="J9" s="14" t="str"/>
-      <x:c r="K9" s="14" t="str"/>
+      <x:c r="I9" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
       <x:c r="L9" s="14" t="str">
         <x:v>aarch64</x:v>
       </x:c>
@@ -1239,34 +1272,62 @@
         <x:v>bad-ice-cream-3.profile</x:v>
       </x:c>
       <x:c r="O9" s="14" t="str">
-        <x:v>0.8.0</x:v>
+        <x:v>0.8.2</x:v>
       </x:c>
       <x:c r="P9" s="14" t="str"/>
-      <x:c r="Q9" s="14" t="str"/>
+      <x:c r="Q9" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
       <x:c r="R9" s="14" t="str">
-        <x:v>Needs a clean community retest on current release.</x:v>
+        <x:v>Game reaches a white screen on the tested setup.</x:v>
       </x:c>
       <x:c r="S9" s="14" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14"/>
+      <x:c r="A10" s="14" t="str">
+        <x:v>Super Mario Bros. Crossover 3</x:v>
+      </x:c>
       <x:c r="B10" s="14"/>
-      <x:c r="C10" s="14"/>
-      <x:c r="D10" s="14"/>
+      <x:c r="C10" s="14" t="str">
+        <x:v>Doesn't open</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
       <x:c r="E10" s="14"/>
       <x:c r="F10" s="14"/>
-      <x:c r="G10" s="14"/>
-      <x:c r="H10" s="14"/>
-      <x:c r="I10" s="14"/>
-      <x:c r="J10" s="14"/>
-      <x:c r="K10" s="14"/>
-      <x:c r="L10" s="14"/>
-      <x:c r="M10" s="14"/>
+      <x:c r="G10" s="14" t="str">
+        <x:v>Multi-file</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>Native Multi-file</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L10" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="N10" s="14"/>
-      <x:c r="O10" s="14"/>
+      <x:c r="O10" s="14" t="str">
+        <x:v>0.8.2</x:v>
+      </x:c>
       <x:c r="P10" s="14"/>
-      <x:c r="Q10" s="14"/>
-      <x:c r="R10" s="14"/>
+      <x:c r="Q10" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R10" s="14" t="str">
+        <x:v>Does not open on the tested setup.</x:v>
+      </x:c>
       <x:c r="S10" s="14"/>
     </x:row>
     <x:row r="11">
@@ -11573,6 +11634,9 @@
     <x:cfRule type="expression" dxfId="3" priority="4">
       <x:formula>C2="Partial"</x:formula>
     </x:cfRule>
+    <x:cfRule type="expression" dxfId="7" priority="8">
+      <x:formula>C2="White screen"</x:formula>
+    </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="D2:D500">
     <x:cfRule type="expression" dxfId="4" priority="5">
@@ -11587,7 +11651,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="C2:C500">
-      <x:formula1>Lists!$A$2:$A$10</x:formula1>
+      <x:formula1>Lists!$A$2:$A$11</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="D2:D500">
       <x:formula1>Lists!$B$2:$B$6</x:formula1>
@@ -11607,7 +11671,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d2d2a5970745af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec27079765044452"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12075,7 +12139,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17a8c9409e0341d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68f5482decb04657"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12125,7 +12189,7 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTA(Compatibility!A2:A500)</x:f>
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="28"/>
       <x:c r="E4" s="28"/>
@@ -12139,7 +12203,7 @@
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF(Compatibility!C2:C500,"Perfect")+COUNTIF(Compatibility!C2:C500,"Playable")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="28"/>
       <x:c r="E5" s="28"/>
@@ -12153,7 +12217,7 @@
       </x:c>
       <x:c r="B6" t="n">
         <x:f>COUNTIF(Compatibility!C2:C500,"Partial")+COUNTIF(Compatibility!C2:C500,"Boots")+COUNTIF(Compatibility!C2:C500,"Doesn't open")+COUNTIF(Compatibility!C2:C500,"Black screen")+COUNTIF(Compatibility!C2:C500,"Crash")+COUNTIF(Compatibility!C2:C500,"Needs assets")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="28"/>
       <x:c r="E6" s="28"/>
@@ -12189,10 +12253,10 @@
       <x:c r="H8" s="28"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="23" t="str">
+      <x:c r="A10" s="30" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="B10" s="23" t="str">
+      <x:c r="B10" s="30" t="str">
         <x:v>Count</x:v>
       </x:c>
     </x:row>
@@ -12211,7 +12275,7 @@
       </x:c>
       <x:c r="B12" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A12)</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -12238,7 +12302,7 @@
       </x:c>
       <x:c r="B15" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A15)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -12252,16 +12316,16 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>Crash</x:v>
+        <x:v>White screen</x:v>
       </x:c>
       <x:c r="B17" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A17)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>Needs assets</x:v>
+        <x:v>Crash</x:v>
       </x:c>
       <x:c r="B18" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A18)</x:f>
@@ -12270,11 +12334,20 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Needs assets</x:v>
       </x:c>
       <x:c r="B19" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A19)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Untested</x:v>
+      </x:c>
+      <x:c r="B20" t="n">
+        <x:f>COUNTIF(Compatibility!$C$2:$C$500,A20)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12283,6 +12356,6 @@
     <x:mergeCell ref="D3:H8"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54036bbbb0104236"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re30770dc5c9a4ae8"/>
 </x:worksheet>
 </file>
--- a/Compatibility.xlsx
+++ b/Compatibility.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R65bd90097b774f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compatibility" sheetId="2" r:id="Rc59a4346584d4cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Profiles" sheetId="3" r:id="R371959962c914bb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" r:id="R3f1efb73afd54a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R44350c46ad3348f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compatibility" sheetId="2" r:id="Rf63abc7da9c04cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Profiles" sheetId="3" r:id="R38f942e9bcbe49cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" r:id="R864c463f86444136"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,6 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -69,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -133,6 +136,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -189,7 +195,7 @@
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -336,7 +342,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9b28a2836ac14bd9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6151e992011740ff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -346,7 +352,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CompatibilityTable" displayName="CompatibilityTable" ref="A1:S9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CompatibilityTable" displayName="CompatibilityTable" ref="A1:S16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="Game"/>
     <x:tableColumn id="2" name="SWF Filename"/>
@@ -373,7 +379,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControlProfilesTable" displayName="ControlProfilesTable" ref="A1:N10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControlProfilesTable" displayName="ControlProfilesTable" ref="A1:N16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Game"/>
     <x:tableColumn id="2" name="Profile File"/>
@@ -893,9 +899,9 @@
         <x:v>the-fancy-pants-adventure-1.profile</x:v>
       </x:c>
       <x:c r="O2" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P2" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P2" s="31" t="str"/>
       <x:c r="Q2" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -948,9 +954,9 @@
         <x:v>the-world-hardest-game.profile</x:v>
       </x:c>
       <x:c r="O3" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P3" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P3" s="31" t="str"/>
       <x:c r="Q3" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1003,9 +1009,9 @@
         <x:v>dad-n-me.profile</x:v>
       </x:c>
       <x:c r="O4" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P4" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P4" s="31" t="str"/>
       <x:c r="Q4" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1058,9 +1064,9 @@
         <x:v>papas-pizzeria.profile</x:v>
       </x:c>
       <x:c r="O5" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P5" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P5" s="31" t="str"/>
       <x:c r="Q5" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1113,9 +1119,9 @@
         <x:v>henry-stickmin-breaking-the-bank.profile</x:v>
       </x:c>
       <x:c r="O6" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P6" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P6" s="31" t="str"/>
       <x:c r="Q6" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1166,9 +1172,9 @@
         <x:v>garfield-s-scary-scavenger-hunt.profile</x:v>
       </x:c>
       <x:c r="O7" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P7" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P7" s="31" t="str"/>
       <x:c r="Q7" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1219,9 +1225,9 @@
         <x:v>super-mario-63.profile</x:v>
       </x:c>
       <x:c r="O8" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P8" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P8" s="31" t="str"/>
       <x:c r="Q8" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1272,9 +1278,9 @@
         <x:v>bad-ice-cream-3.profile</x:v>
       </x:c>
       <x:c r="O9" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P9" s="14" t="str"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P9" s="31" t="str"/>
       <x:c r="Q9" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1319,9 +1325,9 @@
       </x:c>
       <x:c r="N10" s="14"/>
       <x:c r="O10" s="14" t="str">
-        <x:v>0.8.2</x:v>
-      </x:c>
-      <x:c r="P10" s="14"/>
+        <x:v>0.7.7</x:v>
+      </x:c>
+      <x:c r="P10" s="31"/>
       <x:c r="Q10" s="14" t="str">
         <x:v>Maintainer</x:v>
       </x:c>
@@ -1331,129 +1337,335 @@
       <x:c r="S10" s="14"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14"/>
+      <x:c r="A11" s="14" t="str">
+        <x:v>Bejeweled 2 (Original)</x:v>
+      </x:c>
       <x:c r="B11" s="14"/>
-      <x:c r="C11" s="14"/>
-      <x:c r="D11" s="14"/>
-      <x:c r="E11" s="14"/>
-      <x:c r="F11" s="14"/>
-      <x:c r="G11" s="14"/>
-      <x:c r="H11" s="14"/>
-      <x:c r="I11" s="14"/>
-      <x:c r="J11" s="14"/>
-      <x:c r="K11" s="14"/>
-      <x:c r="L11" s="14"/>
-      <x:c r="M11" s="14"/>
-      <x:c r="N11" s="14"/>
-      <x:c r="O11" s="14"/>
-      <x:c r="P11" s="14"/>
-      <x:c r="Q11" s="14"/>
-      <x:c r="R11" s="14"/>
+      <x:c r="C11" s="14" t="str">
+        <x:v>Crash</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>Mouse-only</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>Single SWF</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>Native</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N11" s="14" t="str">
+        <x:v>bejeweled-2.profile</x:v>
+      </x:c>
+      <x:c r="O11" s="14" t="str">
+        <x:v>0.8.21</x:v>
+      </x:c>
+      <x:c r="P11" s="31" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="Q11" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R11" s="14" t="str">
+        <x:v>Original Bejeweled 2 build crashes on the tested setup. The King.com build is tracked separately.</x:v>
+      </x:c>
       <x:c r="S11" s="14"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="14"/>
+      <x:c r="A12" s="14" t="str">
+        <x:v>Minecraft Tower Defense</x:v>
+      </x:c>
       <x:c r="B12" s="14"/>
-      <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
-      <x:c r="G12" s="14"/>
-      <x:c r="H12" s="14"/>
-      <x:c r="I12" s="14"/>
-      <x:c r="J12" s="14"/>
-      <x:c r="K12" s="14"/>
-      <x:c r="L12" s="14"/>
-      <x:c r="M12" s="14"/>
-      <x:c r="N12" s="14"/>
-      <x:c r="O12" s="14"/>
-      <x:c r="P12" s="14"/>
-      <x:c r="Q12" s="14"/>
-      <x:c r="R12" s="14"/>
+      <x:c r="C12" s="14" t="str">
+        <x:v>Playable</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>Mouse-only</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>Single SWF</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>Native</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N12" s="14" t="str">
+        <x:v>minecrafttowerdefense.profile</x:v>
+      </x:c>
+      <x:c r="O12" s="14" t="str">
+        <x:v>0.8.21</x:v>
+      </x:c>
+      <x:c r="P12" s="31" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="Q12" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R12" s="14" t="str">
+        <x:v>Playable with medium performance on the tested RK3326/EmuELEC setup.</x:v>
+      </x:c>
       <x:c r="S12" s="14"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="14"/>
+      <x:c r="A13" s="14" t="str">
+        <x:v>Final Fantasy Sonic X5</x:v>
+      </x:c>
       <x:c r="B13" s="14"/>
-      <x:c r="C13" s="14"/>
-      <x:c r="D13" s="14"/>
-      <x:c r="E13" s="14"/>
-      <x:c r="F13" s="14"/>
-      <x:c r="G13" s="14"/>
-      <x:c r="H13" s="14"/>
-      <x:c r="I13" s="14"/>
-      <x:c r="J13" s="14"/>
-      <x:c r="K13" s="14"/>
-      <x:c r="L13" s="14"/>
-      <x:c r="M13" s="14"/>
-      <x:c r="N13" s="14"/>
-      <x:c r="O13" s="14"/>
-      <x:c r="P13" s="14"/>
-      <x:c r="Q13" s="14"/>
-      <x:c r="R13" s="14"/>
+      <x:c r="C13" s="14" t="str">
+        <x:v>Playable</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>Mouse-only</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>Single SWF</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>Native</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L13" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N13" s="14" t="str">
+        <x:v>final-fantasy-sonic-x5.profile</x:v>
+      </x:c>
+      <x:c r="O13" s="14" t="str">
+        <x:v>0.8.21</x:v>
+      </x:c>
+      <x:c r="P13" s="31" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="Q13" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R13" s="14" t="str">
+        <x:v>Runs well with high performance on the tested RK3326/EmuELEC setup.</x:v>
+      </x:c>
       <x:c r="S13" s="14"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="14"/>
+      <x:c r="A14" s="14" t="str">
+        <x:v>Bejeweled 2 (King.com)</x:v>
+      </x:c>
       <x:c r="B14" s="14"/>
-      <x:c r="C14" s="14"/>
-      <x:c r="D14" s="14"/>
-      <x:c r="E14" s="14"/>
-      <x:c r="F14" s="14"/>
-      <x:c r="G14" s="14"/>
-      <x:c r="H14" s="14"/>
-      <x:c r="I14" s="14"/>
-      <x:c r="J14" s="14"/>
-      <x:c r="K14" s="14"/>
-      <x:c r="L14" s="14"/>
-      <x:c r="M14" s="14"/>
-      <x:c r="N14" s="14"/>
-      <x:c r="O14" s="14"/>
-      <x:c r="P14" s="14"/>
-      <x:c r="Q14" s="14"/>
-      <x:c r="R14" s="14"/>
+      <x:c r="C14" s="14" t="str">
+        <x:v>Playable</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>Mouse-only</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>Single SWF</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>Native</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N14" s="14" t="str">
+        <x:v>bejeweled-2.profile</x:v>
+      </x:c>
+      <x:c r="O14" s="14" t="str">
+        <x:v>0.8.21</x:v>
+      </x:c>
+      <x:c r="P14" s="31" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="Q14" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R14" s="14" t="str">
+        <x:v>King.com build runs well with high performance on the tested setup.</x:v>
+      </x:c>
       <x:c r="S14" s="14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="14"/>
-      <x:c r="B15" s="14"/>
-      <x:c r="C15" s="14"/>
-      <x:c r="D15" s="14"/>
-      <x:c r="E15" s="14"/>
-      <x:c r="F15" s="14"/>
-      <x:c r="G15" s="14"/>
-      <x:c r="H15" s="14"/>
-      <x:c r="I15" s="14"/>
-      <x:c r="J15" s="14"/>
-      <x:c r="K15" s="14"/>
-      <x:c r="L15" s="14"/>
-      <x:c r="M15" s="14"/>
-      <x:c r="N15" s="14"/>
-      <x:c r="O15" s="14"/>
-      <x:c r="P15" s="14"/>
-      <x:c r="Q15" s="14"/>
-      <x:c r="R15" s="14"/>
+      <x:c r="A15" s="14" t="str">
+        <x:v>We Dancing Online</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>we_dancing_online.swf</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>Playable</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>Custom profile</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>Hybrid</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str">
+        <x:v>Single SWF</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str">
+        <x:v>Native</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L15" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N15" s="14" t="str">
+        <x:v>we-dancing-online.profile</x:v>
+      </x:c>
+      <x:c r="O15" s="14" t="str">
+        <x:v>0.8.21</x:v>
+      </x:c>
+      <x:c r="P15" s="31" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="Q15" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R15" s="14" t="str">
+        <x:v>Runs well with high performance. D-pad/keyboard mapping and mouse-menu click profile in use.</x:v>
+      </x:c>
       <x:c r="S15" s="14"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="14"/>
+      <x:c r="A16" s="14" t="str">
+        <x:v>Ultimate Flash Sonic</x:v>
+      </x:c>
       <x:c r="B16" s="14"/>
-      <x:c r="C16" s="14"/>
-      <x:c r="D16" s="14"/>
-      <x:c r="E16" s="14"/>
-      <x:c r="F16" s="14"/>
-      <x:c r="G16" s="14"/>
-      <x:c r="H16" s="14"/>
-      <x:c r="I16" s="14"/>
-      <x:c r="J16" s="14"/>
-      <x:c r="K16" s="14"/>
-      <x:c r="L16" s="14"/>
-      <x:c r="M16" s="14"/>
-      <x:c r="N16" s="14"/>
-      <x:c r="O16" s="14"/>
-      <x:c r="P16" s="14"/>
-      <x:c r="Q16" s="14"/>
-      <x:c r="R16" s="14"/>
+      <x:c r="C16" s="14" t="str">
+        <x:v>Playable</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>Custom profile</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
+        <x:v>Hybrid</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str">
+        <x:v>Single SWF</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str">
+        <x:v>Native</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>EmuELEC</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="str">
+        <x:v>RK3326 handheld</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="str">
+        <x:v>RK3326</x:v>
+      </x:c>
+      <x:c r="L16" s="14" t="str">
+        <x:v>aarch64</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N16" s="14" t="str">
+        <x:v>ultimate-flash-sonic.profile</x:v>
+      </x:c>
+      <x:c r="O16" s="14" t="str">
+        <x:v>0.8.21</x:v>
+      </x:c>
+      <x:c r="P16" s="31" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="Q16" s="14" t="str">
+        <x:v>Maintainer</x:v>
+      </x:c>
+      <x:c r="R16" s="14" t="str">
+        <x:v>Playable with medium performance on the tested RK3326/EmuELEC setup.</x:v>
+      </x:c>
       <x:c r="S16" s="14"/>
     </x:row>
     <x:row r="17">
@@ -1472,7 +1684,7 @@
       <x:c r="M17" s="14"/>
       <x:c r="N17" s="14"/>
       <x:c r="O17" s="14"/>
-      <x:c r="P17" s="14"/>
+      <x:c r="P17" s="31"/>
       <x:c r="Q17" s="14"/>
       <x:c r="R17" s="14"/>
       <x:c r="S17" s="14"/>
@@ -1493,7 +1705,7 @@
       <x:c r="M18" s="14"/>
       <x:c r="N18" s="14"/>
       <x:c r="O18" s="14"/>
-      <x:c r="P18" s="14"/>
+      <x:c r="P18" s="31"/>
       <x:c r="Q18" s="14"/>
       <x:c r="R18" s="14"/>
       <x:c r="S18" s="14"/>
@@ -1514,7 +1726,7 @@
       <x:c r="M19" s="14"/>
       <x:c r="N19" s="14"/>
       <x:c r="O19" s="14"/>
-      <x:c r="P19" s="14"/>
+      <x:c r="P19" s="31"/>
       <x:c r="Q19" s="14"/>
       <x:c r="R19" s="14"/>
       <x:c r="S19" s="14"/>
@@ -1535,7 +1747,7 @@
       <x:c r="M20" s="14"/>
       <x:c r="N20" s="14"/>
       <x:c r="O20" s="14"/>
-      <x:c r="P20" s="14"/>
+      <x:c r="P20" s="31"/>
       <x:c r="Q20" s="14"/>
       <x:c r="R20" s="14"/>
       <x:c r="S20" s="14"/>
@@ -1556,7 +1768,7 @@
       <x:c r="M21" s="14"/>
       <x:c r="N21" s="14"/>
       <x:c r="O21" s="14"/>
-      <x:c r="P21" s="14"/>
+      <x:c r="P21" s="31"/>
       <x:c r="Q21" s="14"/>
       <x:c r="R21" s="14"/>
       <x:c r="S21" s="14"/>
@@ -1577,7 +1789,7 @@
       <x:c r="M22" s="14"/>
       <x:c r="N22" s="14"/>
       <x:c r="O22" s="14"/>
-      <x:c r="P22" s="14"/>
+      <x:c r="P22" s="31"/>
       <x:c r="Q22" s="14"/>
       <x:c r="R22" s="14"/>
       <x:c r="S22" s="14"/>
@@ -1598,7 +1810,7 @@
       <x:c r="M23" s="14"/>
       <x:c r="N23" s="14"/>
       <x:c r="O23" s="14"/>
-      <x:c r="P23" s="14"/>
+      <x:c r="P23" s="31"/>
       <x:c r="Q23" s="14"/>
       <x:c r="R23" s="14"/>
       <x:c r="S23" s="14"/>
@@ -1619,7 +1831,7 @@
       <x:c r="M24" s="14"/>
       <x:c r="N24" s="14"/>
       <x:c r="O24" s="14"/>
-      <x:c r="P24" s="14"/>
+      <x:c r="P24" s="31"/>
       <x:c r="Q24" s="14"/>
       <x:c r="R24" s="14"/>
       <x:c r="S24" s="14"/>
@@ -1640,7 +1852,7 @@
       <x:c r="M25" s="14"/>
       <x:c r="N25" s="14"/>
       <x:c r="O25" s="14"/>
-      <x:c r="P25" s="14"/>
+      <x:c r="P25" s="31"/>
       <x:c r="Q25" s="14"/>
       <x:c r="R25" s="14"/>
       <x:c r="S25" s="14"/>
@@ -1661,7 +1873,7 @@
       <x:c r="M26" s="14"/>
       <x:c r="N26" s="14"/>
       <x:c r="O26" s="14"/>
-      <x:c r="P26" s="14"/>
+      <x:c r="P26" s="31"/>
       <x:c r="Q26" s="14"/>
       <x:c r="R26" s="14"/>
       <x:c r="S26" s="14"/>
@@ -1682,7 +1894,7 @@
       <x:c r="M27" s="14"/>
       <x:c r="N27" s="14"/>
       <x:c r="O27" s="14"/>
-      <x:c r="P27" s="14"/>
+      <x:c r="P27" s="31"/>
       <x:c r="Q27" s="14"/>
       <x:c r="R27" s="14"/>
       <x:c r="S27" s="14"/>
@@ -1703,7 +1915,7 @@
       <x:c r="M28" s="14"/>
       <x:c r="N28" s="14"/>
       <x:c r="O28" s="14"/>
-      <x:c r="P28" s="14"/>
+      <x:c r="P28" s="31"/>
       <x:c r="Q28" s="14"/>
       <x:c r="R28" s="14"/>
       <x:c r="S28" s="14"/>
@@ -1724,7 +1936,7 @@
       <x:c r="M29" s="14"/>
       <x:c r="N29" s="14"/>
       <x:c r="O29" s="14"/>
-      <x:c r="P29" s="14"/>
+      <x:c r="P29" s="31"/>
       <x:c r="Q29" s="14"/>
       <x:c r="R29" s="14"/>
       <x:c r="S29" s="14"/>
@@ -1745,7 +1957,7 @@
       <x:c r="M30" s="14"/>
       <x:c r="N30" s="14"/>
       <x:c r="O30" s="14"/>
-      <x:c r="P30" s="14"/>
+      <x:c r="P30" s="31"/>
       <x:c r="Q30" s="14"/>
       <x:c r="R30" s="14"/>
       <x:c r="S30" s="14"/>
@@ -1766,7 +1978,7 @@
       <x:c r="M31" s="14"/>
       <x:c r="N31" s="14"/>
       <x:c r="O31" s="14"/>
-      <x:c r="P31" s="14"/>
+      <x:c r="P31" s="31"/>
       <x:c r="Q31" s="14"/>
       <x:c r="R31" s="14"/>
       <x:c r="S31" s="14"/>
@@ -1787,7 +1999,7 @@
       <x:c r="M32" s="14"/>
       <x:c r="N32" s="14"/>
       <x:c r="O32" s="14"/>
-      <x:c r="P32" s="14"/>
+      <x:c r="P32" s="31"/>
       <x:c r="Q32" s="14"/>
       <x:c r="R32" s="14"/>
       <x:c r="S32" s="14"/>
@@ -1808,7 +2020,7 @@
       <x:c r="M33" s="14"/>
       <x:c r="N33" s="14"/>
       <x:c r="O33" s="14"/>
-      <x:c r="P33" s="14"/>
+      <x:c r="P33" s="31"/>
       <x:c r="Q33" s="14"/>
       <x:c r="R33" s="14"/>
       <x:c r="S33" s="14"/>
@@ -1829,7 +2041,7 @@
       <x:c r="M34" s="14"/>
       <x:c r="N34" s="14"/>
       <x:c r="O34" s="14"/>
-      <x:c r="P34" s="14"/>
+      <x:c r="P34" s="31"/>
       <x:c r="Q34" s="14"/>
       <x:c r="R34" s="14"/>
       <x:c r="S34" s="14"/>
@@ -1850,7 +2062,7 @@
       <x:c r="M35" s="14"/>
       <x:c r="N35" s="14"/>
       <x:c r="O35" s="14"/>
-      <x:c r="P35" s="14"/>
+      <x:c r="P35" s="31"/>
       <x:c r="Q35" s="14"/>
       <x:c r="R35" s="14"/>
       <x:c r="S35" s="14"/>
@@ -1871,7 +2083,7 @@
       <x:c r="M36" s="14"/>
       <x:c r="N36" s="14"/>
       <x:c r="O36" s="14"/>
-      <x:c r="P36" s="14"/>
+      <x:c r="P36" s="31"/>
       <x:c r="Q36" s="14"/>
       <x:c r="R36" s="14"/>
       <x:c r="S36" s="14"/>
@@ -1892,7 +2104,7 @@
       <x:c r="M37" s="14"/>
       <x:c r="N37" s="14"/>
       <x:c r="O37" s="14"/>
-      <x:c r="P37" s="14"/>
+      <x:c r="P37" s="31"/>
       <x:c r="Q37" s="14"/>
       <x:c r="R37" s="14"/>
       <x:c r="S37" s="14"/>
@@ -1913,7 +2125,7 @@
       <x:c r="M38" s="14"/>
       <x:c r="N38" s="14"/>
       <x:c r="O38" s="14"/>
-      <x:c r="P38" s="14"/>
+      <x:c r="P38" s="31"/>
       <x:c r="Q38" s="14"/>
       <x:c r="R38" s="14"/>
       <x:c r="S38" s="14"/>
@@ -1934,7 +2146,7 @@
       <x:c r="M39" s="14"/>
       <x:c r="N39" s="14"/>
       <x:c r="O39" s="14"/>
-      <x:c r="P39" s="14"/>
+      <x:c r="P39" s="31"/>
       <x:c r="Q39" s="14"/>
       <x:c r="R39" s="14"/>
       <x:c r="S39" s="14"/>
@@ -1955,7 +2167,7 @@
       <x:c r="M40" s="14"/>
       <x:c r="N40" s="14"/>
       <x:c r="O40" s="14"/>
-      <x:c r="P40" s="14"/>
+      <x:c r="P40" s="31"/>
       <x:c r="Q40" s="14"/>
       <x:c r="R40" s="14"/>
       <x:c r="S40" s="14"/>
@@ -1976,7 +2188,7 @@
       <x:c r="M41" s="14"/>
       <x:c r="N41" s="14"/>
       <x:c r="O41" s="14"/>
-      <x:c r="P41" s="14"/>
+      <x:c r="P41" s="31"/>
       <x:c r="Q41" s="14"/>
       <x:c r="R41" s="14"/>
       <x:c r="S41" s="14"/>
@@ -1997,7 +2209,7 @@
       <x:c r="M42" s="14"/>
       <x:c r="N42" s="14"/>
       <x:c r="O42" s="14"/>
-      <x:c r="P42" s="14"/>
+      <x:c r="P42" s="31"/>
       <x:c r="Q42" s="14"/>
       <x:c r="R42" s="14"/>
       <x:c r="S42" s="14"/>
@@ -2018,7 +2230,7 @@
       <x:c r="M43" s="14"/>
       <x:c r="N43" s="14"/>
       <x:c r="O43" s="14"/>
-      <x:c r="P43" s="14"/>
+      <x:c r="P43" s="31"/>
       <x:c r="Q43" s="14"/>
       <x:c r="R43" s="14"/>
       <x:c r="S43" s="14"/>
@@ -2039,7 +2251,7 @@
       <x:c r="M44" s="14"/>
       <x:c r="N44" s="14"/>
       <x:c r="O44" s="14"/>
-      <x:c r="P44" s="14"/>
+      <x:c r="P44" s="31"/>
       <x:c r="Q44" s="14"/>
       <x:c r="R44" s="14"/>
       <x:c r="S44" s="14"/>
@@ -2060,7 +2272,7 @@
       <x:c r="M45" s="14"/>
       <x:c r="N45" s="14"/>
       <x:c r="O45" s="14"/>
-      <x:c r="P45" s="14"/>
+      <x:c r="P45" s="31"/>
       <x:c r="Q45" s="14"/>
       <x:c r="R45" s="14"/>
       <x:c r="S45" s="14"/>
@@ -2081,7 +2293,7 @@
       <x:c r="M46" s="14"/>
       <x:c r="N46" s="14"/>
       <x:c r="O46" s="14"/>
-      <x:c r="P46" s="14"/>
+      <x:c r="P46" s="31"/>
       <x:c r="Q46" s="14"/>
       <x:c r="R46" s="14"/>
       <x:c r="S46" s="14"/>
@@ -2102,7 +2314,7 @@
       <x:c r="M47" s="14"/>
       <x:c r="N47" s="14"/>
       <x:c r="O47" s="14"/>
-      <x:c r="P47" s="14"/>
+      <x:c r="P47" s="31"/>
       <x:c r="Q47" s="14"/>
       <x:c r="R47" s="14"/>
       <x:c r="S47" s="14"/>
@@ -2123,7 +2335,7 @@
       <x:c r="M48" s="14"/>
       <x:c r="N48" s="14"/>
       <x:c r="O48" s="14"/>
-      <x:c r="P48" s="14"/>
+      <x:c r="P48" s="31"/>
       <x:c r="Q48" s="14"/>
       <x:c r="R48" s="14"/>
       <x:c r="S48" s="14"/>
@@ -2144,7 +2356,7 @@
       <x:c r="M49" s="14"/>
       <x:c r="N49" s="14"/>
       <x:c r="O49" s="14"/>
-      <x:c r="P49" s="14"/>
+      <x:c r="P49" s="31"/>
       <x:c r="Q49" s="14"/>
       <x:c r="R49" s="14"/>
       <x:c r="S49" s="14"/>
@@ -2165,7 +2377,7 @@
       <x:c r="M50" s="14"/>
       <x:c r="N50" s="14"/>
       <x:c r="O50" s="14"/>
-      <x:c r="P50" s="14"/>
+      <x:c r="P50" s="31"/>
       <x:c r="Q50" s="14"/>
       <x:c r="R50" s="14"/>
       <x:c r="S50" s="14"/>
@@ -2186,7 +2398,7 @@
       <x:c r="M51" s="14"/>
       <x:c r="N51" s="14"/>
       <x:c r="O51" s="14"/>
-      <x:c r="P51" s="14"/>
+      <x:c r="P51" s="31"/>
       <x:c r="Q51" s="14"/>
       <x:c r="R51" s="14"/>
       <x:c r="S51" s="14"/>
@@ -2207,7 +2419,7 @@
       <x:c r="M52" s="14"/>
       <x:c r="N52" s="14"/>
       <x:c r="O52" s="14"/>
-      <x:c r="P52" s="14"/>
+      <x:c r="P52" s="31"/>
       <x:c r="Q52" s="14"/>
       <x:c r="R52" s="14"/>
       <x:c r="S52" s="14"/>
@@ -2228,7 +2440,7 @@
       <x:c r="M53" s="14"/>
       <x:c r="N53" s="14"/>
       <x:c r="O53" s="14"/>
-      <x:c r="P53" s="14"/>
+      <x:c r="P53" s="31"/>
       <x:c r="Q53" s="14"/>
       <x:c r="R53" s="14"/>
       <x:c r="S53" s="14"/>
@@ -2249,7 +2461,7 @@
       <x:c r="M54" s="14"/>
       <x:c r="N54" s="14"/>
       <x:c r="O54" s="14"/>
-      <x:c r="P54" s="14"/>
+      <x:c r="P54" s="31"/>
       <x:c r="Q54" s="14"/>
       <x:c r="R54" s="14"/>
       <x:c r="S54" s="14"/>
@@ -2270,7 +2482,7 @@
       <x:c r="M55" s="14"/>
       <x:c r="N55" s="14"/>
       <x:c r="O55" s="14"/>
-      <x:c r="P55" s="14"/>
+      <x:c r="P55" s="31"/>
       <x:c r="Q55" s="14"/>
       <x:c r="R55" s="14"/>
       <x:c r="S55" s="14"/>
@@ -2291,7 +2503,7 @@
       <x:c r="M56" s="14"/>
       <x:c r="N56" s="14"/>
       <x:c r="O56" s="14"/>
-      <x:c r="P56" s="14"/>
+      <x:c r="P56" s="31"/>
       <x:c r="Q56" s="14"/>
       <x:c r="R56" s="14"/>
       <x:c r="S56" s="14"/>
@@ -2312,7 +2524,7 @@
       <x:c r="M57" s="14"/>
       <x:c r="N57" s="14"/>
       <x:c r="O57" s="14"/>
-      <x:c r="P57" s="14"/>
+      <x:c r="P57" s="31"/>
       <x:c r="Q57" s="14"/>
       <x:c r="R57" s="14"/>
       <x:c r="S57" s="14"/>
@@ -2333,7 +2545,7 @@
       <x:c r="M58" s="14"/>
       <x:c r="N58" s="14"/>
       <x:c r="O58" s="14"/>
-      <x:c r="P58" s="14"/>
+      <x:c r="P58" s="31"/>
       <x:c r="Q58" s="14"/>
       <x:c r="R58" s="14"/>
       <x:c r="S58" s="14"/>
@@ -2354,7 +2566,7 @@
       <x:c r="M59" s="14"/>
       <x:c r="N59" s="14"/>
       <x:c r="O59" s="14"/>
-      <x:c r="P59" s="14"/>
+      <x:c r="P59" s="31"/>
       <x:c r="Q59" s="14"/>
       <x:c r="R59" s="14"/>
       <x:c r="S59" s="14"/>
@@ -2375,7 +2587,7 @@
       <x:c r="M60" s="14"/>
       <x:c r="N60" s="14"/>
       <x:c r="O60" s="14"/>
-      <x:c r="P60" s="14"/>
+      <x:c r="P60" s="31"/>
       <x:c r="Q60" s="14"/>
       <x:c r="R60" s="14"/>
       <x:c r="S60" s="14"/>
@@ -2396,7 +2608,7 @@
       <x:c r="M61" s="14"/>
       <x:c r="N61" s="14"/>
       <x:c r="O61" s="14"/>
-      <x:c r="P61" s="14"/>
+      <x:c r="P61" s="31"/>
       <x:c r="Q61" s="14"/>
       <x:c r="R61" s="14"/>
       <x:c r="S61" s="14"/>
@@ -2417,7 +2629,7 @@
       <x:c r="M62" s="14"/>
       <x:c r="N62" s="14"/>
       <x:c r="O62" s="14"/>
-      <x:c r="P62" s="14"/>
+      <x:c r="P62" s="31"/>
       <x:c r="Q62" s="14"/>
       <x:c r="R62" s="14"/>
       <x:c r="S62" s="14"/>
@@ -2438,7 +2650,7 @@
       <x:c r="M63" s="14"/>
       <x:c r="N63" s="14"/>
       <x:c r="O63" s="14"/>
-      <x:c r="P63" s="14"/>
+      <x:c r="P63" s="31"/>
       <x:c r="Q63" s="14"/>
       <x:c r="R63" s="14"/>
       <x:c r="S63" s="14"/>
@@ -2459,7 +2671,7 @@
       <x:c r="M64" s="14"/>
       <x:c r="N64" s="14"/>
       <x:c r="O64" s="14"/>
-      <x:c r="P64" s="14"/>
+      <x:c r="P64" s="31"/>
       <x:c r="Q64" s="14"/>
       <x:c r="R64" s="14"/>
       <x:c r="S64" s="14"/>
@@ -2480,7 +2692,7 @@
       <x:c r="M65" s="14"/>
       <x:c r="N65" s="14"/>
       <x:c r="O65" s="14"/>
-      <x:c r="P65" s="14"/>
+      <x:c r="P65" s="31"/>
       <x:c r="Q65" s="14"/>
       <x:c r="R65" s="14"/>
       <x:c r="S65" s="14"/>
@@ -2501,7 +2713,7 @@
       <x:c r="M66" s="14"/>
       <x:c r="N66" s="14"/>
       <x:c r="O66" s="14"/>
-      <x:c r="P66" s="14"/>
+      <x:c r="P66" s="31"/>
       <x:c r="Q66" s="14"/>
       <x:c r="R66" s="14"/>
       <x:c r="S66" s="14"/>
@@ -2522,7 +2734,7 @@
       <x:c r="M67" s="14"/>
       <x:c r="N67" s="14"/>
       <x:c r="O67" s="14"/>
-      <x:c r="P67" s="14"/>
+      <x:c r="P67" s="31"/>
       <x:c r="Q67" s="14"/>
       <x:c r="R67" s="14"/>
       <x:c r="S67" s="14"/>
@@ -2543,7 +2755,7 @@
       <x:c r="M68" s="14"/>
       <x:c r="N68" s="14"/>
       <x:c r="O68" s="14"/>
-      <x:c r="P68" s="14"/>
+      <x:c r="P68" s="31"/>
       <x:c r="Q68" s="14"/>
       <x:c r="R68" s="14"/>
       <x:c r="S68" s="14"/>
@@ -2564,7 +2776,7 @@
       <x:c r="M69" s="14"/>
       <x:c r="N69" s="14"/>
       <x:c r="O69" s="14"/>
-      <x:c r="P69" s="14"/>
+      <x:c r="P69" s="31"/>
       <x:c r="Q69" s="14"/>
       <x:c r="R69" s="14"/>
       <x:c r="S69" s="14"/>
@@ -2585,7 +2797,7 @@
       <x:c r="M70" s="14"/>
       <x:c r="N70" s="14"/>
       <x:c r="O70" s="14"/>
-      <x:c r="P70" s="14"/>
+      <x:c r="P70" s="31"/>
       <x:c r="Q70" s="14"/>
       <x:c r="R70" s="14"/>
       <x:c r="S70" s="14"/>
@@ -2606,7 +2818,7 @@
       <x:c r="M71" s="14"/>
       <x:c r="N71" s="14"/>
       <x:c r="O71" s="14"/>
-      <x:c r="P71" s="14"/>
+      <x:c r="P71" s="31"/>
       <x:c r="Q71" s="14"/>
       <x:c r="R71" s="14"/>
       <x:c r="S71" s="14"/>
@@ -2627,7 +2839,7 @@
       <x:c r="M72" s="14"/>
       <x:c r="N72" s="14"/>
       <x:c r="O72" s="14"/>
-      <x:c r="P72" s="14"/>
+      <x:c r="P72" s="31"/>
       <x:c r="Q72" s="14"/>
       <x:c r="R72" s="14"/>
       <x:c r="S72" s="14"/>
@@ -2648,7 +2860,7 @@
       <x:c r="M73" s="14"/>
       <x:c r="N73" s="14"/>
       <x:c r="O73" s="14"/>
-      <x:c r="P73" s="14"/>
+      <x:c r="P73" s="31"/>
       <x:c r="Q73" s="14"/>
       <x:c r="R73" s="14"/>
       <x:c r="S73" s="14"/>
@@ -2669,7 +2881,7 @@
       <x:c r="M74" s="14"/>
       <x:c r="N74" s="14"/>
       <x:c r="O74" s="14"/>
-      <x:c r="P74" s="14"/>
+      <x:c r="P74" s="31"/>
       <x:c r="Q74" s="14"/>
       <x:c r="R74" s="14"/>
       <x:c r="S74" s="14"/>
@@ -2690,7 +2902,7 @@
       <x:c r="M75" s="14"/>
       <x:c r="N75" s="14"/>
       <x:c r="O75" s="14"/>
-      <x:c r="P75" s="14"/>
+      <x:c r="P75" s="31"/>
       <x:c r="Q75" s="14"/>
       <x:c r="R75" s="14"/>
       <x:c r="S75" s="14"/>
@@ -2711,7 +2923,7 @@
       <x:c r="M76" s="14"/>
       <x:c r="N76" s="14"/>
       <x:c r="O76" s="14"/>
-      <x:c r="P76" s="14"/>
+      <x:c r="P76" s="31"/>
       <x:c r="Q76" s="14"/>
       <x:c r="R76" s="14"/>
       <x:c r="S76" s="14"/>
@@ -2732,7 +2944,7 @@
       <x:c r="M77" s="14"/>
       <x:c r="N77" s="14"/>
       <x:c r="O77" s="14"/>
-      <x:c r="P77" s="14"/>
+      <x:c r="P77" s="31"/>
       <x:c r="Q77" s="14"/>
       <x:c r="R77" s="14"/>
       <x:c r="S77" s="14"/>
@@ -2753,7 +2965,7 @@
       <x:c r="M78" s="14"/>
       <x:c r="N78" s="14"/>
       <x:c r="O78" s="14"/>
-      <x:c r="P78" s="14"/>
+      <x:c r="P78" s="31"/>
       <x:c r="Q78" s="14"/>
       <x:c r="R78" s="14"/>
       <x:c r="S78" s="14"/>
@@ -2774,7 +2986,7 @@
       <x:c r="M79" s="14"/>
       <x:c r="N79" s="14"/>
       <x:c r="O79" s="14"/>
-      <x:c r="P79" s="14"/>
+      <x:c r="P79" s="31"/>
       <x:c r="Q79" s="14"/>
       <x:c r="R79" s="14"/>
       <x:c r="S79" s="14"/>
@@ -2795,7 +3007,7 @@
       <x:c r="M80" s="14"/>
       <x:c r="N80" s="14"/>
       <x:c r="O80" s="14"/>
-      <x:c r="P80" s="14"/>
+      <x:c r="P80" s="31"/>
       <x:c r="Q80" s="14"/>
       <x:c r="R80" s="14"/>
       <x:c r="S80" s="14"/>
@@ -2816,7 +3028,7 @@
       <x:c r="M81" s="14"/>
       <x:c r="N81" s="14"/>
       <x:c r="O81" s="14"/>
-      <x:c r="P81" s="14"/>
+      <x:c r="P81" s="31"/>
       <x:c r="Q81" s="14"/>
       <x:c r="R81" s="14"/>
       <x:c r="S81" s="14"/>
@@ -2837,7 +3049,7 @@
       <x:c r="M82" s="14"/>
       <x:c r="N82" s="14"/>
       <x:c r="O82" s="14"/>
-      <x:c r="P82" s="14"/>
+      <x:c r="P82" s="31"/>
       <x:c r="Q82" s="14"/>
       <x:c r="R82" s="14"/>
       <x:c r="S82" s="14"/>
@@ -2858,7 +3070,7 @@
       <x:c r="M83" s="14"/>
       <x:c r="N83" s="14"/>
       <x:c r="O83" s="14"/>
-      <x:c r="P83" s="14"/>
+      <x:c r="P83" s="31"/>
       <x:c r="Q83" s="14"/>
       <x:c r="R83" s="14"/>
       <x:c r="S83" s="14"/>
@@ -2879,7 +3091,7 @@
       <x:c r="M84" s="14"/>
       <x:c r="N84" s="14"/>
       <x:c r="O84" s="14"/>
-      <x:c r="P84" s="14"/>
+      <x:c r="P84" s="31"/>
       <x:c r="Q84" s="14"/>
       <x:c r="R84" s="14"/>
       <x:c r="S84" s="14"/>
@@ -2900,7 +3112,7 @@
       <x:c r="M85" s="14"/>
       <x:c r="N85" s="14"/>
       <x:c r="O85" s="14"/>
-      <x:c r="P85" s="14"/>
+      <x:c r="P85" s="31"/>
       <x:c r="Q85" s="14"/>
       <x:c r="R85" s="14"/>
       <x:c r="S85" s="14"/>
@@ -2921,7 +3133,7 @@
       <x:c r="M86" s="14"/>
       <x:c r="N86" s="14"/>
       <x:c r="O86" s="14"/>
-      <x:c r="P86" s="14"/>
+      <x:c r="P86" s="31"/>
       <x:c r="Q86" s="14"/>
       <x:c r="R86" s="14"/>
       <x:c r="S86" s="14"/>
@@ -2942,7 +3154,7 @@
       <x:c r="M87" s="14"/>
       <x:c r="N87" s="14"/>
       <x:c r="O87" s="14"/>
-      <x:c r="P87" s="14"/>
+      <x:c r="P87" s="31"/>
       <x:c r="Q87" s="14"/>
       <x:c r="R87" s="14"/>
       <x:c r="S87" s="14"/>
@@ -2963,7 +3175,7 @@
       <x:c r="M88" s="14"/>
       <x:c r="N88" s="14"/>
       <x:c r="O88" s="14"/>
-      <x:c r="P88" s="14"/>
+      <x:c r="P88" s="31"/>
       <x:c r="Q88" s="14"/>
       <x:c r="R88" s="14"/>
       <x:c r="S88" s="14"/>
@@ -2984,7 +3196,7 @@
       <x:c r="M89" s="14"/>
       <x:c r="N89" s="14"/>
       <x:c r="O89" s="14"/>
-      <x:c r="P89" s="14"/>
+      <x:c r="P89" s="31"/>
       <x:c r="Q89" s="14"/>
       <x:c r="R89" s="14"/>
       <x:c r="S89" s="14"/>
@@ -3005,7 +3217,7 @@
       <x:c r="M90" s="14"/>
       <x:c r="N90" s="14"/>
       <x:c r="O90" s="14"/>
-      <x:c r="P90" s="14"/>
+      <x:c r="P90" s="31"/>
       <x:c r="Q90" s="14"/>
       <x:c r="R90" s="14"/>
       <x:c r="S90" s="14"/>
@@ -3026,7 +3238,7 @@
       <x:c r="M91" s="14"/>
       <x:c r="N91" s="14"/>
       <x:c r="O91" s="14"/>
-      <x:c r="P91" s="14"/>
+      <x:c r="P91" s="31"/>
       <x:c r="Q91" s="14"/>
       <x:c r="R91" s="14"/>
       <x:c r="S91" s="14"/>
@@ -3047,7 +3259,7 @@
       <x:c r="M92" s="14"/>
       <x:c r="N92" s="14"/>
       <x:c r="O92" s="14"/>
-      <x:c r="P92" s="14"/>
+      <x:c r="P92" s="31"/>
       <x:c r="Q92" s="14"/>
       <x:c r="R92" s="14"/>
       <x:c r="S92" s="14"/>
@@ -3068,7 +3280,7 @@
       <x:c r="M93" s="14"/>
       <x:c r="N93" s="14"/>
       <x:c r="O93" s="14"/>
-      <x:c r="P93" s="14"/>
+      <x:c r="P93" s="31"/>
       <x:c r="Q93" s="14"/>
       <x:c r="R93" s="14"/>
       <x:c r="S93" s="14"/>
@@ -3089,7 +3301,7 @@
       <x:c r="M94" s="14"/>
       <x:c r="N94" s="14"/>
       <x:c r="O94" s="14"/>
-      <x:c r="P94" s="14"/>
+      <x:c r="P94" s="31"/>
       <x:c r="Q94" s="14"/>
       <x:c r="R94" s="14"/>
       <x:c r="S94" s="14"/>
@@ -3110,7 +3322,7 @@
       <x:c r="M95" s="14"/>
       <x:c r="N95" s="14"/>
       <x:c r="O95" s="14"/>
-      <x:c r="P95" s="14"/>
+      <x:c r="P95" s="31"/>
       <x:c r="Q95" s="14"/>
       <x:c r="R95" s="14"/>
       <x:c r="S95" s="14"/>
@@ -3131,7 +3343,7 @@
       <x:c r="M96" s="14"/>
       <x:c r="N96" s="14"/>
       <x:c r="O96" s="14"/>
-      <x:c r="P96" s="14"/>
+      <x:c r="P96" s="31"/>
       <x:c r="Q96" s="14"/>
       <x:c r="R96" s="14"/>
       <x:c r="S96" s="14"/>
@@ -3152,7 +3364,7 @@
       <x:c r="M97" s="14"/>
       <x:c r="N97" s="14"/>
       <x:c r="O97" s="14"/>
-      <x:c r="P97" s="14"/>
+      <x:c r="P97" s="31"/>
       <x:c r="Q97" s="14"/>
       <x:c r="R97" s="14"/>
       <x:c r="S97" s="14"/>
@@ -3173,7 +3385,7 @@
       <x:c r="M98" s="14"/>
       <x:c r="N98" s="14"/>
       <x:c r="O98" s="14"/>
-      <x:c r="P98" s="14"/>
+      <x:c r="P98" s="31"/>
       <x:c r="Q98" s="14"/>
       <x:c r="R98" s="14"/>
       <x:c r="S98" s="14"/>
@@ -3194,7 +3406,7 @@
       <x:c r="M99" s="14"/>
       <x:c r="N99" s="14"/>
       <x:c r="O99" s="14"/>
-      <x:c r="P99" s="14"/>
+      <x:c r="P99" s="31"/>
       <x:c r="Q99" s="14"/>
       <x:c r="R99" s="14"/>
       <x:c r="S99" s="14"/>
@@ -3215,7 +3427,7 @@
       <x:c r="M100" s="14"/>
       <x:c r="N100" s="14"/>
       <x:c r="O100" s="14"/>
-      <x:c r="P100" s="14"/>
+      <x:c r="P100" s="31"/>
       <x:c r="Q100" s="14"/>
       <x:c r="R100" s="14"/>
       <x:c r="S100" s="14"/>
@@ -3236,7 +3448,7 @@
       <x:c r="M101" s="14"/>
       <x:c r="N101" s="14"/>
       <x:c r="O101" s="14"/>
-      <x:c r="P101" s="14"/>
+      <x:c r="P101" s="31"/>
       <x:c r="Q101" s="14"/>
       <x:c r="R101" s="14"/>
       <x:c r="S101" s="14"/>
@@ -3257,7 +3469,7 @@
       <x:c r="M102" s="14"/>
       <x:c r="N102" s="14"/>
       <x:c r="O102" s="14"/>
-      <x:c r="P102" s="14"/>
+      <x:c r="P102" s="31"/>
       <x:c r="Q102" s="14"/>
       <x:c r="R102" s="14"/>
       <x:c r="S102" s="14"/>
@@ -3278,7 +3490,7 @@
       <x:c r="M103" s="14"/>
       <x:c r="N103" s="14"/>
       <x:c r="O103" s="14"/>
-      <x:c r="P103" s="14"/>
+      <x:c r="P103" s="31"/>
       <x:c r="Q103" s="14"/>
       <x:c r="R103" s="14"/>
       <x:c r="S103" s="14"/>
@@ -3299,7 +3511,7 @@
       <x:c r="M104" s="14"/>
       <x:c r="N104" s="14"/>
       <x:c r="O104" s="14"/>
-      <x:c r="P104" s="14"/>
+      <x:c r="P104" s="31"/>
       <x:c r="Q104" s="14"/>
       <x:c r="R104" s="14"/>
       <x:c r="S104" s="14"/>
@@ -3320,7 +3532,7 @@
       <x:c r="M105" s="14"/>
       <x:c r="N105" s="14"/>
       <x:c r="O105" s="14"/>
-      <x:c r="P105" s="14"/>
+      <x:c r="P105" s="31"/>
       <x:c r="Q105" s="14"/>
       <x:c r="R105" s="14"/>
       <x:c r="S105" s="14"/>
@@ -3341,7 +3553,7 @@
       <x:c r="M106" s="14"/>
       <x:c r="N106" s="14"/>
       <x:c r="O106" s="14"/>
-      <x:c r="P106" s="14"/>
+      <x:c r="P106" s="31"/>
       <x:c r="Q106" s="14"/>
       <x:c r="R106" s="14"/>
       <x:c r="S106" s="14"/>
@@ -3362,7 +3574,7 @@
       <x:c r="M107" s="14"/>
       <x:c r="N107" s="14"/>
       <x:c r="O107" s="14"/>
-      <x:c r="P107" s="14"/>
+      <x:c r="P107" s="31"/>
       <x:c r="Q107" s="14"/>
       <x:c r="R107" s="14"/>
       <x:c r="S107" s="14"/>
@@ -3383,7 +3595,7 @@
       <x:c r="M108" s="14"/>
       <x:c r="N108" s="14"/>
       <x:c r="O108" s="14"/>
-      <x:c r="P108" s="14"/>
+      <x:c r="P108" s="31"/>
       <x:c r="Q108" s="14"/>
       <x:c r="R108" s="14"/>
       <x:c r="S108" s="14"/>
@@ -3404,7 +3616,7 @@
       <x:c r="M109" s="14"/>
       <x:c r="N109" s="14"/>
       <x:c r="O109" s="14"/>
-      <x:c r="P109" s="14"/>
+      <x:c r="P109" s="31"/>
       <x:c r="Q109" s="14"/>
       <x:c r="R109" s="14"/>
       <x:c r="S109" s="14"/>
@@ -3425,7 +3637,7 @@
       <x:c r="M110" s="14"/>
       <x:c r="N110" s="14"/>
       <x:c r="O110" s="14"/>
-      <x:c r="P110" s="14"/>
+      <x:c r="P110" s="31"/>
       <x:c r="Q110" s="14"/>
       <x:c r="R110" s="14"/>
       <x:c r="S110" s="14"/>
@@ -3446,7 +3658,7 @@
       <x:c r="M111" s="14"/>
       <x:c r="N111" s="14"/>
       <x:c r="O111" s="14"/>
-      <x:c r="P111" s="14"/>
+      <x:c r="P111" s="31"/>
       <x:c r="Q111" s="14"/>
       <x:c r="R111" s="14"/>
       <x:c r="S111" s="14"/>
@@ -3467,7 +3679,7 @@
       <x:c r="M112" s="14"/>
       <x:c r="N112" s="14"/>
       <x:c r="O112" s="14"/>
-      <x:c r="P112" s="14"/>
+      <x:c r="P112" s="31"/>
       <x:c r="Q112" s="14"/>
       <x:c r="R112" s="14"/>
       <x:c r="S112" s="14"/>
@@ -3488,7 +3700,7 @@
       <x:c r="M113" s="14"/>
       <x:c r="N113" s="14"/>
       <x:c r="O113" s="14"/>
-      <x:c r="P113" s="14"/>
+      <x:c r="P113" s="31"/>
       <x:c r="Q113" s="14"/>
       <x:c r="R113" s="14"/>
       <x:c r="S113" s="14"/>
@@ -3509,7 +3721,7 @@
       <x:c r="M114" s="14"/>
       <x:c r="N114" s="14"/>
       <x:c r="O114" s="14"/>
-      <x:c r="P114" s="14"/>
+      <x:c r="P114" s="31"/>
       <x:c r="Q114" s="14"/>
       <x:c r="R114" s="14"/>
       <x:c r="S114" s="14"/>
@@ -3530,7 +3742,7 @@
       <x:c r="M115" s="14"/>
       <x:c r="N115" s="14"/>
       <x:c r="O115" s="14"/>
-      <x:c r="P115" s="14"/>
+      <x:c r="P115" s="31"/>
       <x:c r="Q115" s="14"/>
       <x:c r="R115" s="14"/>
       <x:c r="S115" s="14"/>
@@ -3551,7 +3763,7 @@
       <x:c r="M116" s="14"/>
       <x:c r="N116" s="14"/>
       <x:c r="O116" s="14"/>
-      <x:c r="P116" s="14"/>
+      <x:c r="P116" s="31"/>
       <x:c r="Q116" s="14"/>
       <x:c r="R116" s="14"/>
       <x:c r="S116" s="14"/>
@@ -3572,7 +3784,7 @@
       <x:c r="M117" s="14"/>
       <x:c r="N117" s="14"/>
       <x:c r="O117" s="14"/>
-      <x:c r="P117" s="14"/>
+      <x:c r="P117" s="31"/>
       <x:c r="Q117" s="14"/>
       <x:c r="R117" s="14"/>
       <x:c r="S117" s="14"/>
@@ -3593,7 +3805,7 @@
       <x:c r="M118" s="14"/>
       <x:c r="N118" s="14"/>
       <x:c r="O118" s="14"/>
-      <x:c r="P118" s="14"/>
+      <x:c r="P118" s="31"/>
       <x:c r="Q118" s="14"/>
       <x:c r="R118" s="14"/>
       <x:c r="S118" s="14"/>
@@ -3614,7 +3826,7 @@
       <x:c r="M119" s="14"/>
       <x:c r="N119" s="14"/>
       <x:c r="O119" s="14"/>
-      <x:c r="P119" s="14"/>
+      <x:c r="P119" s="31"/>
       <x:c r="Q119" s="14"/>
       <x:c r="R119" s="14"/>
       <x:c r="S119" s="14"/>
@@ -3635,7 +3847,7 @@
       <x:c r="M120" s="14"/>
       <x:c r="N120" s="14"/>
       <x:c r="O120" s="14"/>
-      <x:c r="P120" s="14"/>
+      <x:c r="P120" s="31"/>
       <x:c r="Q120" s="14"/>
       <x:c r="R120" s="14"/>
       <x:c r="S120" s="14"/>
@@ -3656,7 +3868,7 @@
       <x:c r="M121" s="14"/>
       <x:c r="N121" s="14"/>
       <x:c r="O121" s="14"/>
-      <x:c r="P121" s="14"/>
+      <x:c r="P121" s="31"/>
       <x:c r="Q121" s="14"/>
       <x:c r="R121" s="14"/>
       <x:c r="S121" s="14"/>
@@ -3677,7 +3889,7 @@
       <x:c r="M122" s="14"/>
       <x:c r="N122" s="14"/>
       <x:c r="O122" s="14"/>
-      <x:c r="P122" s="14"/>
+      <x:c r="P122" s="31"/>
       <x:c r="Q122" s="14"/>
       <x:c r="R122" s="14"/>
       <x:c r="S122" s="14"/>
@@ -3698,7 +3910,7 @@
       <x:c r="M123" s="14"/>
       <x:c r="N123" s="14"/>
       <x:c r="O123" s="14"/>
-      <x:c r="P123" s="14"/>
+      <x:c r="P123" s="31"/>
       <x:c r="Q123" s="14"/>
       <x:c r="R123" s="14"/>
       <x:c r="S123" s="14"/>
@@ -3719,7 +3931,7 @@
       <x:c r="M124" s="14"/>
       <x:c r="N124" s="14"/>
       <x:c r="O124" s="14"/>
-      <x:c r="P124" s="14"/>
+      <x:c r="P124" s="31"/>
       <x:c r="Q124" s="14"/>
       <x:c r="R124" s="14"/>
       <x:c r="S124" s="14"/>
@@ -3740,7 +3952,7 @@
       <x:c r="M125" s="14"/>
       <x:c r="N125" s="14"/>
       <x:c r="O125" s="14"/>
-      <x:c r="P125" s="14"/>
+      <x:c r="P125" s="31"/>
       <x:c r="Q125" s="14"/>
       <x:c r="R125" s="14"/>
       <x:c r="S125" s="14"/>
@@ -3761,7 +3973,7 @@
       <x:c r="M126" s="14"/>
       <x:c r="N126" s="14"/>
       <x:c r="O126" s="14"/>
-      <x:c r="P126" s="14"/>
+      <x:c r="P126" s="31"/>
       <x:c r="Q126" s="14"/>
       <x:c r="R126" s="14"/>
       <x:c r="S126" s="14"/>
@@ -3782,7 +3994,7 @@
       <x:c r="M127" s="14"/>
       <x:c r="N127" s="14"/>
       <x:c r="O127" s="14"/>
-      <x:c r="P127" s="14"/>
+      <x:c r="P127" s="31"/>
       <x:c r="Q127" s="14"/>
       <x:c r="R127" s="14"/>
       <x:c r="S127" s="14"/>
@@ -3803,7 +4015,7 @@
       <x:c r="M128" s="14"/>
       <x:c r="N128" s="14"/>
       <x:c r="O128" s="14"/>
-      <x:c r="P128" s="14"/>
+      <x:c r="P128" s="31"/>
       <x:c r="Q128" s="14"/>
       <x:c r="R128" s="14"/>
       <x:c r="S128" s="14"/>
@@ -3824,7 +4036,7 @@
       <x:c r="M129" s="14"/>
       <x:c r="N129" s="14"/>
       <x:c r="O129" s="14"/>
-      <x:c r="P129" s="14"/>
+      <x:c r="P129" s="31"/>
       <x:c r="Q129" s="14"/>
       <x:c r="R129" s="14"/>
       <x:c r="S129" s="14"/>
@@ -3845,7 +4057,7 @@
       <x:c r="M130" s="14"/>
       <x:c r="N130" s="14"/>
       <x:c r="O130" s="14"/>
-      <x:c r="P130" s="14"/>
+      <x:c r="P130" s="31"/>
       <x:c r="Q130" s="14"/>
       <x:c r="R130" s="14"/>
       <x:c r="S130" s="14"/>
@@ -3866,7 +4078,7 @@
       <x:c r="M131" s="14"/>
       <x:c r="N131" s="14"/>
       <x:c r="O131" s="14"/>
-      <x:c r="P131" s="14"/>
+      <x:c r="P131" s="31"/>
       <x:c r="Q131" s="14"/>
       <x:c r="R131" s="14"/>
       <x:c r="S131" s="14"/>
@@ -3887,7 +4099,7 @@
       <x:c r="M132" s="14"/>
       <x:c r="N132" s="14"/>
       <x:c r="O132" s="14"/>
-      <x:c r="P132" s="14"/>
+      <x:c r="P132" s="31"/>
       <x:c r="Q132" s="14"/>
       <x:c r="R132" s="14"/>
       <x:c r="S132" s="14"/>
@@ -3908,7 +4120,7 @@
       <x:c r="M133" s="14"/>
       <x:c r="N133" s="14"/>
       <x:c r="O133" s="14"/>
-      <x:c r="P133" s="14"/>
+      <x:c r="P133" s="31"/>
       <x:c r="Q133" s="14"/>
       <x:c r="R133" s="14"/>
       <x:c r="S133" s="14"/>
@@ -3929,7 +4141,7 @@
       <x:c r="M134" s="14"/>
       <x:c r="N134" s="14"/>
       <x:c r="O134" s="14"/>
-      <x:c r="P134" s="14"/>
+      <x:c r="P134" s="31"/>
       <x:c r="Q134" s="14"/>
       <x:c r="R134" s="14"/>
       <x:c r="S134" s="14"/>
@@ -3950,7 +4162,7 @@
       <x:c r="M135" s="14"/>
       <x:c r="N135" s="14"/>
       <x:c r="O135" s="14"/>
-      <x:c r="P135" s="14"/>
+      <x:c r="P135" s="31"/>
       <x:c r="Q135" s="14"/>
       <x:c r="R135" s="14"/>
       <x:c r="S135" s="14"/>
@@ -3971,7 +4183,7 @@
       <x:c r="M136" s="14"/>
       <x:c r="N136" s="14"/>
       <x:c r="O136" s="14"/>
-      <x:c r="P136" s="14"/>
+      <x:c r="P136" s="31"/>
       <x:c r="Q136" s="14"/>
       <x:c r="R136" s="14"/>
       <x:c r="S136" s="14"/>
@@ -3992,7 +4204,7 @@
       <x:c r="M137" s="14"/>
       <x:c r="N137" s="14"/>
       <x:c r="O137" s="14"/>
-      <x:c r="P137" s="14"/>
+      <x:c r="P137" s="31"/>
       <x:c r="Q137" s="14"/>
       <x:c r="R137" s="14"/>
       <x:c r="S137" s="14"/>
@@ -4013,7 +4225,7 @@
       <x:c r="M138" s="14"/>
       <x:c r="N138" s="14"/>
       <x:c r="O138" s="14"/>
-      <x:c r="P138" s="14"/>
+      <x:c r="P138" s="31"/>
       <x:c r="Q138" s="14"/>
       <x:c r="R138" s="14"/>
       <x:c r="S138" s="14"/>
@@ -4034,7 +4246,7 @@
       <x:c r="M139" s="14"/>
       <x:c r="N139" s="14"/>
       <x:c r="O139" s="14"/>
-      <x:c r="P139" s="14"/>
+      <x:c r="P139" s="31"/>
       <x:c r="Q139" s="14"/>
       <x:c r="R139" s="14"/>
       <x:c r="S139" s="14"/>
@@ -4055,7 +4267,7 @@
       <x:c r="M140" s="14"/>
       <x:c r="N140" s="14"/>
       <x:c r="O140" s="14"/>
-      <x:c r="P140" s="14"/>
+      <x:c r="P140" s="31"/>
       <x:c r="Q140" s="14"/>
       <x:c r="R140" s="14"/>
       <x:c r="S140" s="14"/>
@@ -4076,7 +4288,7 @@
       <x:c r="M141" s="14"/>
       <x:c r="N141" s="14"/>
       <x:c r="O141" s="14"/>
-      <x:c r="P141" s="14"/>
+      <x:c r="P141" s="31"/>
       <x:c r="Q141" s="14"/>
       <x:c r="R141" s="14"/>
       <x:c r="S141" s="14"/>
@@ -4097,7 +4309,7 @@
       <x:c r="M142" s="14"/>
       <x:c r="N142" s="14"/>
       <x:c r="O142" s="14"/>
-      <x:c r="P142" s="14"/>
+      <x:c r="P142" s="31"/>
       <x:c r="Q142" s="14"/>
       <x:c r="R142" s="14"/>
       <x:c r="S142" s="14"/>
@@ -4118,7 +4330,7 @@
       <x:c r="M143" s="14"/>
       <x:c r="N143" s="14"/>
       <x:c r="O143" s="14"/>
-      <x:c r="P143" s="14"/>
+      <x:c r="P143" s="31"/>
       <x:c r="Q143" s="14"/>
       <x:c r="R143" s="14"/>
       <x:c r="S143" s="14"/>
@@ -4139,7 +4351,7 @@
       <x:c r="M144" s="14"/>
       <x:c r="N144" s="14"/>
       <x:c r="O144" s="14"/>
-      <x:c r="P144" s="14"/>
+      <x:c r="P144" s="31"/>
       <x:c r="Q144" s="14"/>
       <x:c r="R144" s="14"/>
       <x:c r="S144" s="14"/>
@@ -4160,7 +4372,7 @@
       <x:c r="M145" s="14"/>
       <x:c r="N145" s="14"/>
       <x:c r="O145" s="14"/>
-      <x:c r="P145" s="14"/>
+      <x:c r="P145" s="31"/>
       <x:c r="Q145" s="14"/>
       <x:c r="R145" s="14"/>
       <x:c r="S145" s="14"/>
@@ -4181,7 +4393,7 @@
       <x:c r="M146" s="14"/>
       <x:c r="N146" s="14"/>
       <x:c r="O146" s="14"/>
-      <x:c r="P146" s="14"/>
+      <x:c r="P146" s="31"/>
       <x:c r="Q146" s="14"/>
       <x:c r="R146" s="14"/>
       <x:c r="S146" s="14"/>
@@ -4202,7 +4414,7 @@
       <x:c r="M147" s="14"/>
       <x:c r="N147" s="14"/>
       <x:c r="O147" s="14"/>
-      <x:c r="P147" s="14"/>
+      <x:c r="P147" s="31"/>
       <x:c r="Q147" s="14"/>
       <x:c r="R147" s="14"/>
       <x:c r="S147" s="14"/>
@@ -4223,7 +4435,7 @@
       <x:c r="M148" s="14"/>
       <x:c r="N148" s="14"/>
       <x:c r="O148" s="14"/>
-      <x:c r="P148" s="14"/>
+      <x:c r="P148" s="31"/>
       <x:c r="Q148" s="14"/>
       <x:c r="R148" s="14"/>
       <x:c r="S148" s="14"/>
@@ -4244,7 +4456,7 @@
       <x:c r="M149" s="14"/>
       <x:c r="N149" s="14"/>
       <x:c r="O149" s="14"/>
-      <x:c r="P149" s="14"/>
+      <x:c r="P149" s="31"/>
       <x:c r="Q149" s="14"/>
       <x:c r="R149" s="14"/>
       <x:c r="S149" s="14"/>
@@ -4265,7 +4477,7 @@
       <x:c r="M150" s="14"/>
       <x:c r="N150" s="14"/>
       <x:c r="O150" s="14"/>
-      <x:c r="P150" s="14"/>
+      <x:c r="P150" s="31"/>
       <x:c r="Q150" s="14"/>
       <x:c r="R150" s="14"/>
       <x:c r="S150" s="14"/>
@@ -4286,7 +4498,7 @@
       <x:c r="M151" s="14"/>
       <x:c r="N151" s="14"/>
       <x:c r="O151" s="14"/>
-      <x:c r="P151" s="14"/>
+      <x:c r="P151" s="31"/>
       <x:c r="Q151" s="14"/>
       <x:c r="R151" s="14"/>
       <x:c r="S151" s="14"/>
@@ -4307,7 +4519,7 @@
       <x:c r="M152" s="14"/>
       <x:c r="N152" s="14"/>
       <x:c r="O152" s="14"/>
-      <x:c r="P152" s="14"/>
+      <x:c r="P152" s="31"/>
       <x:c r="Q152" s="14"/>
       <x:c r="R152" s="14"/>
       <x:c r="S152" s="14"/>
@@ -4328,7 +4540,7 @@
       <x:c r="M153" s="14"/>
       <x:c r="N153" s="14"/>
       <x:c r="O153" s="14"/>
-      <x:c r="P153" s="14"/>
+      <x:c r="P153" s="31"/>
       <x:c r="Q153" s="14"/>
       <x:c r="R153" s="14"/>
       <x:c r="S153" s="14"/>
@@ -4349,7 +4561,7 @@
       <x:c r="M154" s="14"/>
       <x:c r="N154" s="14"/>
       <x:c r="O154" s="14"/>
-      <x:c r="P154" s="14"/>
+      <x:c r="P154" s="31"/>
       <x:c r="Q154" s="14"/>
       <x:c r="R154" s="14"/>
       <x:c r="S154" s="14"/>
@@ -4370,7 +4582,7 @@
       <x:c r="M155" s="14"/>
       <x:c r="N155" s="14"/>
       <x:c r="O155" s="14"/>
-      <x:c r="P155" s="14"/>
+      <x:c r="P155" s="31"/>
       <x:c r="Q155" s="14"/>
       <x:c r="R155" s="14"/>
       <x:c r="S155" s="14"/>
@@ -4391,7 +4603,7 @@
       <x:c r="M156" s="14"/>
       <x:c r="N156" s="14"/>
       <x:c r="O156" s="14"/>
-      <x:c r="P156" s="14"/>
+      <x:c r="P156" s="31"/>
       <x:c r="Q156" s="14"/>
       <x:c r="R156" s="14"/>
       <x:c r="S156" s="14"/>
@@ -4412,7 +4624,7 @@
       <x:c r="M157" s="14"/>
       <x:c r="N157" s="14"/>
       <x:c r="O157" s="14"/>
-      <x:c r="P157" s="14"/>
+      <x:c r="P157" s="31"/>
       <x:c r="Q157" s="14"/>
       <x:c r="R157" s="14"/>
       <x:c r="S157" s="14"/>
@@ -4433,7 +4645,7 @@
       <x:c r="M158" s="14"/>
       <x:c r="N158" s="14"/>
       <x:c r="O158" s="14"/>
-      <x:c r="P158" s="14"/>
+      <x:c r="P158" s="31"/>
       <x:c r="Q158" s="14"/>
       <x:c r="R158" s="14"/>
       <x:c r="S158" s="14"/>
@@ -4454,7 +4666,7 @@
       <x:c r="M159" s="14"/>
       <x:c r="N159" s="14"/>
       <x:c r="O159" s="14"/>
-      <x:c r="P159" s="14"/>
+      <x:c r="P159" s="31"/>
       <x:c r="Q159" s="14"/>
       <x:c r="R159" s="14"/>
       <x:c r="S159" s="14"/>
@@ -4475,7 +4687,7 @@
       <x:c r="M160" s="14"/>
       <x:c r="N160" s="14"/>
       <x:c r="O160" s="14"/>
-      <x:c r="P160" s="14"/>
+      <x:c r="P160" s="31"/>
       <x:c r="Q160" s="14"/>
       <x:c r="R160" s="14"/>
       <x:c r="S160" s="14"/>
@@ -4496,7 +4708,7 @@
       <x:c r="M161" s="14"/>
       <x:c r="N161" s="14"/>
       <x:c r="O161" s="14"/>
-      <x:c r="P161" s="14"/>
+      <x:c r="P161" s="31"/>
       <x:c r="Q161" s="14"/>
       <x:c r="R161" s="14"/>
       <x:c r="S161" s="14"/>
@@ -4517,7 +4729,7 @@
       <x:c r="M162" s="14"/>
       <x:c r="N162" s="14"/>
       <x:c r="O162" s="14"/>
-      <x:c r="P162" s="14"/>
+      <x:c r="P162" s="31"/>
       <x:c r="Q162" s="14"/>
       <x:c r="R162" s="14"/>
       <x:c r="S162" s="14"/>
@@ -4538,7 +4750,7 @@
       <x:c r="M163" s="14"/>
       <x:c r="N163" s="14"/>
       <x:c r="O163" s="14"/>
-      <x:c r="P163" s="14"/>
+      <x:c r="P163" s="31"/>
       <x:c r="Q163" s="14"/>
       <x:c r="R163" s="14"/>
       <x:c r="S163" s="14"/>
@@ -4559,7 +4771,7 @@
       <x:c r="M164" s="14"/>
       <x:c r="N164" s="14"/>
       <x:c r="O164" s="14"/>
-      <x:c r="P164" s="14"/>
+      <x:c r="P164" s="31"/>
       <x:c r="Q164" s="14"/>
       <x:c r="R164" s="14"/>
       <x:c r="S164" s="14"/>
@@ -4580,7 +4792,7 @@
       <x:c r="M165" s="14"/>
       <x:c r="N165" s="14"/>
       <x:c r="O165" s="14"/>
-      <x:c r="P165" s="14"/>
+      <x:c r="P165" s="31"/>
       <x:c r="Q165" s="14"/>
       <x:c r="R165" s="14"/>
       <x:c r="S165" s="14"/>
@@ -4601,7 +4813,7 @@
       <x:c r="M166" s="14"/>
       <x:c r="N166" s="14"/>
       <x:c r="O166" s="14"/>
-      <x:c r="P166" s="14"/>
+      <x:c r="P166" s="31"/>
       <x:c r="Q166" s="14"/>
       <x:c r="R166" s="14"/>
       <x:c r="S166" s="14"/>
@@ -4622,7 +4834,7 @@
       <x:c r="M167" s="14"/>
       <x:c r="N167" s="14"/>
       <x:c r="O167" s="14"/>
-      <x:c r="P167" s="14"/>
+      <x:c r="P167" s="31"/>
       <x:c r="Q167" s="14"/>
       <x:c r="R167" s="14"/>
       <x:c r="S167" s="14"/>
@@ -4643,7 +4855,7 @@
       <x:c r="M168" s="14"/>
       <x:c r="N168" s="14"/>
       <x:c r="O168" s="14"/>
-      <x:c r="P168" s="14"/>
+      <x:c r="P168" s="31"/>
       <x:c r="Q168" s="14"/>
       <x:c r="R168" s="14"/>
       <x:c r="S168" s="14"/>
@@ -4664,7 +4876,7 @@
       <x:c r="M169" s="14"/>
       <x:c r="N169" s="14"/>
       <x:c r="O169" s="14"/>
-      <x:c r="P169" s="14"/>
+      <x:c r="P169" s="31"/>
       <x:c r="Q169" s="14"/>
       <x:c r="R169" s="14"/>
       <x:c r="S169" s="14"/>
@@ -4685,7 +4897,7 @@
       <x:c r="M170" s="14"/>
       <x:c r="N170" s="14"/>
       <x:c r="O170" s="14"/>
-      <x:c r="P170" s="14"/>
+      <x:c r="P170" s="31"/>
       <x:c r="Q170" s="14"/>
       <x:c r="R170" s="14"/>
       <x:c r="S170" s="14"/>
@@ -4706,7 +4918,7 @@
       <x:c r="M171" s="14"/>
       <x:c r="N171" s="14"/>
       <x:c r="O171" s="14"/>
-      <x:c r="P171" s="14"/>
+      <x:c r="P171" s="31"/>
       <x:c r="Q171" s="14"/>
       <x:c r="R171" s="14"/>
       <x:c r="S171" s="14"/>
@@ -4727,7 +4939,7 @@
       <x:c r="M172" s="14"/>
       <x:c r="N172" s="14"/>
       <x:c r="O172" s="14"/>
-      <x:c r="P172" s="14"/>
+      <x:c r="P172" s="31"/>
       <x:c r="Q172" s="14"/>
       <x:c r="R172" s="14"/>
       <x:c r="S172" s="14"/>
@@ -4748,7 +4960,7 @@
       <x:c r="M173" s="14"/>
       <x:c r="N173" s="14"/>
       <x:c r="O173" s="14"/>
-      <x:c r="P173" s="14"/>
+      <x:c r="P173" s="31"/>
       <x:c r="Q173" s="14"/>
       <x:c r="R173" s="14"/>
       <x:c r="S173" s="14"/>
@@ -4769,7 +4981,7 @@
       <x:c r="M174" s="14"/>
       <x:c r="N174" s="14"/>
       <x:c r="O174" s="14"/>
-      <x:c r="P174" s="14"/>
+      <x:c r="P174" s="31"/>
       <x:c r="Q174" s="14"/>
       <x:c r="R174" s="14"/>
       <x:c r="S174" s="14"/>
@@ -4790,7 +5002,7 @@
       <x:c r="M175" s="14"/>
       <x:c r="N175" s="14"/>
       <x:c r="O175" s="14"/>
-      <x:c r="P175" s="14"/>
+      <x:c r="P175" s="31"/>
       <x:c r="Q175" s="14"/>
       <x:c r="R175" s="14"/>
       <x:c r="S175" s="14"/>
@@ -4811,7 +5023,7 @@
       <x:c r="M176" s="14"/>
       <x:c r="N176" s="14"/>
       <x:c r="O176" s="14"/>
-      <x:c r="P176" s="14"/>
+      <x:c r="P176" s="31"/>
       <x:c r="Q176" s="14"/>
       <x:c r="R176" s="14"/>
       <x:c r="S176" s="14"/>
@@ -4832,7 +5044,7 @@
       <x:c r="M177" s="14"/>
       <x:c r="N177" s="14"/>
       <x:c r="O177" s="14"/>
-      <x:c r="P177" s="14"/>
+      <x:c r="P177" s="31"/>
       <x:c r="Q177" s="14"/>
       <x:c r="R177" s="14"/>
       <x:c r="S177" s="14"/>
@@ -4853,7 +5065,7 @@
       <x:c r="M178" s="14"/>
       <x:c r="N178" s="14"/>
       <x:c r="O178" s="14"/>
-      <x:c r="P178" s="14"/>
+      <x:c r="P178" s="31"/>
       <x:c r="Q178" s="14"/>
       <x:c r="R178" s="14"/>
       <x:c r="S178" s="14"/>
@@ -4874,7 +5086,7 @@
       <x:c r="M179" s="14"/>
       <x:c r="N179" s="14"/>
       <x:c r="O179" s="14"/>
-      <x:c r="P179" s="14"/>
+      <x:c r="P179" s="31"/>
       <x:c r="Q179" s="14"/>
       <x:c r="R179" s="14"/>
       <x:c r="S179" s="14"/>
@@ -4895,7 +5107,7 @@
       <x:c r="M180" s="14"/>
       <x:c r="N180" s="14"/>
       <x:c r="O180" s="14"/>
-      <x:c r="P180" s="14"/>
+      <x:c r="P180" s="31"/>
       <x:c r="Q180" s="14"/>
       <x:c r="R180" s="14"/>
       <x:c r="S180" s="14"/>
@@ -4916,7 +5128,7 @@
       <x:c r="M181" s="14"/>
       <x:c r="N181" s="14"/>
       <x:c r="O181" s="14"/>
-      <x:c r="P181" s="14"/>
+      <x:c r="P181" s="31"/>
       <x:c r="Q181" s="14"/>
       <x:c r="R181" s="14"/>
       <x:c r="S181" s="14"/>
@@ -4937,7 +5149,7 @@
       <x:c r="M182" s="14"/>
       <x:c r="N182" s="14"/>
       <x:c r="O182" s="14"/>
-      <x:c r="P182" s="14"/>
+      <x:c r="P182" s="31"/>
       <x:c r="Q182" s="14"/>
       <x:c r="R182" s="14"/>
       <x:c r="S182" s="14"/>
@@ -4958,7 +5170,7 @@
       <x:c r="M183" s="14"/>
       <x:c r="N183" s="14"/>
       <x:c r="O183" s="14"/>
-      <x:c r="P183" s="14"/>
+      <x:c r="P183" s="31"/>
       <x:c r="Q183" s="14"/>
       <x:c r="R183" s="14"/>
       <x:c r="S183" s="14"/>
@@ -4979,7 +5191,7 @@
       <x:c r="M184" s="14"/>
       <x:c r="N184" s="14"/>
       <x:c r="O184" s="14"/>
-      <x:c r="P184" s="14"/>
+      <x:c r="P184" s="31"/>
       <x:c r="Q184" s="14"/>
       <x:c r="R184" s="14"/>
       <x:c r="S184" s="14"/>
@@ -5000,7 +5212,7 @@
       <x:c r="M185" s="14"/>
       <x:c r="N185" s="14"/>
       <x:c r="O185" s="14"/>
-      <x:c r="P185" s="14"/>
+      <x:c r="P185" s="31"/>
       <x:c r="Q185" s="14"/>
       <x:c r="R185" s="14"/>
       <x:c r="S185" s="14"/>
@@ -5021,7 +5233,7 @@
       <x:c r="M186" s="14"/>
       <x:c r="N186" s="14"/>
       <x:c r="O186" s="14"/>
-      <x:c r="P186" s="14"/>
+      <x:c r="P186" s="31"/>
       <x:c r="Q186" s="14"/>
       <x:c r="R186" s="14"/>
       <x:c r="S186" s="14"/>
@@ -5042,7 +5254,7 @@
       <x:c r="M187" s="14"/>
       <x:c r="N187" s="14"/>
       <x:c r="O187" s="14"/>
-      <x:c r="P187" s="14"/>
+      <x:c r="P187" s="31"/>
       <x:c r="Q187" s="14"/>
       <x:c r="R187" s="14"/>
       <x:c r="S187" s="14"/>
@@ -5063,7 +5275,7 @@
       <x:c r="M188" s="14"/>
       <x:c r="N188" s="14"/>
       <x:c r="O188" s="14"/>
-      <x:c r="P188" s="14"/>
+      <x:c r="P188" s="31"/>
       <x:c r="Q188" s="14"/>
       <x:c r="R188" s="14"/>
       <x:c r="S188" s="14"/>
@@ -5084,7 +5296,7 @@
       <x:c r="M189" s="14"/>
       <x:c r="N189" s="14"/>
       <x:c r="O189" s="14"/>
-      <x:c r="P189" s="14"/>
+      <x:c r="P189" s="31"/>
       <x:c r="Q189" s="14"/>
       <x:c r="R189" s="14"/>
       <x:c r="S189" s="14"/>
@@ -5105,7 +5317,7 @@
       <x:c r="M190" s="14"/>
       <x:c r="N190" s="14"/>
       <x:c r="O190" s="14"/>
-      <x:c r="P190" s="14"/>
+      <x:c r="P190" s="31"/>
       <x:c r="Q190" s="14"/>
       <x:c r="R190" s="14"/>
       <x:c r="S190" s="14"/>
@@ -5126,7 +5338,7 @@
       <x:c r="M191" s="14"/>
       <x:c r="N191" s="14"/>
       <x:c r="O191" s="14"/>
-      <x:c r="P191" s="14"/>
+      <x:c r="P191" s="31"/>
       <x:c r="Q191" s="14"/>
       <x:c r="R191" s="14"/>
       <x:c r="S191" s="14"/>
@@ -5147,7 +5359,7 @@
       <x:c r="M192" s="14"/>
       <x:c r="N192" s="14"/>
       <x:c r="O192" s="14"/>
-      <x:c r="P192" s="14"/>
+      <x:c r="P192" s="31"/>
       <x:c r="Q192" s="14"/>
       <x:c r="R192" s="14"/>
       <x:c r="S192" s="14"/>
@@ -5168,7 +5380,7 @@
       <x:c r="M193" s="14"/>
       <x:c r="N193" s="14"/>
       <x:c r="O193" s="14"/>
-      <x:c r="P193" s="14"/>
+      <x:c r="P193" s="31"/>
       <x:c r="Q193" s="14"/>
       <x:c r="R193" s="14"/>
       <x:c r="S193" s="14"/>
@@ -5189,7 +5401,7 @@
       <x:c r="M194" s="14"/>
       <x:c r="N194" s="14"/>
       <x:c r="O194" s="14"/>
-      <x:c r="P194" s="14"/>
+      <x:c r="P194" s="31"/>
       <x:c r="Q194" s="14"/>
       <x:c r="R194" s="14"/>
       <x:c r="S194" s="14"/>
@@ -5210,7 +5422,7 @@
       <x:c r="M195" s="14"/>
       <x:c r="N195" s="14"/>
       <x:c r="O195" s="14"/>
-      <x:c r="P195" s="14"/>
+      <x:c r="P195" s="31"/>
       <x:c r="Q195" s="14"/>
       <x:c r="R195" s="14"/>
       <x:c r="S195" s="14"/>
@@ -5231,7 +5443,7 @@
       <x:c r="M196" s="14"/>
       <x:c r="N196" s="14"/>
       <x:c r="O196" s="14"/>
-      <x:c r="P196" s="14"/>
+      <x:c r="P196" s="31"/>
       <x:c r="Q196" s="14"/>
       <x:c r="R196" s="14"/>
       <x:c r="S196" s="14"/>
@@ -5252,7 +5464,7 @@
       <x:c r="M197" s="14"/>
       <x:c r="N197" s="14"/>
       <x:c r="O197" s="14"/>
-      <x:c r="P197" s="14"/>
+      <x:c r="P197" s="31"/>
       <x:c r="Q197" s="14"/>
       <x:c r="R197" s="14"/>
       <x:c r="S197" s="14"/>
@@ -5273,7 +5485,7 @@
       <x:c r="M198" s="14"/>
       <x:c r="N198" s="14"/>
       <x:c r="O198" s="14"/>
-      <x:c r="P198" s="14"/>
+      <x:c r="P198" s="31"/>
       <x:c r="Q198" s="14"/>
       <x:c r="R198" s="14"/>
       <x:c r="S198" s="14"/>
@@ -5294,7 +5506,7 @@
       <x:c r="M199" s="14"/>
       <x:c r="N199" s="14"/>
       <x:c r="O199" s="14"/>
-      <x:c r="P199" s="14"/>
+      <x:c r="P199" s="31"/>
       <x:c r="Q199" s="14"/>
       <x:c r="R199" s="14"/>
       <x:c r="S199" s="14"/>
@@ -5315,7 +5527,7 @@
       <x:c r="M200" s="14"/>
       <x:c r="N200" s="14"/>
       <x:c r="O200" s="14"/>
-      <x:c r="P200" s="14"/>
+      <x:c r="P200" s="31"/>
       <x:c r="Q200" s="14"/>
       <x:c r="R200" s="14"/>
       <x:c r="S200" s="14"/>
@@ -5336,7 +5548,7 @@
       <x:c r="M201" s="14"/>
       <x:c r="N201" s="14"/>
       <x:c r="O201" s="14"/>
-      <x:c r="P201" s="14"/>
+      <x:c r="P201" s="31"/>
       <x:c r="Q201" s="14"/>
       <x:c r="R201" s="14"/>
       <x:c r="S201" s="14"/>
@@ -5357,7 +5569,7 @@
       <x:c r="M202" s="14"/>
       <x:c r="N202" s="14"/>
       <x:c r="O202" s="14"/>
-      <x:c r="P202" s="14"/>
+      <x:c r="P202" s="31"/>
       <x:c r="Q202" s="14"/>
       <x:c r="R202" s="14"/>
       <x:c r="S202" s="14"/>
@@ -5378,7 +5590,7 @@
       <x:c r="M203" s="14"/>
       <x:c r="N203" s="14"/>
       <x:c r="O203" s="14"/>
-      <x:c r="P203" s="14"/>
+      <x:c r="P203" s="31"/>
       <x:c r="Q203" s="14"/>
       <x:c r="R203" s="14"/>
       <x:c r="S203" s="14"/>
@@ -5399,7 +5611,7 @@
       <x:c r="M204" s="14"/>
       <x:c r="N204" s="14"/>
       <x:c r="O204" s="14"/>
-      <x:c r="P204" s="14"/>
+      <x:c r="P204" s="31"/>
       <x:c r="Q204" s="14"/>
       <x:c r="R204" s="14"/>
       <x:c r="S204" s="14"/>
@@ -5420,7 +5632,7 @@
       <x:c r="M205" s="14"/>
       <x:c r="N205" s="14"/>
       <x:c r="O205" s="14"/>
-      <x:c r="P205" s="14"/>
+      <x:c r="P205" s="31"/>
       <x:c r="Q205" s="14"/>
       <x:c r="R205" s="14"/>
       <x:c r="S205" s="14"/>
@@ -5441,7 +5653,7 @@
       <x:c r="M206" s="14"/>
       <x:c r="N206" s="14"/>
       <x:c r="O206" s="14"/>
-      <x:c r="P206" s="14"/>
+      <x:c r="P206" s="31"/>
       <x:c r="Q206" s="14"/>
       <x:c r="R206" s="14"/>
       <x:c r="S206" s="14"/>
@@ -5462,7 +5674,7 @@
       <x:c r="M207" s="14"/>
       <x:c r="N207" s="14"/>
       <x:c r="O207" s="14"/>
-      <x:c r="P207" s="14"/>
+      <x:c r="P207" s="31"/>
       <x:c r="Q207" s="14"/>
       <x:c r="R207" s="14"/>
       <x:c r="S207" s="14"/>
@@ -5483,7 +5695,7 @@
       <x:c r="M208" s="14"/>
       <x:c r="N208" s="14"/>
       <x:c r="O208" s="14"/>
-      <x:c r="P208" s="14"/>
+      <x:c r="P208" s="31"/>
       <x:c r="Q208" s="14"/>
       <x:c r="R208" s="14"/>
       <x:c r="S208" s="14"/>
@@ -5504,7 +5716,7 @@
       <x:c r="M209" s="14"/>
       <x:c r="N209" s="14"/>
       <x:c r="O209" s="14"/>
-      <x:c r="P209" s="14"/>
+      <x:c r="P209" s="31"/>
       <x:c r="Q209" s="14"/>
       <x:c r="R209" s="14"/>
       <x:c r="S209" s="14"/>
@@ -5525,7 +5737,7 @@
       <x:c r="M210" s="14"/>
       <x:c r="N210" s="14"/>
       <x:c r="O210" s="14"/>
-      <x:c r="P210" s="14"/>
+      <x:c r="P210" s="31"/>
       <x:c r="Q210" s="14"/>
       <x:c r="R210" s="14"/>
       <x:c r="S210" s="14"/>
@@ -5546,7 +5758,7 @@
       <x:c r="M211" s="14"/>
       <x:c r="N211" s="14"/>
       <x:c r="O211" s="14"/>
-      <x:c r="P211" s="14"/>
+      <x:c r="P211" s="31"/>
       <x:c r="Q211" s="14"/>
       <x:c r="R211" s="14"/>
       <x:c r="S211" s="14"/>
@@ -5567,7 +5779,7 @@
       <x:c r="M212" s="14"/>
       <x:c r="N212" s="14"/>
       <x:c r="O212" s="14"/>
-      <x:c r="P212" s="14"/>
+      <x:c r="P212" s="31"/>
       <x:c r="Q212" s="14"/>
       <x:c r="R212" s="14"/>
       <x:c r="S212" s="14"/>
@@ -5588,7 +5800,7 @@
       <x:c r="M213" s="14"/>
       <x:c r="N213" s="14"/>
       <x:c r="O213" s="14"/>
-      <x:c r="P213" s="14"/>
+      <x:c r="P213" s="31"/>
       <x:c r="Q213" s="14"/>
       <x:c r="R213" s="14"/>
       <x:c r="S213" s="14"/>
@@ -5609,7 +5821,7 @@
       <x:c r="M214" s="14"/>
       <x:c r="N214" s="14"/>
       <x:c r="O214" s="14"/>
-      <x:c r="P214" s="14"/>
+      <x:c r="P214" s="31"/>
       <x:c r="Q214" s="14"/>
       <x:c r="R214" s="14"/>
       <x:c r="S214" s="14"/>
@@ -5630,7 +5842,7 @@
       <x:c r="M215" s="14"/>
       <x:c r="N215" s="14"/>
       <x:c r="O215" s="14"/>
-      <x:c r="P215" s="14"/>
+      <x:c r="P215" s="31"/>
       <x:c r="Q215" s="14"/>
       <x:c r="R215" s="14"/>
       <x:c r="S215" s="14"/>
@@ -5651,7 +5863,7 @@
       <x:c r="M216" s="14"/>
       <x:c r="N216" s="14"/>
       <x:c r="O216" s="14"/>
-      <x:c r="P216" s="14"/>
+      <x:c r="P216" s="31"/>
       <x:c r="Q216" s="14"/>
       <x:c r="R216" s="14"/>
       <x:c r="S216" s="14"/>
@@ -5672,7 +5884,7 @@
       <x:c r="M217" s="14"/>
       <x:c r="N217" s="14"/>
       <x:c r="O217" s="14"/>
-      <x:c r="P217" s="14"/>
+      <x:c r="P217" s="31"/>
       <x:c r="Q217" s="14"/>
       <x:c r="R217" s="14"/>
       <x:c r="S217" s="14"/>
@@ -5693,7 +5905,7 @@
       <x:c r="M218" s="14"/>
       <x:c r="N218" s="14"/>
       <x:c r="O218" s="14"/>
-      <x:c r="P218" s="14"/>
+      <x:c r="P218" s="31"/>
       <x:c r="Q218" s="14"/>
       <x:c r="R218" s="14"/>
       <x:c r="S218" s="14"/>
@@ -5714,7 +5926,7 @@
       <x:c r="M219" s="14"/>
       <x:c r="N219" s="14"/>
       <x:c r="O219" s="14"/>
-      <x:c r="P219" s="14"/>
+      <x:c r="P219" s="31"/>
       <x:c r="Q219" s="14"/>
       <x:c r="R219" s="14"/>
       <x:c r="S219" s="14"/>
@@ -5735,7 +5947,7 @@
       <x:c r="M220" s="14"/>
       <x:c r="N220" s="14"/>
       <x:c r="O220" s="14"/>
-      <x:c r="P220" s="14"/>
+      <x:c r="P220" s="31"/>
       <x:c r="Q220" s="14"/>
       <x:c r="R220" s="14"/>
       <x:c r="S220" s="14"/>
@@ -5756,7 +5968,7 @@
       <x:c r="M221" s="14"/>
       <x:c r="N221" s="14"/>
       <x:c r="O221" s="14"/>
-      <x:c r="P221" s="14"/>
+      <x:c r="P221" s="31"/>
       <x:c r="Q221" s="14"/>
       <x:c r="R221" s="14"/>
       <x:c r="S221" s="14"/>
@@ -5777,7 +5989,7 @@
       <x:c r="M222" s="14"/>
       <x:c r="N222" s="14"/>
       <x:c r="O222" s="14"/>
-      <x:c r="P222" s="14"/>
+      <x:c r="P222" s="31"/>
       <x:c r="Q222" s="14"/>
       <x:c r="R222" s="14"/>
       <x:c r="S222" s="14"/>
@@ -5798,7 +6010,7 @@
       <x:c r="M223" s="14"/>
       <x:c r="N223" s="14"/>
       <x:c r="O223" s="14"/>
-      <x:c r="P223" s="14"/>
+      <x:c r="P223" s="31"/>
       <x:c r="Q223" s="14"/>
       <x:c r="R223" s="14"/>
       <x:c r="S223" s="14"/>
@@ -5819,7 +6031,7 @@
       <x:c r="M224" s="14"/>
       <x:c r="N224" s="14"/>
       <x:c r="O224" s="14"/>
-      <x:c r="P224" s="14"/>
+      <x:c r="P224" s="31"/>
       <x:c r="Q224" s="14"/>
       <x:c r="R224" s="14"/>
       <x:c r="S224" s="14"/>
@@ -5840,7 +6052,7 @@
       <x:c r="M225" s="14"/>
       <x:c r="N225" s="14"/>
       <x:c r="O225" s="14"/>
-      <x:c r="P225" s="14"/>
+      <x:c r="P225" s="31"/>
       <x:c r="Q225" s="14"/>
       <x:c r="R225" s="14"/>
       <x:c r="S225" s="14"/>
@@ -5861,7 +6073,7 @@
       <x:c r="M226" s="14"/>
       <x:c r="N226" s="14"/>
       <x:c r="O226" s="14"/>
-      <x:c r="P226" s="14"/>
+      <x:c r="P226" s="31"/>
       <x:c r="Q226" s="14"/>
       <x:c r="R226" s="14"/>
       <x:c r="S226" s="14"/>
@@ -5882,7 +6094,7 @@
       <x:c r="M227" s="14"/>
       <x:c r="N227" s="14"/>
       <x:c r="O227" s="14"/>
-      <x:c r="P227" s="14"/>
+      <x:c r="P227" s="31"/>
       <x:c r="Q227" s="14"/>
       <x:c r="R227" s="14"/>
       <x:c r="S227" s="14"/>
@@ -5903,7 +6115,7 @@
       <x:c r="M228" s="14"/>
       <x:c r="N228" s="14"/>
       <x:c r="O228" s="14"/>
-      <x:c r="P228" s="14"/>
+      <x:c r="P228" s="31"/>
       <x:c r="Q228" s="14"/>
       <x:c r="R228" s="14"/>
       <x:c r="S228" s="14"/>
@@ -5924,7 +6136,7 @@
       <x:c r="M229" s="14"/>
       <x:c r="N229" s="14"/>
       <x:c r="O229" s="14"/>
-      <x:c r="P229" s="14"/>
+      <x:c r="P229" s="31"/>
       <x:c r="Q229" s="14"/>
       <x:c r="R229" s="14"/>
       <x:c r="S229" s="14"/>
@@ -5945,7 +6157,7 @@
       <x:c r="M230" s="14"/>
       <x:c r="N230" s="14"/>
       <x:c r="O230" s="14"/>
-      <x:c r="P230" s="14"/>
+      <x:c r="P230" s="31"/>
       <x:c r="Q230" s="14"/>
       <x:c r="R230" s="14"/>
       <x:c r="S230" s="14"/>
@@ -5966,7 +6178,7 @@
       <x:c r="M231" s="14"/>
       <x:c r="N231" s="14"/>
       <x:c r="O231" s="14"/>
-      <x:c r="P231" s="14"/>
+      <x:c r="P231" s="31"/>
       <x:c r="Q231" s="14"/>
       <x:c r="R231" s="14"/>
       <x:c r="S231" s="14"/>
@@ -5987,7 +6199,7 @@
       <x:c r="M232" s="14"/>
       <x:c r="N232" s="14"/>
       <x:c r="O232" s="14"/>
-      <x:c r="P232" s="14"/>
+      <x:c r="P232" s="31"/>
       <x:c r="Q232" s="14"/>
       <x:c r="R232" s="14"/>
       <x:c r="S232" s="14"/>
@@ -6008,7 +6220,7 @@
       <x:c r="M233" s="14"/>
       <x:c r="N233" s="14"/>
       <x:c r="O233" s="14"/>
-      <x:c r="P233" s="14"/>
+      <x:c r="P233" s="31"/>
       <x:c r="Q233" s="14"/>
       <x:c r="R233" s="14"/>
       <x:c r="S233" s="14"/>
@@ -6029,7 +6241,7 @@
       <x:c r="M234" s="14"/>
       <x:c r="N234" s="14"/>
       <x:c r="O234" s="14"/>
-      <x:c r="P234" s="14"/>
+      <x:c r="P234" s="31"/>
       <x:c r="Q234" s="14"/>
       <x:c r="R234" s="14"/>
       <x:c r="S234" s="14"/>
@@ -6050,7 +6262,7 @@
       <x:c r="M235" s="14"/>
       <x:c r="N235" s="14"/>
       <x:c r="O235" s="14"/>
-      <x:c r="P235" s="14"/>
+      <x:c r="P235" s="31"/>
       <x:c r="Q235" s="14"/>
       <x:c r="R235" s="14"/>
       <x:c r="S235" s="14"/>
@@ -6071,7 +6283,7 @@
       <x:c r="M236" s="14"/>
       <x:c r="N236" s="14"/>
       <x:c r="O236" s="14"/>
-      <x:c r="P236" s="14"/>
+      <x:c r="P236" s="31"/>
       <x:c r="Q236" s="14"/>
       <x:c r="R236" s="14"/>
       <x:c r="S236" s="14"/>
@@ -6092,7 +6304,7 @@
       <x:c r="M237" s="14"/>
       <x:c r="N237" s="14"/>
       <x:c r="O237" s="14"/>
-      <x:c r="P237" s="14"/>
+      <x:c r="P237" s="31"/>
       <x:c r="Q237" s="14"/>
       <x:c r="R237" s="14"/>
       <x:c r="S237" s="14"/>
@@ -6113,7 +6325,7 @@
       <x:c r="M238" s="14"/>
       <x:c r="N238" s="14"/>
       <x:c r="O238" s="14"/>
-      <x:c r="P238" s="14"/>
+      <x:c r="P238" s="31"/>
       <x:c r="Q238" s="14"/>
       <x:c r="R238" s="14"/>
       <x:c r="S238" s="14"/>
@@ -6134,7 +6346,7 @@
       <x:c r="M239" s="14"/>
       <x:c r="N239" s="14"/>
       <x:c r="O239" s="14"/>
-      <x:c r="P239" s="14"/>
+      <x:c r="P239" s="31"/>
       <x:c r="Q239" s="14"/>
       <x:c r="R239" s="14"/>
       <x:c r="S239" s="14"/>
@@ -6155,7 +6367,7 @@
       <x:c r="M240" s="14"/>
       <x:c r="N240" s="14"/>
       <x:c r="O240" s="14"/>
-      <x:c r="P240" s="14"/>
+      <x:c r="P240" s="31"/>
       <x:c r="Q240" s="14"/>
       <x:c r="R240" s="14"/>
       <x:c r="S240" s="14"/>
@@ -6176,7 +6388,7 @@
       <x:c r="M241" s="14"/>
       <x:c r="N241" s="14"/>
       <x:c r="O241" s="14"/>
-      <x:c r="P241" s="14"/>
+      <x:c r="P241" s="31"/>
       <x:c r="Q241" s="14"/>
       <x:c r="R241" s="14"/>
       <x:c r="S241" s="14"/>
@@ -6197,7 +6409,7 @@
       <x:c r="M242" s="14"/>
       <x:c r="N242" s="14"/>
       <x:c r="O242" s="14"/>
-      <x:c r="P242" s="14"/>
+      <x:c r="P242" s="31"/>
       <x:c r="Q242" s="14"/>
       <x:c r="R242" s="14"/>
       <x:c r="S242" s="14"/>
@@ -6218,7 +6430,7 @@
       <x:c r="M243" s="14"/>
       <x:c r="N243" s="14"/>
       <x:c r="O243" s="14"/>
-      <x:c r="P243" s="14"/>
+      <x:c r="P243" s="31"/>
       <x:c r="Q243" s="14"/>
       <x:c r="R243" s="14"/>
       <x:c r="S243" s="14"/>
@@ -6239,7 +6451,7 @@
       <x:c r="M244" s="14"/>
       <x:c r="N244" s="14"/>
       <x:c r="O244" s="14"/>
-      <x:c r="P244" s="14"/>
+      <x:c r="P244" s="31"/>
       <x:c r="Q244" s="14"/>
       <x:c r="R244" s="14"/>
       <x:c r="S244" s="14"/>
@@ -6260,7 +6472,7 @@
       <x:c r="M245" s="14"/>
       <x:c r="N245" s="14"/>
       <x:c r="O245" s="14"/>
-      <x:c r="P245" s="14"/>
+      <x:c r="P245" s="31"/>
       <x:c r="Q245" s="14"/>
       <x:c r="R245" s="14"/>
       <x:c r="S245" s="14"/>
@@ -6281,7 +6493,7 @@
       <x:c r="M246" s="14"/>
       <x:c r="N246" s="14"/>
       <x:c r="O246" s="14"/>
-      <x:c r="P246" s="14"/>
+      <x:c r="P246" s="31"/>
       <x:c r="Q246" s="14"/>
       <x:c r="R246" s="14"/>
       <x:c r="S246" s="14"/>
@@ -6302,7 +6514,7 @@
       <x:c r="M247" s="14"/>
       <x:c r="N247" s="14"/>
       <x:c r="O247" s="14"/>
-      <x:c r="P247" s="14"/>
+      <x:c r="P247" s="31"/>
       <x:c r="Q247" s="14"/>
       <x:c r="R247" s="14"/>
       <x:c r="S247" s="14"/>
@@ -6323,7 +6535,7 @@
       <x:c r="M248" s="14"/>
       <x:c r="N248" s="14"/>
       <x:c r="O248" s="14"/>
-      <x:c r="P248" s="14"/>
+      <x:c r="P248" s="31"/>
       <x:c r="Q248" s="14"/>
       <x:c r="R248" s="14"/>
       <x:c r="S248" s="14"/>
@@ -6344,7 +6556,7 @@
       <x:c r="M249" s="14"/>
       <x:c r="N249" s="14"/>
       <x:c r="O249" s="14"/>
-      <x:c r="P249" s="14"/>
+      <x:c r="P249" s="31"/>
       <x:c r="Q249" s="14"/>
       <x:c r="R249" s="14"/>
       <x:c r="S249" s="14"/>
@@ -6365,7 +6577,7 @@
       <x:c r="M250" s="14"/>
       <x:c r="N250" s="14"/>
       <x:c r="O250" s="14"/>
-      <x:c r="P250" s="14"/>
+      <x:c r="P250" s="31"/>
       <x:c r="Q250" s="14"/>
       <x:c r="R250" s="14"/>
       <x:c r="S250" s="14"/>
@@ -6386,7 +6598,7 @@
       <x:c r="M251" s="14"/>
       <x:c r="N251" s="14"/>
       <x:c r="O251" s="14"/>
-      <x:c r="P251" s="14"/>
+      <x:c r="P251" s="31"/>
       <x:c r="Q251" s="14"/>
       <x:c r="R251" s="14"/>
       <x:c r="S251" s="14"/>
@@ -6407,7 +6619,7 @@
       <x:c r="M252" s="14"/>
       <x:c r="N252" s="14"/>
       <x:c r="O252" s="14"/>
-      <x:c r="P252" s="14"/>
+      <x:c r="P252" s="31"/>
       <x:c r="Q252" s="14"/>
       <x:c r="R252" s="14"/>
       <x:c r="S252" s="14"/>
@@ -6428,7 +6640,7 @@
       <x:c r="M253" s="14"/>
       <x:c r="N253" s="14"/>
       <x:c r="O253" s="14"/>
-      <x:c r="P253" s="14"/>
+      <x:c r="P253" s="31"/>
       <x:c r="Q253" s="14"/>
       <x:c r="R253" s="14"/>
       <x:c r="S253" s="14"/>
@@ -6449,7 +6661,7 @@
       <x:c r="M254" s="14"/>
       <x:c r="N254" s="14"/>
       <x:c r="O254" s="14"/>
-      <x:c r="P254" s="14"/>
+      <x:c r="P254" s="31"/>
       <x:c r="Q254" s="14"/>
       <x:c r="R254" s="14"/>
       <x:c r="S254" s="14"/>
@@ -6470,7 +6682,7 @@
       <x:c r="M255" s="14"/>
       <x:c r="N255" s="14"/>
       <x:c r="O255" s="14"/>
-      <x:c r="P255" s="14"/>
+      <x:c r="P255" s="31"/>
       <x:c r="Q255" s="14"/>
       <x:c r="R255" s="14"/>
       <x:c r="S255" s="14"/>
@@ -6491,7 +6703,7 @@
       <x:c r="M256" s="14"/>
       <x:c r="N256" s="14"/>
       <x:c r="O256" s="14"/>
-      <x:c r="P256" s="14"/>
+      <x:c r="P256" s="31"/>
       <x:c r="Q256" s="14"/>
       <x:c r="R256" s="14"/>
       <x:c r="S256" s="14"/>
@@ -6512,7 +6724,7 @@
       <x:c r="M257" s="14"/>
       <x:c r="N257" s="14"/>
       <x:c r="O257" s="14"/>
-      <x:c r="P257" s="14"/>
+      <x:c r="P257" s="31"/>
       <x:c r="Q257" s="14"/>
       <x:c r="R257" s="14"/>
       <x:c r="S257" s="14"/>
@@ -6533,7 +6745,7 @@
       <x:c r="M258" s="14"/>
       <x:c r="N258" s="14"/>
       <x:c r="O258" s="14"/>
-      <x:c r="P258" s="14"/>
+      <x:c r="P258" s="31"/>
       <x:c r="Q258" s="14"/>
       <x:c r="R258" s="14"/>
       <x:c r="S258" s="14"/>
@@ -6554,7 +6766,7 @@
       <x:c r="M259" s="14"/>
       <x:c r="N259" s="14"/>
       <x:c r="O259" s="14"/>
-      <x:c r="P259" s="14"/>
+      <x:c r="P259" s="31"/>
       <x:c r="Q259" s="14"/>
       <x:c r="R259" s="14"/>
       <x:c r="S259" s="14"/>
@@ -6575,7 +6787,7 @@
       <x:c r="M260" s="14"/>
       <x:c r="N260" s="14"/>
       <x:c r="O260" s="14"/>
-      <x:c r="P260" s="14"/>
+      <x:c r="P260" s="31"/>
       <x:c r="Q260" s="14"/>
       <x:c r="R260" s="14"/>
       <x:c r="S260" s="14"/>
@@ -6596,7 +6808,7 @@
       <x:c r="M261" s="14"/>
       <x:c r="N261" s="14"/>
       <x:c r="O261" s="14"/>
-      <x:c r="P261" s="14"/>
+      <x:c r="P261" s="31"/>
       <x:c r="Q261" s="14"/>
       <x:c r="R261" s="14"/>
       <x:c r="S261" s="14"/>
@@ -6617,7 +6829,7 @@
       <x:c r="M262" s="14"/>
       <x:c r="N262" s="14"/>
       <x:c r="O262" s="14"/>
-      <x:c r="P262" s="14"/>
+      <x:c r="P262" s="31"/>
       <x:c r="Q262" s="14"/>
       <x:c r="R262" s="14"/>
       <x:c r="S262" s="14"/>
@@ -6638,7 +6850,7 @@
       <x:c r="M263" s="14"/>
       <x:c r="N263" s="14"/>
       <x:c r="O263" s="14"/>
-      <x:c r="P263" s="14"/>
+      <x:c r="P263" s="31"/>
       <x:c r="Q263" s="14"/>
       <x:c r="R263" s="14"/>
       <x:c r="S263" s="14"/>
@@ -6659,7 +6871,7 @@
       <x:c r="M264" s="14"/>
       <x:c r="N264" s="14"/>
       <x:c r="O264" s="14"/>
-      <x:c r="P264" s="14"/>
+      <x:c r="P264" s="31"/>
       <x:c r="Q264" s="14"/>
       <x:c r="R264" s="14"/>
       <x:c r="S264" s="14"/>
@@ -6680,7 +6892,7 @@
       <x:c r="M265" s="14"/>
       <x:c r="N265" s="14"/>
       <x:c r="O265" s="14"/>
-      <x:c r="P265" s="14"/>
+      <x:c r="P265" s="31"/>
       <x:c r="Q265" s="14"/>
       <x:c r="R265" s="14"/>
       <x:c r="S265" s="14"/>
@@ -6701,7 +6913,7 @@
       <x:c r="M266" s="14"/>
       <x:c r="N266" s="14"/>
       <x:c r="O266" s="14"/>
-      <x:c r="P266" s="14"/>
+      <x:c r="P266" s="31"/>
       <x:c r="Q266" s="14"/>
       <x:c r="R266" s="14"/>
       <x:c r="S266" s="14"/>
@@ -6722,7 +6934,7 @@
       <x:c r="M267" s="14"/>
       <x:c r="N267" s="14"/>
       <x:c r="O267" s="14"/>
-      <x:c r="P267" s="14"/>
+      <x:c r="P267" s="31"/>
       <x:c r="Q267" s="14"/>
       <x:c r="R267" s="14"/>
       <x:c r="S267" s="14"/>
@@ -6743,7 +6955,7 @@
       <x:c r="M268" s="14"/>
       <x:c r="N268" s="14"/>
       <x:c r="O268" s="14"/>
-      <x:c r="P268" s="14"/>
+      <x:c r="P268" s="31"/>
       <x:c r="Q268" s="14"/>
       <x:c r="R268" s="14"/>
       <x:c r="S268" s="14"/>
@@ -6764,7 +6976,7 @@
       <x:c r="M269" s="14"/>
       <x:c r="N269" s="14"/>
       <x:c r="O269" s="14"/>
-      <x:c r="P269" s="14"/>
+      <x:c r="P269" s="31"/>
       <x:c r="Q269" s="14"/>
       <x:c r="R269" s="14"/>
       <x:c r="S269" s="14"/>
@@ -6785,7 +6997,7 @@
       <x:c r="M270" s="14"/>
       <x:c r="N270" s="14"/>
       <x:c r="O270" s="14"/>
-      <x:c r="P270" s="14"/>
+      <x:c r="P270" s="31"/>
       <x:c r="Q270" s="14"/>
       <x:c r="R270" s="14"/>
       <x:c r="S270" s="14"/>
@@ -6806,7 +7018,7 @@
       <x:c r="M271" s="14"/>
       <x:c r="N271" s="14"/>
       <x:c r="O271" s="14"/>
-      <x:c r="P271" s="14"/>
+      <x:c r="P271" s="31"/>
       <x:c r="Q271" s="14"/>
       <x:c r="R271" s="14"/>
       <x:c r="S271" s="14"/>
@@ -6827,7 +7039,7 @@
       <x:c r="M272" s="14"/>
       <x:c r="N272" s="14"/>
       <x:c r="O272" s="14"/>
-      <x:c r="P272" s="14"/>
+      <x:c r="P272" s="31"/>
       <x:c r="Q272" s="14"/>
       <x:c r="R272" s="14"/>
       <x:c r="S272" s="14"/>
@@ -6848,7 +7060,7 @@
       <x:c r="M273" s="14"/>
       <x:c r="N273" s="14"/>
       <x:c r="O273" s="14"/>
-      <x:c r="P273" s="14"/>
+      <x:c r="P273" s="31"/>
       <x:c r="Q273" s="14"/>
       <x:c r="R273" s="14"/>
       <x:c r="S273" s="14"/>
@@ -6869,7 +7081,7 @@
       <x:c r="M274" s="14"/>
       <x:c r="N274" s="14"/>
       <x:c r="O274" s="14"/>
-      <x:c r="P274" s="14"/>
+      <x:c r="P274" s="31"/>
       <x:c r="Q274" s="14"/>
       <x:c r="R274" s="14"/>
       <x:c r="S274" s="14"/>
@@ -6890,7 +7102,7 @@
       <x:c r="M275" s="14"/>
       <x:c r="N275" s="14"/>
       <x:c r="O275" s="14"/>
-      <x:c r="P275" s="14"/>
+      <x:c r="P275" s="31"/>
       <x:c r="Q275" s="14"/>
       <x:c r="R275" s="14"/>
       <x:c r="S275" s="14"/>
@@ -6911,7 +7123,7 @@
       <x:c r="M276" s="14"/>
       <x:c r="N276" s="14"/>
       <x:c r="O276" s="14"/>
-      <x:c r="P276" s="14"/>
+      <x:c r="P276" s="31"/>
       <x:c r="Q276" s="14"/>
       <x:c r="R276" s="14"/>
       <x:c r="S276" s="14"/>
@@ -6932,7 +7144,7 @@
       <x:c r="M277" s="14"/>
       <x:c r="N277" s="14"/>
       <x:c r="O277" s="14"/>
-      <x:c r="P277" s="14"/>
+      <x:c r="P277" s="31"/>
       <x:c r="Q277" s="14"/>
       <x:c r="R277" s="14"/>
       <x:c r="S277" s="14"/>
@@ -6953,7 +7165,7 @@
       <x:c r="M278" s="14"/>
       <x:c r="N278" s="14"/>
       <x:c r="O278" s="14"/>
-      <x:c r="P278" s="14"/>
+      <x:c r="P278" s="31"/>
       <x:c r="Q278" s="14"/>
       <x:c r="R278" s="14"/>
       <x:c r="S278" s="14"/>
@@ -6974,7 +7186,7 @@
       <x:c r="M279" s="14"/>
       <x:c r="N279" s="14"/>
       <x:c r="O279" s="14"/>
-      <x:c r="P279" s="14"/>
+      <x:c r="P279" s="31"/>
       <x:c r="Q279" s="14"/>
       <x:c r="R279" s="14"/>
       <x:c r="S279" s="14"/>
@@ -6995,7 +7207,7 @@
       <x:c r="M280" s="14"/>
       <x:c r="N280" s="14"/>
       <x:c r="O280" s="14"/>
-      <x:c r="P280" s="14"/>
+      <x:c r="P280" s="31"/>
       <x:c r="Q280" s="14"/>
       <x:c r="R280" s="14"/>
       <x:c r="S280" s="14"/>
@@ -7016,7 +7228,7 @@
       <x:c r="M281" s="14"/>
       <x:c r="N281" s="14"/>
       <x:c r="O281" s="14"/>
-      <x:c r="P281" s="14"/>
+      <x:c r="P281" s="31"/>
       <x:c r="Q281" s="14"/>
       <x:c r="R281" s="14"/>
       <x:c r="S281" s="14"/>
@@ -7037,7 +7249,7 @@
       <x:c r="M282" s="14"/>
       <x:c r="N282" s="14"/>
       <x:c r="O282" s="14"/>
-      <x:c r="P282" s="14"/>
+      <x:c r="P282" s="31"/>
       <x:c r="Q282" s="14"/>
       <x:c r="R282" s="14"/>
       <x:c r="S282" s="14"/>
@@ -7058,7 +7270,7 @@
       <x:c r="M283" s="14"/>
       <x:c r="N283" s="14"/>
       <x:c r="O283" s="14"/>
-      <x:c r="P283" s="14"/>
+      <x:c r="P283" s="31"/>
       <x:c r="Q283" s="14"/>
       <x:c r="R283" s="14"/>
       <x:c r="S283" s="14"/>
@@ -7079,7 +7291,7 @@
       <x:c r="M284" s="14"/>
       <x:c r="N284" s="14"/>
       <x:c r="O284" s="14"/>
-      <x:c r="P284" s="14"/>
+      <x:c r="P284" s="31"/>
       <x:c r="Q284" s="14"/>
       <x:c r="R284" s="14"/>
       <x:c r="S284" s="14"/>
@@ -7100,7 +7312,7 @@
       <x:c r="M285" s="14"/>
       <x:c r="N285" s="14"/>
       <x:c r="O285" s="14"/>
-      <x:c r="P285" s="14"/>
+      <x:c r="P285" s="31"/>
       <x:c r="Q285" s="14"/>
       <x:c r="R285" s="14"/>
       <x:c r="S285" s="14"/>
@@ -7121,7 +7333,7 @@
       <x:c r="M286" s="14"/>
       <x:c r="N286" s="14"/>
       <x:c r="O286" s="14"/>
-      <x:c r="P286" s="14"/>
+      <x:c r="P286" s="31"/>
       <x:c r="Q286" s="14"/>
       <x:c r="R286" s="14"/>
       <x:c r="S286" s="14"/>
@@ -7142,7 +7354,7 @@
       <x:c r="M287" s="14"/>
       <x:c r="N287" s="14"/>
       <x:c r="O287" s="14"/>
-      <x:c r="P287" s="14"/>
+      <x:c r="P287" s="31"/>
       <x:c r="Q287" s="14"/>
       <x:c r="R287" s="14"/>
       <x:c r="S287" s="14"/>
@@ -7163,7 +7375,7 @@
       <x:c r="M288" s="14"/>
       <x:c r="N288" s="14"/>
       <x:c r="O288" s="14"/>
-      <x:c r="P288" s="14"/>
+      <x:c r="P288" s="31"/>
       <x:c r="Q288" s="14"/>
       <x:c r="R288" s="14"/>
       <x:c r="S288" s="14"/>
@@ -7184,7 +7396,7 @@
       <x:c r="M289" s="14"/>
       <x:c r="N289" s="14"/>
       <x:c r="O289" s="14"/>
-      <x:c r="P289" s="14"/>
+      <x:c r="P289" s="31"/>
       <x:c r="Q289" s="14"/>
       <x:c r="R289" s="14"/>
       <x:c r="S289" s="14"/>
@@ -7205,7 +7417,7 @@
       <x:c r="M290" s="14"/>
       <x:c r="N290" s="14"/>
       <x:c r="O290" s="14"/>
-      <x:c r="P290" s="14"/>
+      <x:c r="P290" s="31"/>
       <x:c r="Q290" s="14"/>
       <x:c r="R290" s="14"/>
       <x:c r="S290" s="14"/>
@@ -7226,7 +7438,7 @@
       <x:c r="M291" s="14"/>
       <x:c r="N291" s="14"/>
       <x:c r="O291" s="14"/>
-      <x:c r="P291" s="14"/>
+      <x:c r="P291" s="31"/>
       <x:c r="Q291" s="14"/>
       <x:c r="R291" s="14"/>
       <x:c r="S291" s="14"/>
@@ -7247,7 +7459,7 @@
       <x:c r="M292" s="14"/>
       <x:c r="N292" s="14"/>
       <x:c r="O292" s="14"/>
-      <x:c r="P292" s="14"/>
+      <x:c r="P292" s="31"/>
       <x:c r="Q292" s="14"/>
       <x:c r="R292" s="14"/>
       <x:c r="S292" s="14"/>
@@ -7268,7 +7480,7 @@
       <x:c r="M293" s="14"/>
       <x:c r="N293" s="14"/>
       <x:c r="O293" s="14"/>
-      <x:c r="P293" s="14"/>
+      <x:c r="P293" s="31"/>
       <x:c r="Q293" s="14"/>
       <x:c r="R293" s="14"/>
       <x:c r="S293" s="14"/>
@@ -7289,7 +7501,7 @@
       <x:c r="M294" s="14"/>
       <x:c r="N294" s="14"/>
       <x:c r="O294" s="14"/>
-      <x:c r="P294" s="14"/>
+      <x:c r="P294" s="31"/>
       <x:c r="Q294" s="14"/>
       <x:c r="R294" s="14"/>
       <x:c r="S294" s="14"/>
@@ -7310,7 +7522,7 @@
       <x:c r="M295" s="14"/>
       <x:c r="N295" s="14"/>
       <x:c r="O295" s="14"/>
-      <x:c r="P295" s="14"/>
+      <x:c r="P295" s="31"/>
       <x:c r="Q295" s="14"/>
       <x:c r="R295" s="14"/>
       <x:c r="S295" s="14"/>
@@ -7331,7 +7543,7 @@
       <x:c r="M296" s="14"/>
       <x:c r="N296" s="14"/>
       <x:c r="O296" s="14"/>
-      <x:c r="P296" s="14"/>
+      <x:c r="P296" s="31"/>
       <x:c r="Q296" s="14"/>
       <x:c r="R296" s="14"/>
       <x:c r="S296" s="14"/>
@@ -7352,7 +7564,7 @@
       <x:c r="M297" s="14"/>
       <x:c r="N297" s="14"/>
       <x:c r="O297" s="14"/>
-      <x:c r="P297" s="14"/>
+      <x:c r="P297" s="31"/>
       <x:c r="Q297" s="14"/>
       <x:c r="R297" s="14"/>
       <x:c r="S297" s="14"/>
@@ -7373,7 +7585,7 @@
       <x:c r="M298" s="14"/>
       <x:c r="N298" s="14"/>
       <x:c r="O298" s="14"/>
-      <x:c r="P298" s="14"/>
+      <x:c r="P298" s="31"/>
       <x:c r="Q298" s="14"/>
       <x:c r="R298" s="14"/>
       <x:c r="S298" s="14"/>
@@ -7394,7 +7606,7 @@
       <x:c r="M299" s="14"/>
       <x:c r="N299" s="14"/>
       <x:c r="O299" s="14"/>
-      <x:c r="P299" s="14"/>
+      <x:c r="P299" s="31"/>
       <x:c r="Q299" s="14"/>
       <x:c r="R299" s="14"/>
       <x:c r="S299" s="14"/>
@@ -7415,7 +7627,7 @@
       <x:c r="M300" s="14"/>
       <x:c r="N300" s="14"/>
       <x:c r="O300" s="14"/>
-      <x:c r="P300" s="14"/>
+      <x:c r="P300" s="31"/>
       <x:c r="Q300" s="14"/>
       <x:c r="R300" s="14"/>
       <x:c r="S300" s="14"/>
@@ -7436,7 +7648,7 @@
       <x:c r="M301" s="14"/>
       <x:c r="N301" s="14"/>
       <x:c r="O301" s="14"/>
-      <x:c r="P301" s="14"/>
+      <x:c r="P301" s="31"/>
       <x:c r="Q301" s="14"/>
       <x:c r="R301" s="14"/>
       <x:c r="S301" s="14"/>
@@ -7457,7 +7669,7 @@
       <x:c r="M302" s="14"/>
       <x:c r="N302" s="14"/>
       <x:c r="O302" s="14"/>
-      <x:c r="P302" s="14"/>
+      <x:c r="P302" s="31"/>
       <x:c r="Q302" s="14"/>
       <x:c r="R302" s="14"/>
       <x:c r="S302" s="14"/>
@@ -7478,7 +7690,7 @@
       <x:c r="M303" s="14"/>
       <x:c r="N303" s="14"/>
       <x:c r="O303" s="14"/>
-      <x:c r="P303" s="14"/>
+      <x:c r="P303" s="31"/>
       <x:c r="Q303" s="14"/>
       <x:c r="R303" s="14"/>
       <x:c r="S303" s="14"/>
@@ -7499,7 +7711,7 @@
       <x:c r="M304" s="14"/>
       <x:c r="N304" s="14"/>
       <x:c r="O304" s="14"/>
-      <x:c r="P304" s="14"/>
+      <x:c r="P304" s="31"/>
       <x:c r="Q304" s="14"/>
       <x:c r="R304" s="14"/>
       <x:c r="S304" s="14"/>
@@ -7520,7 +7732,7 @@
       <x:c r="M305" s="14"/>
       <x:c r="N305" s="14"/>
       <x:c r="O305" s="14"/>
-      <x:c r="P305" s="14"/>
+      <x:c r="P305" s="31"/>
       <x:c r="Q305" s="14"/>
       <x:c r="R305" s="14"/>
       <x:c r="S305" s="14"/>
@@ -7541,7 +7753,7 @@
       <x:c r="M306" s="14"/>
       <x:c r="N306" s="14"/>
       <x:c r="O306" s="14"/>
-      <x:c r="P306" s="14"/>
+      <x:c r="P306" s="31"/>
       <x:c r="Q306" s="14"/>
       <x:c r="R306" s="14"/>
       <x:c r="S306" s="14"/>
@@ -7562,7 +7774,7 @@
       <x:c r="M307" s="14"/>
       <x:c r="N307" s="14"/>
       <x:c r="O307" s="14"/>
-      <x:c r="P307" s="14"/>
+      <x:c r="P307" s="31"/>
       <x:c r="Q307" s="14"/>
       <x:c r="R307" s="14"/>
       <x:c r="S307" s="14"/>
@@ -7583,7 +7795,7 @@
       <x:c r="M308" s="14"/>
       <x:c r="N308" s="14"/>
       <x:c r="O308" s="14"/>
-      <x:c r="P308" s="14"/>
+      <x:c r="P308" s="31"/>
       <x:c r="Q308" s="14"/>
       <x:c r="R308" s="14"/>
       <x:c r="S308" s="14"/>
@@ -7604,7 +7816,7 @@
       <x:c r="M309" s="14"/>
       <x:c r="N309" s="14"/>
       <x:c r="O309" s="14"/>
-      <x:c r="P309" s="14"/>
+      <x:c r="P309" s="31"/>
       <x:c r="Q309" s="14"/>
       <x:c r="R309" s="14"/>
       <x:c r="S309" s="14"/>
@@ -7625,7 +7837,7 @@
       <x:c r="M310" s="14"/>
       <x:c r="N310" s="14"/>
       <x:c r="O310" s="14"/>
-      <x:c r="P310" s="14"/>
+      <x:c r="P310" s="31"/>
       <x:c r="Q310" s="14"/>
       <x:c r="R310" s="14"/>
       <x:c r="S310" s="14"/>
@@ -7646,7 +7858,7 @@
       <x:c r="M311" s="14"/>
       <x:c r="N311" s="14"/>
       <x:c r="O311" s="14"/>
-      <x:c r="P311" s="14"/>
+      <x:c r="P311" s="31"/>
       <x:c r="Q311" s="14"/>
       <x:c r="R311" s="14"/>
       <x:c r="S311" s="14"/>
@@ -7667,7 +7879,7 @@
       <x:c r="M312" s="14"/>
       <x:c r="N312" s="14"/>
       <x:c r="O312" s="14"/>
-      <x:c r="P312" s="14"/>
+      <x:c r="P312" s="31"/>
       <x:c r="Q312" s="14"/>
       <x:c r="R312" s="14"/>
       <x:c r="S312" s="14"/>
@@ -7688,7 +7900,7 @@
       <x:c r="M313" s="14"/>
       <x:c r="N313" s="14"/>
       <x:c r="O313" s="14"/>
-      <x:c r="P313" s="14"/>
+      <x:c r="P313" s="31"/>
       <x:c r="Q313" s="14"/>
       <x:c r="R313" s="14"/>
       <x:c r="S313" s="14"/>
@@ -7709,7 +7921,7 @@
       <x:c r="M314" s="14"/>
       <x:c r="N314" s="14"/>
       <x:c r="O314" s="14"/>
-      <x:c r="P314" s="14"/>
+      <x:c r="P314" s="31"/>
       <x:c r="Q314" s="14"/>
       <x:c r="R314" s="14"/>
       <x:c r="S314" s="14"/>
@@ -7730,7 +7942,7 @@
       <x:c r="M315" s="14"/>
       <x:c r="N315" s="14"/>
       <x:c r="O315" s="14"/>
-      <x:c r="P315" s="14"/>
+      <x:c r="P315" s="31"/>
       <x:c r="Q315" s="14"/>
       <x:c r="R315" s="14"/>
       <x:c r="S315" s="14"/>
@@ -7751,7 +7963,7 @@
       <x:c r="M316" s="14"/>
       <x:c r="N316" s="14"/>
       <x:c r="O316" s="14"/>
-      <x:c r="P316" s="14"/>
+      <x:c r="P316" s="31"/>
       <x:c r="Q316" s="14"/>
       <x:c r="R316" s="14"/>
       <x:c r="S316" s="14"/>
@@ -7772,7 +7984,7 @@
       <x:c r="M317" s="14"/>
       <x:c r="N317" s="14"/>
       <x:c r="O317" s="14"/>
-      <x:c r="P317" s="14"/>
+      <x:c r="P317" s="31"/>
       <x:c r="Q317" s="14"/>
       <x:c r="R317" s="14"/>
       <x:c r="S317" s="14"/>
@@ -7793,7 +8005,7 @@
       <x:c r="M318" s="14"/>
       <x:c r="N318" s="14"/>
       <x:c r="O318" s="14"/>
-      <x:c r="P318" s="14"/>
+      <x:c r="P318" s="31"/>
       <x:c r="Q318" s="14"/>
       <x:c r="R318" s="14"/>
       <x:c r="S318" s="14"/>
@@ -7814,7 +8026,7 @@
       <x:c r="M319" s="14"/>
       <x:c r="N319" s="14"/>
       <x:c r="O319" s="14"/>
-      <x:c r="P319" s="14"/>
+      <x:c r="P319" s="31"/>
       <x:c r="Q319" s="14"/>
       <x:c r="R319" s="14"/>
       <x:c r="S319" s="14"/>
@@ -7835,7 +8047,7 @@
       <x:c r="M320" s="14"/>
       <x:c r="N320" s="14"/>
       <x:c r="O320" s="14"/>
-      <x:c r="P320" s="14"/>
+      <x:c r="P320" s="31"/>
       <x:c r="Q320" s="14"/>
       <x:c r="R320" s="14"/>
       <x:c r="S320" s="14"/>
@@ -7856,7 +8068,7 @@
       <x:c r="M321" s="14"/>
       <x:c r="N321" s="14"/>
       <x:c r="O321" s="14"/>
-      <x:c r="P321" s="14"/>
+      <x:c r="P321" s="31"/>
       <x:c r="Q321" s="14"/>
       <x:c r="R321" s="14"/>
       <x:c r="S321" s="14"/>
@@ -7877,7 +8089,7 @@
       <x:c r="M322" s="14"/>
       <x:c r="N322" s="14"/>
       <x:c r="O322" s="14"/>
-      <x:c r="P322" s="14"/>
+      <x:c r="P322" s="31"/>
       <x:c r="Q322" s="14"/>
       <x:c r="R322" s="14"/>
       <x:c r="S322" s="14"/>
@@ -7898,7 +8110,7 @@
       <x:c r="M323" s="14"/>
       <x:c r="N323" s="14"/>
       <x:c r="O323" s="14"/>
-      <x:c r="P323" s="14"/>
+      <x:c r="P323" s="31"/>
       <x:c r="Q323" s="14"/>
       <x:c r="R323" s="14"/>
       <x:c r="S323" s="14"/>
@@ -7919,7 +8131,7 @@
       <x:c r="M324" s="14"/>
       <x:c r="N324" s="14"/>
       <x:c r="O324" s="14"/>
-      <x:c r="P324" s="14"/>
+      <x:c r="P324" s="31"/>
       <x:c r="Q324" s="14"/>
       <x:c r="R324" s="14"/>
       <x:c r="S324" s="14"/>
@@ -7940,7 +8152,7 @@
       <x:c r="M325" s="14"/>
       <x:c r="N325" s="14"/>
       <x:c r="O325" s="14"/>
-      <x:c r="P325" s="14"/>
+      <x:c r="P325" s="31"/>
       <x:c r="Q325" s="14"/>
       <x:c r="R325" s="14"/>
       <x:c r="S325" s="14"/>
@@ -7961,7 +8173,7 @@
       <x:c r="M326" s="14"/>
       <x:c r="N326" s="14"/>
       <x:c r="O326" s="14"/>
-      <x:c r="P326" s="14"/>
+      <x:c r="P326" s="31"/>
       <x:c r="Q326" s="14"/>
       <x:c r="R326" s="14"/>
       <x:c r="S326" s="14"/>
@@ -7982,7 +8194,7 @@
       <x:c r="M327" s="14"/>
       <x:c r="N327" s="14"/>
       <x:c r="O327" s="14"/>
-      <x:c r="P327" s="14"/>
+      <x:c r="P327" s="31"/>
       <x:c r="Q327" s="14"/>
       <x:c r="R327" s="14"/>
       <x:c r="S327" s="14"/>
@@ -8003,7 +8215,7 @@
       <x:c r="M328" s="14"/>
       <x:c r="N328" s="14"/>
       <x:c r="O328" s="14"/>
-      <x:c r="P328" s="14"/>
+      <x:c r="P328" s="31"/>
       <x:c r="Q328" s="14"/>
       <x:c r="R328" s="14"/>
       <x:c r="S328" s="14"/>
@@ -8024,7 +8236,7 @@
       <x:c r="M329" s="14"/>
       <x:c r="N329" s="14"/>
       <x:c r="O329" s="14"/>
-      <x:c r="P329" s="14"/>
+      <x:c r="P329" s="31"/>
       <x:c r="Q329" s="14"/>
       <x:c r="R329" s="14"/>
       <x:c r="S329" s="14"/>
@@ -8045,7 +8257,7 @@
       <x:c r="M330" s="14"/>
       <x:c r="N330" s="14"/>
       <x:c r="O330" s="14"/>
-      <x:c r="P330" s="14"/>
+      <x:c r="P330" s="31"/>
       <x:c r="Q330" s="14"/>
       <x:c r="R330" s="14"/>
       <x:c r="S330" s="14"/>
@@ -8066,7 +8278,7 @@
       <x:c r="M331" s="14"/>
       <x:c r="N331" s="14"/>
       <x:c r="O331" s="14"/>
-      <x:c r="P331" s="14"/>
+      <x:c r="P331" s="31"/>
       <x:c r="Q331" s="14"/>
       <x:c r="R331" s="14"/>
       <x:c r="S331" s="14"/>
@@ -8087,7 +8299,7 @@
       <x:c r="M332" s="14"/>
       <x:c r="N332" s="14"/>
       <x:c r="O332" s="14"/>
-      <x:c r="P332" s="14"/>
+      <x:c r="P332" s="31"/>
       <x:c r="Q332" s="14"/>
       <x:c r="R332" s="14"/>
       <x:c r="S332" s="14"/>
@@ -8108,7 +8320,7 @@
       <x:c r="M333" s="14"/>
       <x:c r="N333" s="14"/>
       <x:c r="O333" s="14"/>
-      <x:c r="P333" s="14"/>
+      <x:c r="P333" s="31"/>
       <x:c r="Q333" s="14"/>
       <x:c r="R333" s="14"/>
       <x:c r="S333" s="14"/>
@@ -8129,7 +8341,7 @@
       <x:c r="M334" s="14"/>
       <x:c r="N334" s="14"/>
       <x:c r="O334" s="14"/>
-      <x:c r="P334" s="14"/>
+      <x:c r="P334" s="31"/>
       <x:c r="Q334" s="14"/>
       <x:c r="R334" s="14"/>
       <x:c r="S334" s="14"/>
@@ -8150,7 +8362,7 @@
       <x:c r="M335" s="14"/>
       <x:c r="N335" s="14"/>
       <x:c r="O335" s="14"/>
-      <x:c r="P335" s="14"/>
+      <x:c r="P335" s="31"/>
       <x:c r="Q335" s="14"/>
       <x:c r="R335" s="14"/>
       <x:c r="S335" s="14"/>
@@ -8171,7 +8383,7 @@
       <x:c r="M336" s="14"/>
       <x:c r="N336" s="14"/>
       <x:c r="O336" s="14"/>
-      <x:c r="P336" s="14"/>
+      <x:c r="P336" s="31"/>
       <x:c r="Q336" s="14"/>
       <x:c r="R336" s="14"/>
       <x:c r="S336" s="14"/>
@@ -8192,7 +8404,7 @@
       <x:c r="M337" s="14"/>
       <x:c r="N337" s="14"/>
       <x:c r="O337" s="14"/>
-      <x:c r="P337" s="14"/>
+      <x:c r="P337" s="31"/>
       <x:c r="Q337" s="14"/>
       <x:c r="R337" s="14"/>
       <x:c r="S337" s="14"/>
@@ -8213,7 +8425,7 @@
       <x:c r="M338" s="14"/>
       <x:c r="N338" s="14"/>
       <x:c r="O338" s="14"/>
-      <x:c r="P338" s="14"/>
+      <x:c r="P338" s="31"/>
       <x:c r="Q338" s="14"/>
       <x:c r="R338" s="14"/>
       <x:c r="S338" s="14"/>
@@ -8234,7 +8446,7 @@
       <x:c r="M339" s="14"/>
       <x:c r="N339" s="14"/>
       <x:c r="O339" s="14"/>
-      <x:c r="P339" s="14"/>
+      <x:c r="P339" s="31"/>
       <x:c r="Q339" s="14"/>
       <x:c r="R339" s="14"/>
       <x:c r="S339" s="14"/>
@@ -8255,7 +8467,7 @@
       <x:c r="M340" s="14"/>
       <x:c r="N340" s="14"/>
       <x:c r="O340" s="14"/>
-      <x:c r="P340" s="14"/>
+      <x:c r="P340" s="31"/>
       <x:c r="Q340" s="14"/>
       <x:c r="R340" s="14"/>
       <x:c r="S340" s="14"/>
@@ -8276,7 +8488,7 @@
       <x:c r="M341" s="14"/>
       <x:c r="N341" s="14"/>
       <x:c r="O341" s="14"/>
-      <x:c r="P341" s="14"/>
+      <x:c r="P341" s="31"/>
       <x:c r="Q341" s="14"/>
       <x:c r="R341" s="14"/>
       <x:c r="S341" s="14"/>
@@ -8297,7 +8509,7 @@
       <x:c r="M342" s="14"/>
       <x:c r="N342" s="14"/>
       <x:c r="O342" s="14"/>
-      <x:c r="P342" s="14"/>
+      <x:c r="P342" s="31"/>
       <x:c r="Q342" s="14"/>
       <x:c r="R342" s="14"/>
       <x:c r="S342" s="14"/>
@@ -8318,7 +8530,7 @@
       <x:c r="M343" s="14"/>
       <x:c r="N343" s="14"/>
       <x:c r="O343" s="14"/>
-      <x:c r="P343" s="14"/>
+      <x:c r="P343" s="31"/>
       <x:c r="Q343" s="14"/>
       <x:c r="R343" s="14"/>
       <x:c r="S343" s="14"/>
@@ -8339,7 +8551,7 @@
       <x:c r="M344" s="14"/>
       <x:c r="N344" s="14"/>
       <x:c r="O344" s="14"/>
-      <x:c r="P344" s="14"/>
+      <x:c r="P344" s="31"/>
       <x:c r="Q344" s="14"/>
       <x:c r="R344" s="14"/>
       <x:c r="S344" s="14"/>
@@ -8360,7 +8572,7 @@
       <x:c r="M345" s="14"/>
       <x:c r="N345" s="14"/>
       <x:c r="O345" s="14"/>
-      <x:c r="P345" s="14"/>
+      <x:c r="P345" s="31"/>
       <x:c r="Q345" s="14"/>
       <x:c r="R345" s="14"/>
       <x:c r="S345" s="14"/>
@@ -8381,7 +8593,7 @@
       <x:c r="M346" s="14"/>
       <x:c r="N346" s="14"/>
       <x:c r="O346" s="14"/>
-      <x:c r="P346" s="14"/>
+      <x:c r="P346" s="31"/>
       <x:c r="Q346" s="14"/>
       <x:c r="R346" s="14"/>
       <x:c r="S346" s="14"/>
@@ -8402,7 +8614,7 @@
       <x:c r="M347" s="14"/>
       <x:c r="N347" s="14"/>
       <x:c r="O347" s="14"/>
-      <x:c r="P347" s="14"/>
+      <x:c r="P347" s="31"/>
       <x:c r="Q347" s="14"/>
       <x:c r="R347" s="14"/>
       <x:c r="S347" s="14"/>
@@ -8423,7 +8635,7 @@
       <x:c r="M348" s="14"/>
       <x:c r="N348" s="14"/>
       <x:c r="O348" s="14"/>
-      <x:c r="P348" s="14"/>
+      <x:c r="P348" s="31"/>
       <x:c r="Q348" s="14"/>
       <x:c r="R348" s="14"/>
       <x:c r="S348" s="14"/>
@@ -8444,7 +8656,7 @@
       <x:c r="M349" s="14"/>
       <x:c r="N349" s="14"/>
       <x:c r="O349" s="14"/>
-      <x:c r="P349" s="14"/>
+      <x:c r="P349" s="31"/>
       <x:c r="Q349" s="14"/>
       <x:c r="R349" s="14"/>
       <x:c r="S349" s="14"/>
@@ -8465,7 +8677,7 @@
       <x:c r="M350" s="14"/>
       <x:c r="N350" s="14"/>
       <x:c r="O350" s="14"/>
-      <x:c r="P350" s="14"/>
+      <x:c r="P350" s="31"/>
       <x:c r="Q350" s="14"/>
       <x:c r="R350" s="14"/>
       <x:c r="S350" s="14"/>
@@ -8486,7 +8698,7 @@
       <x:c r="M351" s="14"/>
       <x:c r="N351" s="14"/>
       <x:c r="O351" s="14"/>
-      <x:c r="P351" s="14"/>
+      <x:c r="P351" s="31"/>
       <x:c r="Q351" s="14"/>
       <x:c r="R351" s="14"/>
       <x:c r="S351" s="14"/>
@@ -8507,7 +8719,7 @@
       <x:c r="M352" s="14"/>
       <x:c r="N352" s="14"/>
       <x:c r="O352" s="14"/>
-      <x:c r="P352" s="14"/>
+      <x:c r="P352" s="31"/>
       <x:c r="Q352" s="14"/>
       <x:c r="R352" s="14"/>
       <x:c r="S352" s="14"/>
@@ -8528,7 +8740,7 @@
       <x:c r="M353" s="14"/>
       <x:c r="N353" s="14"/>
       <x:c r="O353" s="14"/>
-      <x:c r="P353" s="14"/>
+      <x:c r="P353" s="31"/>
       <x:c r="Q353" s="14"/>
       <x:c r="R353" s="14"/>
       <x:c r="S353" s="14"/>
@@ -8549,7 +8761,7 @@
       <x:c r="M354" s="14"/>
       <x:c r="N354" s="14"/>
       <x:c r="O354" s="14"/>
-      <x:c r="P354" s="14"/>
+      <x:c r="P354" s="31"/>
       <x:c r="Q354" s="14"/>
       <x:c r="R354" s="14"/>
       <x:c r="S354" s="14"/>
@@ -8570,7 +8782,7 @@
       <x:c r="M355" s="14"/>
       <x:c r="N355" s="14"/>
       <x:c r="O355" s="14"/>
-      <x:c r="P355" s="14"/>
+      <x:c r="P355" s="31"/>
       <x:c r="Q355" s="14"/>
       <x:c r="R355" s="14"/>
       <x:c r="S355" s="14"/>
@@ -8591,7 +8803,7 @@
       <x:c r="M356" s="14"/>
       <x:c r="N356" s="14"/>
       <x:c r="O356" s="14"/>
-      <x:c r="P356" s="14"/>
+      <x:c r="P356" s="31"/>
       <x:c r="Q356" s="14"/>
       <x:c r="R356" s="14"/>
       <x:c r="S356" s="14"/>
@@ -8612,7 +8824,7 @@
       <x:c r="M357" s="14"/>
       <x:c r="N357" s="14"/>
       <x:c r="O357" s="14"/>
-      <x:c r="P357" s="14"/>
+      <x:c r="P357" s="31"/>
       <x:c r="Q357" s="14"/>
       <x:c r="R357" s="14"/>
       <x:c r="S357" s="14"/>
@@ -8633,7 +8845,7 @@
       <x:c r="M358" s="14"/>
       <x:c r="N358" s="14"/>
       <x:c r="O358" s="14"/>
-      <x:c r="P358" s="14"/>
+      <x:c r="P358" s="31"/>
       <x:c r="Q358" s="14"/>
       <x:c r="R358" s="14"/>
       <x:c r="S358" s="14"/>
@@ -8654,7 +8866,7 @@
       <x:c r="M359" s="14"/>
       <x:c r="N359" s="14"/>
       <x:c r="O359" s="14"/>
-      <x:c r="P359" s="14"/>
+      <x:c r="P359" s="31"/>
       <x:c r="Q359" s="14"/>
       <x:c r="R359" s="14"/>
       <x:c r="S359" s="14"/>
@@ -8675,7 +8887,7 @@
       <x:c r="M360" s="14"/>
       <x:c r="N360" s="14"/>
       <x:c r="O360" s="14"/>
-      <x:c r="P360" s="14"/>
+      <x:c r="P360" s="31"/>
       <x:c r="Q360" s="14"/>
       <x:c r="R360" s="14"/>
       <x:c r="S360" s="14"/>
@@ -8696,7 +8908,7 @@
       <x:c r="M361" s="14"/>
       <x:c r="N361" s="14"/>
       <x:c r="O361" s="14"/>
-      <x:c r="P361" s="14"/>
+      <x:c r="P361" s="31"/>
       <x:c r="Q361" s="14"/>
       <x:c r="R361" s="14"/>
       <x:c r="S361" s="14"/>
@@ -8717,7 +8929,7 @@
       <x:c r="M362" s="14"/>
       <x:c r="N362" s="14"/>
       <x:c r="O362" s="14"/>
-      <x:c r="P362" s="14"/>
+      <x:c r="P362" s="31"/>
       <x:c r="Q362" s="14"/>
       <x:c r="R362" s="14"/>
       <x:c r="S362" s="14"/>
@@ -8738,7 +8950,7 @@
       <x:c r="M363" s="14"/>
       <x:c r="N363" s="14"/>
       <x:c r="O363" s="14"/>
-      <x:c r="P363" s="14"/>
+      <x:c r="P363" s="31"/>
       <x:c r="Q363" s="14"/>
       <x:c r="R363" s="14"/>
       <x:c r="S363" s="14"/>
@@ -8759,7 +8971,7 @@
       <x:c r="M364" s="14"/>
       <x:c r="N364" s="14"/>
       <x:c r="O364" s="14"/>
-      <x:c r="P364" s="14"/>
+      <x:c r="P364" s="31"/>
       <x:c r="Q364" s="14"/>
       <x:c r="R364" s="14"/>
       <x:c r="S364" s="14"/>
@@ -8780,7 +8992,7 @@
       <x:c r="M365" s="14"/>
       <x:c r="N365" s="14"/>
       <x:c r="O365" s="14"/>
-      <x:c r="P365" s="14"/>
+      <x:c r="P365" s="31"/>
       <x:c r="Q365" s="14"/>
       <x:c r="R365" s="14"/>
       <x:c r="S365" s="14"/>
@@ -8801,7 +9013,7 @@
       <x:c r="M366" s="14"/>
       <x:c r="N366" s="14"/>
       <x:c r="O366" s="14"/>
-      <x:c r="P366" s="14"/>
+      <x:c r="P366" s="31"/>
       <x:c r="Q366" s="14"/>
       <x:c r="R366" s="14"/>
       <x:c r="S366" s="14"/>
@@ -8822,7 +9034,7 @@
       <x:c r="M367" s="14"/>
       <x:c r="N367" s="14"/>
       <x:c r="O367" s="14"/>
-      <x:c r="P367" s="14"/>
+      <x:c r="P367" s="31"/>
       <x:c r="Q367" s="14"/>
       <x:c r="R367" s="14"/>
       <x:c r="S367" s="14"/>
@@ -8843,7 +9055,7 @@
       <x:c r="M368" s="14"/>
       <x:c r="N368" s="14"/>
       <x:c r="O368" s="14"/>
-      <x:c r="P368" s="14"/>
+      <x:c r="P368" s="31"/>
       <x:c r="Q368" s="14"/>
       <x:c r="R368" s="14"/>
       <x:c r="S368" s="14"/>
@@ -8864,7 +9076,7 @@
       <x:c r="M369" s="14"/>
       <x:c r="N369" s="14"/>
       <x:c r="O369" s="14"/>
-      <x:c r="P369" s="14"/>
+      <x:c r="P369" s="31"/>
       <x:c r="Q369" s="14"/>
       <x:c r="R369" s="14"/>
       <x:c r="S369" s="14"/>
@@ -8885,7 +9097,7 @@
       <x:c r="M370" s="14"/>
       <x:c r="N370" s="14"/>
       <x:c r="O370" s="14"/>
-      <x:c r="P370" s="14"/>
+      <x:c r="P370" s="31"/>
       <x:c r="Q370" s="14"/>
       <x:c r="R370" s="14"/>
       <x:c r="S370" s="14"/>
@@ -8906,7 +9118,7 @@
       <x:c r="M371" s="14"/>
       <x:c r="N371" s="14"/>
       <x:c r="O371" s="14"/>
-      <x:c r="P371" s="14"/>
+      <x:c r="P371" s="31"/>
       <x:c r="Q371" s="14"/>
       <x:c r="R371" s="14"/>
       <x:c r="S371" s="14"/>
@@ -8927,7 +9139,7 @@
       <x:c r="M372" s="14"/>
       <x:c r="N372" s="14"/>
       <x:c r="O372" s="14"/>
-      <x:c r="P372" s="14"/>
+      <x:c r="P372" s="31"/>
       <x:c r="Q372" s="14"/>
       <x:c r="R372" s="14"/>
       <x:c r="S372" s="14"/>
@@ -8948,7 +9160,7 @@
       <x:c r="M373" s="14"/>
       <x:c r="N373" s="14"/>
       <x:c r="O373" s="14"/>
-      <x:c r="P373" s="14"/>
+      <x:c r="P373" s="31"/>
       <x:c r="Q373" s="14"/>
       <x:c r="R373" s="14"/>
       <x:c r="S373" s="14"/>
@@ -8969,7 +9181,7 @@
       <x:c r="M374" s="14"/>
       <x:c r="N374" s="14"/>
       <x:c r="O374" s="14"/>
-      <x:c r="P374" s="14"/>
+      <x:c r="P374" s="31"/>
       <x:c r="Q374" s="14"/>
       <x:c r="R374" s="14"/>
       <x:c r="S374" s="14"/>
@@ -8990,7 +9202,7 @@
       <x:c r="M375" s="14"/>
       <x:c r="N375" s="14"/>
       <x:c r="O375" s="14"/>
-      <x:c r="P375" s="14"/>
+      <x:c r="P375" s="31"/>
       <x:c r="Q375" s="14"/>
       <x:c r="R375" s="14"/>
       <x:c r="S375" s="14"/>
@@ -9011,7 +9223,7 @@
       <x:c r="M376" s="14"/>
       <x:c r="N376" s="14"/>
       <x:c r="O376" s="14"/>
-      <x:c r="P376" s="14"/>
+      <x:c r="P376" s="31"/>
       <x:c r="Q376" s="14"/>
       <x:c r="R376" s="14"/>
       <x:c r="S376" s="14"/>
@@ -9032,7 +9244,7 @@
       <x:c r="M377" s="14"/>
       <x:c r="N377" s="14"/>
       <x:c r="O377" s="14"/>
-      <x:c r="P377" s="14"/>
+      <x:c r="P377" s="31"/>
       <x:c r="Q377" s="14"/>
       <x:c r="R377" s="14"/>
       <x:c r="S377" s="14"/>
@@ -9053,7 +9265,7 @@
       <x:c r="M378" s="14"/>
       <x:c r="N378" s="14"/>
       <x:c r="O378" s="14"/>
-      <x:c r="P378" s="14"/>
+      <x:c r="P378" s="31"/>
       <x:c r="Q378" s="14"/>
       <x:c r="R378" s="14"/>
       <x:c r="S378" s="14"/>
@@ -9074,7 +9286,7 @@
       <x:c r="M379" s="14"/>
       <x:c r="N379" s="14"/>
       <x:c r="O379" s="14"/>
-      <x:c r="P379" s="14"/>
+      <x:c r="P379" s="31"/>
       <x:c r="Q379" s="14"/>
       <x:c r="R379" s="14"/>
       <x:c r="S379" s="14"/>
@@ -9095,7 +9307,7 @@
       <x:c r="M380" s="14"/>
       <x:c r="N380" s="14"/>
       <x:c r="O380" s="14"/>
-      <x:c r="P380" s="14"/>
+      <x:c r="P380" s="31"/>
       <x:c r="Q380" s="14"/>
       <x:c r="R380" s="14"/>
       <x:c r="S380" s="14"/>
@@ -9116,7 +9328,7 @@
       <x:c r="M381" s="14"/>
       <x:c r="N381" s="14"/>
       <x:c r="O381" s="14"/>
-      <x:c r="P381" s="14"/>
+      <x:c r="P381" s="31"/>
       <x:c r="Q381" s="14"/>
       <x:c r="R381" s="14"/>
       <x:c r="S381" s="14"/>
@@ -9137,7 +9349,7 @@
       <x:c r="M382" s="14"/>
       <x:c r="N382" s="14"/>
       <x:c r="O382" s="14"/>
-      <x:c r="P382" s="14"/>
+      <x:c r="P382" s="31"/>
       <x:c r="Q382" s="14"/>
       <x:c r="R382" s="14"/>
       <x:c r="S382" s="14"/>
@@ -9158,7 +9370,7 @@
       <x:c r="M383" s="14"/>
       <x:c r="N383" s="14"/>
       <x:c r="O383" s="14"/>
-      <x:c r="P383" s="14"/>
+      <x:c r="P383" s="31"/>
       <x:c r="Q383" s="14"/>
       <x:c r="R383" s="14"/>
       <x:c r="S383" s="14"/>
@@ -9179,7 +9391,7 @@
       <x:c r="M384" s="14"/>
       <x:c r="N384" s="14"/>
       <x:c r="O384" s="14"/>
-      <x:c r="P384" s="14"/>
+      <x:c r="P384" s="31"/>
       <x:c r="Q384" s="14"/>
       <x:c r="R384" s="14"/>
       <x:c r="S384" s="14"/>
@@ -9200,7 +9412,7 @@
       <x:c r="M385" s="14"/>
       <x:c r="N385" s="14"/>
       <x:c r="O385" s="14"/>
-      <x:c r="P385" s="14"/>
+      <x:c r="P385" s="31"/>
       <x:c r="Q385" s="14"/>
       <x:c r="R385" s="14"/>
       <x:c r="S385" s="14"/>
@@ -9221,7 +9433,7 @@
       <x:c r="M386" s="14"/>
       <x:c r="N386" s="14"/>
       <x:c r="O386" s="14"/>
-      <x:c r="P386" s="14"/>
+      <x:c r="P386" s="31"/>
       <x:c r="Q386" s="14"/>
       <x:c r="R386" s="14"/>
       <x:c r="S386" s="14"/>
@@ -9242,7 +9454,7 @@
       <x:c r="M387" s="14"/>
       <x:c r="N387" s="14"/>
       <x:c r="O387" s="14"/>
-      <x:c r="P387" s="14"/>
+      <x:c r="P387" s="31"/>
       <x:c r="Q387" s="14"/>
       <x:c r="R387" s="14"/>
       <x:c r="S387" s="14"/>
@@ -9263,7 +9475,7 @@
       <x:c r="M388" s="14"/>
       <x:c r="N388" s="14"/>
       <x:c r="O388" s="14"/>
-      <x:c r="P388" s="14"/>
+      <x:c r="P388" s="31"/>
       <x:c r="Q388" s="14"/>
       <x:c r="R388" s="14"/>
       <x:c r="S388" s="14"/>
@@ -9284,7 +9496,7 @@
       <x:c r="M389" s="14"/>
       <x:c r="N389" s="14"/>
       <x:c r="O389" s="14"/>
-      <x:c r="P389" s="14"/>
+      <x:c r="P389" s="31"/>
       <x:c r="Q389" s="14"/>
       <x:c r="R389" s="14"/>
       <x:c r="S389" s="14"/>
@@ -9305,7 +9517,7 @@
       <x:c r="M390" s="14"/>
       <x:c r="N390" s="14"/>
       <x:c r="O390" s="14"/>
-      <x:c r="P390" s="14"/>
+      <x:c r="P390" s="31"/>
       <x:c r="Q390" s="14"/>
       <x:c r="R390" s="14"/>
       <x:c r="S390" s="14"/>
@@ -9326,7 +9538,7 @@
       <x:c r="M391" s="14"/>
       <x:c r="N391" s="14"/>
       <x:c r="O391" s="14"/>
-      <x:c r="P391" s="14"/>
+      <x:c r="P391" s="31"/>
       <x:c r="Q391" s="14"/>
       <x:c r="R391" s="14"/>
       <x:c r="S391" s="14"/>
@@ -9347,7 +9559,7 @@
       <x:c r="M392" s="14"/>
       <x:c r="N392" s="14"/>
       <x:c r="O392" s="14"/>
-      <x:c r="P392" s="14"/>
+      <x:c r="P392" s="31"/>
       <x:c r="Q392" s="14"/>
       <x:c r="R392" s="14"/>
       <x:c r="S392" s="14"/>
@@ -9368,7 +9580,7 @@
       <x:c r="M393" s="14"/>
       <x:c r="N393" s="14"/>
       <x:c r="O393" s="14"/>
-      <x:c r="P393" s="14"/>
+      <x:c r="P393" s="31"/>
       <x:c r="Q393" s="14"/>
       <x:c r="R393" s="14"/>
       <x:c r="S393" s="14"/>
@@ -9389,7 +9601,7 @@
       <x:c r="M394" s="14"/>
       <x:c r="N394" s="14"/>
       <x:c r="O394" s="14"/>
-      <x:c r="P394" s="14"/>
+      <x:c r="P394" s="31"/>
       <x:c r="Q394" s="14"/>
       <x:c r="R394" s="14"/>
       <x:c r="S394" s="14"/>
@@ -9410,7 +9622,7 @@
       <x:c r="M395" s="14"/>
       <x:c r="N395" s="14"/>
       <x:c r="O395" s="14"/>
-      <x:c r="P395" s="14"/>
+      <x:c r="P395" s="31"/>
       <x:c r="Q395" s="14"/>
       <x:c r="R395" s="14"/>
       <x:c r="S395" s="14"/>
@@ -9431,7 +9643,7 @@
       <x:c r="M396" s="14"/>
       <x:c r="N396" s="14"/>
       <x:c r="O396" s="14"/>
-      <x:c r="P396" s="14"/>
+      <x:c r="P396" s="31"/>
       <x:c r="Q396" s="14"/>
       <x:c r="R396" s="14"/>
       <x:c r="S396" s="14"/>
@@ -9452,7 +9664,7 @@
       <x:c r="M397" s="14"/>
       <x:c r="N397" s="14"/>
       <x:c r="O397" s="14"/>
-      <x:c r="P397" s="14"/>
+      <x:c r="P397" s="31"/>
       <x:c r="Q397" s="14"/>
       <x:c r="R397" s="14"/>
       <x:c r="S397" s="14"/>
@@ -9473,7 +9685,7 @@
       <x:c r="M398" s="14"/>
       <x:c r="N398" s="14"/>
       <x:c r="O398" s="14"/>
-      <x:c r="P398" s="14"/>
+      <x:c r="P398" s="31"/>
       <x:c r="Q398" s="14"/>
       <x:c r="R398" s="14"/>
       <x:c r="S398" s="14"/>
@@ -9494,7 +9706,7 @@
       <x:c r="M399" s="14"/>
       <x:c r="N399" s="14"/>
       <x:c r="O399" s="14"/>
-      <x:c r="P399" s="14"/>
+      <x:c r="P399" s="31"/>
       <x:c r="Q399" s="14"/>
       <x:c r="R399" s="14"/>
       <x:c r="S399" s="14"/>
@@ -9515,7 +9727,7 @@
       <x:c r="M400" s="14"/>
       <x:c r="N400" s="14"/>
       <x:c r="O400" s="14"/>
-      <x:c r="P400" s="14"/>
+      <x:c r="P400" s="31"/>
       <x:c r="Q400" s="14"/>
       <x:c r="R400" s="14"/>
       <x:c r="S400" s="14"/>
@@ -9536,7 +9748,7 @@
       <x:c r="M401" s="14"/>
       <x:c r="N401" s="14"/>
       <x:c r="O401" s="14"/>
-      <x:c r="P401" s="14"/>
+      <x:c r="P401" s="31"/>
       <x:c r="Q401" s="14"/>
       <x:c r="R401" s="14"/>
       <x:c r="S401" s="14"/>
@@ -9557,7 +9769,7 @@
       <x:c r="M402" s="14"/>
       <x:c r="N402" s="14"/>
       <x:c r="O402" s="14"/>
-      <x:c r="P402" s="14"/>
+      <x:c r="P402" s="31"/>
       <x:c r="Q402" s="14"/>
       <x:c r="R402" s="14"/>
       <x:c r="S402" s="14"/>
@@ -9578,7 +9790,7 @@
       <x:c r="M403" s="14"/>
       <x:c r="N403" s="14"/>
       <x:c r="O403" s="14"/>
-      <x:c r="P403" s="14"/>
+      <x:c r="P403" s="31"/>
       <x:c r="Q403" s="14"/>
       <x:c r="R403" s="14"/>
       <x:c r="S403" s="14"/>
@@ -9599,7 +9811,7 @@
       <x:c r="M404" s="14"/>
       <x:c r="N404" s="14"/>
       <x:c r="O404" s="14"/>
-      <x:c r="P404" s="14"/>
+      <x:c r="P404" s="31"/>
       <x:c r="Q404" s="14"/>
       <x:c r="R404" s="14"/>
       <x:c r="S404" s="14"/>
@@ -9620,7 +9832,7 @@
       <x:c r="M405" s="14"/>
       <x:c r="N405" s="14"/>
       <x:c r="O405" s="14"/>
-      <x:c r="P405" s="14"/>
+      <x:c r="P405" s="31"/>
       <x:c r="Q405" s="14"/>
       <x:c r="R405" s="14"/>
       <x:c r="S405" s="14"/>
@@ -9641,7 +9853,7 @@
       <x:c r="M406" s="14"/>
       <x:c r="N406" s="14"/>
       <x:c r="O406" s="14"/>
-      <x:c r="P406" s="14"/>
+      <x:c r="P406" s="31"/>
       <x:c r="Q406" s="14"/>
       <x:c r="R406" s="14"/>
       <x:c r="S406" s="14"/>
@@ -9662,7 +9874,7 @@
       <x:c r="M407" s="14"/>
       <x:c r="N407" s="14"/>
       <x:c r="O407" s="14"/>
-      <x:c r="P407" s="14"/>
+      <x:c r="P407" s="31"/>
       <x:c r="Q407" s="14"/>
       <x:c r="R407" s="14"/>
       <x:c r="S407" s="14"/>
@@ -9683,7 +9895,7 @@
       <x:c r="M408" s="14"/>
       <x:c r="N408" s="14"/>
       <x:c r="O408" s="14"/>
-      <x:c r="P408" s="14"/>
+      <x:c r="P408" s="31"/>
       <x:c r="Q408" s="14"/>
       <x:c r="R408" s="14"/>
       <x:c r="S408" s="14"/>
@@ -9704,7 +9916,7 @@
       <x:c r="M409" s="14"/>
       <x:c r="N409" s="14"/>
       <x:c r="O409" s="14"/>
-      <x:c r="P409" s="14"/>
+      <x:c r="P409" s="31"/>
       <x:c r="Q409" s="14"/>
       <x:c r="R409" s="14"/>
       <x:c r="S409" s="14"/>
@@ -9725,7 +9937,7 @@
       <x:c r="M410" s="14"/>
       <x:c r="N410" s="14"/>
       <x:c r="O410" s="14"/>
-      <x:c r="P410" s="14"/>
+      <x:c r="P410" s="31"/>
       <x:c r="Q410" s="14"/>
       <x:c r="R410" s="14"/>
       <x:c r="S410" s="14"/>
@@ -9746,7 +9958,7 @@
       <x:c r="M411" s="14"/>
       <x:c r="N411" s="14"/>
       <x:c r="O411" s="14"/>
-      <x:c r="P411" s="14"/>
+      <x:c r="P411" s="31"/>
       <x:c r="Q411" s="14"/>
       <x:c r="R411" s="14"/>
       <x:c r="S411" s="14"/>
@@ -9767,7 +9979,7 @@
       <x:c r="M412" s="14"/>
       <x:c r="N412" s="14"/>
       <x:c r="O412" s="14"/>
-      <x:c r="P412" s="14"/>
+      <x:c r="P412" s="31"/>
       <x:c r="Q412" s="14"/>
       <x:c r="R412" s="14"/>
       <x:c r="S412" s="14"/>
@@ -9788,7 +10000,7 @@
       <x:c r="M413" s="14"/>
       <x:c r="N413" s="14"/>
       <x:c r="O413" s="14"/>
-      <x:c r="P413" s="14"/>
+      <x:c r="P413" s="31"/>
       <x:c r="Q413" s="14"/>
       <x:c r="R413" s="14"/>
       <x:c r="S413" s="14"/>
@@ -9809,7 +10021,7 @@
       <x:c r="M414" s="14"/>
       <x:c r="N414" s="14"/>
       <x:c r="O414" s="14"/>
-      <x:c r="P414" s="14"/>
+      <x:c r="P414" s="31"/>
       <x:c r="Q414" s="14"/>
       <x:c r="R414" s="14"/>
       <x:c r="S414" s="14"/>
@@ -9830,7 +10042,7 @@
       <x:c r="M415" s="14"/>
       <x:c r="N415" s="14"/>
       <x:c r="O415" s="14"/>
-      <x:c r="P415" s="14"/>
+      <x:c r="P415" s="31"/>
       <x:c r="Q415" s="14"/>
       <x:c r="R415" s="14"/>
       <x:c r="S415" s="14"/>
@@ -9851,7 +10063,7 @@
       <x:c r="M416" s="14"/>
       <x:c r="N416" s="14"/>
       <x:c r="O416" s="14"/>
-      <x:c r="P416" s="14"/>
+      <x:c r="P416" s="31"/>
       <x:c r="Q416" s="14"/>
       <x:c r="R416" s="14"/>
       <x:c r="S416" s="14"/>
@@ -9872,7 +10084,7 @@
       <x:c r="M417" s="14"/>
       <x:c r="N417" s="14"/>
       <x:c r="O417" s="14"/>
-      <x:c r="P417" s="14"/>
+      <x:c r="P417" s="31"/>
       <x:c r="Q417" s="14"/>
       <x:c r="R417" s="14"/>
       <x:c r="S417" s="14"/>
@@ -9893,7 +10105,7 @@
       <x:c r="M418" s="14"/>
       <x:c r="N418" s="14"/>
       <x:c r="O418" s="14"/>
-      <x:c r="P418" s="14"/>
+      <x:c r="P418" s="31"/>
       <x:c r="Q418" s="14"/>
       <x:c r="R418" s="14"/>
       <x:c r="S418" s="14"/>
@@ -9914,7 +10126,7 @@
       <x:c r="M419" s="14"/>
       <x:c r="N419" s="14"/>
       <x:c r="O419" s="14"/>
-      <x:c r="P419" s="14"/>
+      <x:c r="P419" s="31"/>
       <x:c r="Q419" s="14"/>
       <x:c r="R419" s="14"/>
       <x:c r="S419" s="14"/>
@@ -9935,7 +10147,7 @@
       <x:c r="M420" s="14"/>
       <x:c r="N420" s="14"/>
       <x:c r="O420" s="14"/>
-      <x:c r="P420" s="14"/>
+      <x:c r="P420" s="31"/>
       <x:c r="Q420" s="14"/>
       <x:c r="R420" s="14"/>
       <x:c r="S420" s="14"/>
@@ -9956,7 +10168,7 @@
       <x:c r="M421" s="14"/>
       <x:c r="N421" s="14"/>
       <x:c r="O421" s="14"/>
-      <x:c r="P421" s="14"/>
+      <x:c r="P421" s="31"/>
       <x:c r="Q421" s="14"/>
       <x:c r="R421" s="14"/>
       <x:c r="S421" s="14"/>
@@ -9977,7 +10189,7 @@
       <x:c r="M422" s="14"/>
       <x:c r="N422" s="14"/>
       <x:c r="O422" s="14"/>
-      <x:c r="P422" s="14"/>
+      <x:c r="P422" s="31"/>
       <x:c r="Q422" s="14"/>
       <x:c r="R422" s="14"/>
       <x:c r="S422" s="14"/>
@@ -9998,7 +10210,7 @@
       <x:c r="M423" s="14"/>
       <x:c r="N423" s="14"/>
       <x:c r="O423" s="14"/>
-      <x:c r="P423" s="14"/>
+      <x:c r="P423" s="31"/>
       <x:c r="Q423" s="14"/>
       <x:c r="R423" s="14"/>
       <x:c r="S423" s="14"/>
@@ -10019,7 +10231,7 @@
       <x:c r="M424" s="14"/>
       <x:c r="N424" s="14"/>
       <x:c r="O424" s="14"/>
-      <x:c r="P424" s="14"/>
+      <x:c r="P424" s="31"/>
       <x:c r="Q424" s="14"/>
       <x:c r="R424" s="14"/>
       <x:c r="S424" s="14"/>
@@ -10040,7 +10252,7 @@
       <x:c r="M425" s="14"/>
       <x:c r="N425" s="14"/>
       <x:c r="O425" s="14"/>
-      <x:c r="P425" s="14"/>
+      <x:c r="P425" s="31"/>
       <x:c r="Q425" s="14"/>
       <x:c r="R425" s="14"/>
       <x:c r="S425" s="14"/>
@@ -10061,7 +10273,7 @@
       <x:c r="M426" s="14"/>
       <x:c r="N426" s="14"/>
       <x:c r="O426" s="14"/>
-      <x:c r="P426" s="14"/>
+      <x:c r="P426" s="31"/>
       <x:c r="Q426" s="14"/>
       <x:c r="R426" s="14"/>
       <x:c r="S426" s="14"/>
@@ -10082,7 +10294,7 @@
       <x:c r="M427" s="14"/>
       <x:c r="N427" s="14"/>
       <x:c r="O427" s="14"/>
-      <x:c r="P427" s="14"/>
+      <x:c r="P427" s="31"/>
       <x:c r="Q427" s="14"/>
       <x:c r="R427" s="14"/>
       <x:c r="S427" s="14"/>
@@ -10103,7 +10315,7 @@
       <x:c r="M428" s="14"/>
       <x:c r="N428" s="14"/>
       <x:c r="O428" s="14"/>
-      <x:c r="P428" s="14"/>
+      <x:c r="P428" s="31"/>
       <x:c r="Q428" s="14"/>
       <x:c r="R428" s="14"/>
       <x:c r="S428" s="14"/>
@@ -10124,7 +10336,7 @@
       <x:c r="M429" s="14"/>
       <x:c r="N429" s="14"/>
       <x:c r="O429" s="14"/>
-      <x:c r="P429" s="14"/>
+      <x:c r="P429" s="31"/>
       <x:c r="Q429" s="14"/>
       <x:c r="R429" s="14"/>
       <x:c r="S429" s="14"/>
@@ -10145,7 +10357,7 @@
       <x:c r="M430" s="14"/>
       <x:c r="N430" s="14"/>
       <x:c r="O430" s="14"/>
-      <x:c r="P430" s="14"/>
+      <x:c r="P430" s="31"/>
       <x:c r="Q430" s="14"/>
       <x:c r="R430" s="14"/>
       <x:c r="S430" s="14"/>
@@ -10166,7 +10378,7 @@
       <x:c r="M431" s="14"/>
       <x:c r="N431" s="14"/>
       <x:c r="O431" s="14"/>
-      <x:c r="P431" s="14"/>
+      <x:c r="P431" s="31"/>
       <x:c r="Q431" s="14"/>
       <x:c r="R431" s="14"/>
       <x:c r="S431" s="14"/>
@@ -10187,7 +10399,7 @@
       <x:c r="M432" s="14"/>
       <x:c r="N432" s="14"/>
       <x:c r="O432" s="14"/>
-      <x:c r="P432" s="14"/>
+      <x:c r="P432" s="31"/>
       <x:c r="Q432" s="14"/>
       <x:c r="R432" s="14"/>
       <x:c r="S432" s="14"/>
@@ -10208,7 +10420,7 @@
       <x:c r="M433" s="14"/>
       <x:c r="N433" s="14"/>
       <x:c r="O433" s="14"/>
-      <x:c r="P433" s="14"/>
+      <x:c r="P433" s="31"/>
       <x:c r="Q433" s="14"/>
       <x:c r="R433" s="14"/>
       <x:c r="S433" s="14"/>
@@ -10229,7 +10441,7 @@
       <x:c r="M434" s="14"/>
       <x:c r="N434" s="14"/>
       <x:c r="O434" s="14"/>
-      <x:c r="P434" s="14"/>
+      <x:c r="P434" s="31"/>
       <x:c r="Q434" s="14"/>
       <x:c r="R434" s="14"/>
       <x:c r="S434" s="14"/>
@@ -10250,7 +10462,7 @@
       <x:c r="M435" s="14"/>
       <x:c r="N435" s="14"/>
       <x:c r="O435" s="14"/>
-      <x:c r="P435" s="14"/>
+      <x:c r="P435" s="31"/>
       <x:c r="Q435" s="14"/>
       <x:c r="R435" s="14"/>
       <x:c r="S435" s="14"/>
@@ -10271,7 +10483,7 @@
       <x:c r="M436" s="14"/>
       <x:c r="N436" s="14"/>
       <x:c r="O436" s="14"/>
-      <x:c r="P436" s="14"/>
+      <x:c r="P436" s="31"/>
       <x:c r="Q436" s="14"/>
       <x:c r="R436" s="14"/>
       <x:c r="S436" s="14"/>
@@ -10292,7 +10504,7 @@
       <x:c r="M437" s="14"/>
       <x:c r="N437" s="14"/>
       <x:c r="O437" s="14"/>
-      <x:c r="P437" s="14"/>
+      <x:c r="P437" s="31"/>
       <x:c r="Q437" s="14"/>
       <x:c r="R437" s="14"/>
       <x:c r="S437" s="14"/>
@@ -10313,7 +10525,7 @@
       <x:c r="M438" s="14"/>
       <x:c r="N438" s="14"/>
       <x:c r="O438" s="14"/>
-      <x:c r="P438" s="14"/>
+      <x:c r="P438" s="31"/>
       <x:c r="Q438" s="14"/>
       <x:c r="R438" s="14"/>
       <x:c r="S438" s="14"/>
@@ -10334,7 +10546,7 @@
       <x:c r="M439" s="14"/>
       <x:c r="N439" s="14"/>
       <x:c r="O439" s="14"/>
-      <x:c r="P439" s="14"/>
+      <x:c r="P439" s="31"/>
       <x:c r="Q439" s="14"/>
       <x:c r="R439" s="14"/>
       <x:c r="S439" s="14"/>
@@ -10355,7 +10567,7 @@
       <x:c r="M440" s="14"/>
       <x:c r="N440" s="14"/>
       <x:c r="O440" s="14"/>
-      <x:c r="P440" s="14"/>
+      <x:c r="P440" s="31"/>
       <x:c r="Q440" s="14"/>
       <x:c r="R440" s="14"/>
       <x:c r="S440" s="14"/>
@@ -10376,7 +10588,7 @@
       <x:c r="M441" s="14"/>
       <x:c r="N441" s="14"/>
       <x:c r="O441" s="14"/>
-      <x:c r="P441" s="14"/>
+      <x:c r="P441" s="31"/>
       <x:c r="Q441" s="14"/>
       <x:c r="R441" s="14"/>
       <x:c r="S441" s="14"/>
@@ -10397,7 +10609,7 @@
       <x:c r="M442" s="14"/>
       <x:c r="N442" s="14"/>
       <x:c r="O442" s="14"/>
-      <x:c r="P442" s="14"/>
+      <x:c r="P442" s="31"/>
       <x:c r="Q442" s="14"/>
       <x:c r="R442" s="14"/>
       <x:c r="S442" s="14"/>
@@ -10418,7 +10630,7 @@
       <x:c r="M443" s="14"/>
       <x:c r="N443" s="14"/>
       <x:c r="O443" s="14"/>
-      <x:c r="P443" s="14"/>
+      <x:c r="P443" s="31"/>
       <x:c r="Q443" s="14"/>
       <x:c r="R443" s="14"/>
       <x:c r="S443" s="14"/>
@@ -10439,7 +10651,7 @@
       <x:c r="M444" s="14"/>
       <x:c r="N444" s="14"/>
       <x:c r="O444" s="14"/>
-      <x:c r="P444" s="14"/>
+      <x:c r="P444" s="31"/>
       <x:c r="Q444" s="14"/>
       <x:c r="R444" s="14"/>
       <x:c r="S444" s="14"/>
@@ -10460,7 +10672,7 @@
       <x:c r="M445" s="14"/>
       <x:c r="N445" s="14"/>
       <x:c r="O445" s="14"/>
-      <x:c r="P445" s="14"/>
+      <x:c r="P445" s="31"/>
       <x:c r="Q445" s="14"/>
       <x:c r="R445" s="14"/>
       <x:c r="S445" s="14"/>
@@ -10481,7 +10693,7 @@
       <x:c r="M446" s="14"/>
       <x:c r="N446" s="14"/>
       <x:c r="O446" s="14"/>
-      <x:c r="P446" s="14"/>
+      <x:c r="P446" s="31"/>
       <x:c r="Q446" s="14"/>
       <x:c r="R446" s="14"/>
       <x:c r="S446" s="14"/>
@@ -10502,7 +10714,7 @@
       <x:c r="M447" s="14"/>
       <x:c r="N447" s="14"/>
       <x:c r="O447" s="14"/>
-      <x:c r="P447" s="14"/>
+      <x:c r="P447" s="31"/>
       <x:c r="Q447" s="14"/>
       <x:c r="R447" s="14"/>
       <x:c r="S447" s="14"/>
@@ -10523,7 +10735,7 @@
       <x:c r="M448" s="14"/>
       <x:c r="N448" s="14"/>
       <x:c r="O448" s="14"/>
-      <x:c r="P448" s="14"/>
+      <x:c r="P448" s="31"/>
       <x:c r="Q448" s="14"/>
       <x:c r="R448" s="14"/>
       <x:c r="S448" s="14"/>
@@ -10544,7 +10756,7 @@
       <x:c r="M449" s="14"/>
       <x:c r="N449" s="14"/>
       <x:c r="O449" s="14"/>
-      <x:c r="P449" s="14"/>
+      <x:c r="P449" s="31"/>
       <x:c r="Q449" s="14"/>
       <x:c r="R449" s="14"/>
       <x:c r="S449" s="14"/>
@@ -10565,7 +10777,7 @@
       <x:c r="M450" s="14"/>
       <x:c r="N450" s="14"/>
       <x:c r="O450" s="14"/>
-      <x:c r="P450" s="14"/>
+      <x:c r="P450" s="31"/>
       <x:c r="Q450" s="14"/>
       <x:c r="R450" s="14"/>
       <x:c r="S450" s="14"/>
@@ -10586,7 +10798,7 @@
       <x:c r="M451" s="14"/>
       <x:c r="N451" s="14"/>
       <x:c r="O451" s="14"/>
-      <x:c r="P451" s="14"/>
+      <x:c r="P451" s="31"/>
       <x:c r="Q451" s="14"/>
       <x:c r="R451" s="14"/>
       <x:c r="S451" s="14"/>
@@ -10607,7 +10819,7 @@
       <x:c r="M452" s="14"/>
       <x:c r="N452" s="14"/>
       <x:c r="O452" s="14"/>
-      <x:c r="P452" s="14"/>
+      <x:c r="P452" s="31"/>
       <x:c r="Q452" s="14"/>
       <x:c r="R452" s="14"/>
       <x:c r="S452" s="14"/>
@@ -10628,7 +10840,7 @@
       <x:c r="M453" s="14"/>
       <x:c r="N453" s="14"/>
       <x:c r="O453" s="14"/>
-      <x:c r="P453" s="14"/>
+      <x:c r="P453" s="31"/>
       <x:c r="Q453" s="14"/>
       <x:c r="R453" s="14"/>
       <x:c r="S453" s="14"/>
@@ -10649,7 +10861,7 @@
       <x:c r="M454" s="14"/>
       <x:c r="N454" s="14"/>
       <x:c r="O454" s="14"/>
-      <x:c r="P454" s="14"/>
+      <x:c r="P454" s="31"/>
       <x:c r="Q454" s="14"/>
       <x:c r="R454" s="14"/>
       <x:c r="S454" s="14"/>
@@ -10670,7 +10882,7 @@
       <x:c r="M455" s="14"/>
       <x:c r="N455" s="14"/>
       <x:c r="O455" s="14"/>
-      <x:c r="P455" s="14"/>
+      <x:c r="P455" s="31"/>
       <x:c r="Q455" s="14"/>
       <x:c r="R455" s="14"/>
       <x:c r="S455" s="14"/>
@@ -10691,7 +10903,7 @@
       <x:c r="M456" s="14"/>
       <x:c r="N456" s="14"/>
       <x:c r="O456" s="14"/>
-      <x:c r="P456" s="14"/>
+      <x:c r="P456" s="31"/>
       <x:c r="Q456" s="14"/>
       <x:c r="R456" s="14"/>
       <x:c r="S456" s="14"/>
@@ -10712,7 +10924,7 @@
       <x:c r="M457" s="14"/>
       <x:c r="N457" s="14"/>
       <x:c r="O457" s="14"/>
-      <x:c r="P457" s="14"/>
+      <x:c r="P457" s="31"/>
       <x:c r="Q457" s="14"/>
       <x:c r="R457" s="14"/>
       <x:c r="S457" s="14"/>
@@ -10733,7 +10945,7 @@
       <x:c r="M458" s="14"/>
       <x:c r="N458" s="14"/>
       <x:c r="O458" s="14"/>
-      <x:c r="P458" s="14"/>
+      <x:c r="P458" s="31"/>
       <x:c r="Q458" s="14"/>
       <x:c r="R458" s="14"/>
       <x:c r="S458" s="14"/>
@@ -10754,7 +10966,7 @@
       <x:c r="M459" s="14"/>
       <x:c r="N459" s="14"/>
       <x:c r="O459" s="14"/>
-      <x:c r="P459" s="14"/>
+      <x:c r="P459" s="31"/>
       <x:c r="Q459" s="14"/>
       <x:c r="R459" s="14"/>
       <x:c r="S459" s="14"/>
@@ -10775,7 +10987,7 @@
       <x:c r="M460" s="14"/>
       <x:c r="N460" s="14"/>
       <x:c r="O460" s="14"/>
-      <x:c r="P460" s="14"/>
+      <x:c r="P460" s="31"/>
       <x:c r="Q460" s="14"/>
       <x:c r="R460" s="14"/>
       <x:c r="S460" s="14"/>
@@ -10796,7 +11008,7 @@
       <x:c r="M461" s="14"/>
       <x:c r="N461" s="14"/>
       <x:c r="O461" s="14"/>
-      <x:c r="P461" s="14"/>
+      <x:c r="P461" s="31"/>
       <x:c r="Q461" s="14"/>
       <x:c r="R461" s="14"/>
       <x:c r="S461" s="14"/>
@@ -10817,7 +11029,7 @@
       <x:c r="M462" s="14"/>
       <x:c r="N462" s="14"/>
       <x:c r="O462" s="14"/>
-      <x:c r="P462" s="14"/>
+      <x:c r="P462" s="31"/>
       <x:c r="Q462" s="14"/>
       <x:c r="R462" s="14"/>
       <x:c r="S462" s="14"/>
@@ -10838,7 +11050,7 @@
       <x:c r="M463" s="14"/>
       <x:c r="N463" s="14"/>
       <x:c r="O463" s="14"/>
-      <x:c r="P463" s="14"/>
+      <x:c r="P463" s="31"/>
       <x:c r="Q463" s="14"/>
       <x:c r="R463" s="14"/>
       <x:c r="S463" s="14"/>
@@ -10859,7 +11071,7 @@
       <x:c r="M464" s="14"/>
       <x:c r="N464" s="14"/>
       <x:c r="O464" s="14"/>
-      <x:c r="P464" s="14"/>
+      <x:c r="P464" s="31"/>
       <x:c r="Q464" s="14"/>
       <x:c r="R464" s="14"/>
       <x:c r="S464" s="14"/>
@@ -10880,7 +11092,7 @@
       <x:c r="M465" s="14"/>
       <x:c r="N465" s="14"/>
       <x:c r="O465" s="14"/>
-      <x:c r="P465" s="14"/>
+      <x:c r="P465" s="31"/>
       <x:c r="Q465" s="14"/>
       <x:c r="R465" s="14"/>
       <x:c r="S465" s="14"/>
@@ -10901,7 +11113,7 @@
       <x:c r="M466" s="14"/>
       <x:c r="N466" s="14"/>
       <x:c r="O466" s="14"/>
-      <x:c r="P466" s="14"/>
+      <x:c r="P466" s="31"/>
       <x:c r="Q466" s="14"/>
       <x:c r="R466" s="14"/>
       <x:c r="S466" s="14"/>
@@ -10922,7 +11134,7 @@
       <x:c r="M467" s="14"/>
       <x:c r="N467" s="14"/>
       <x:c r="O467" s="14"/>
-      <x:c r="P467" s="14"/>
+      <x:c r="P467" s="31"/>
       <x:c r="Q467" s="14"/>
       <x:c r="R467" s="14"/>
       <x:c r="S467" s="14"/>
@@ -10943,7 +11155,7 @@
       <x:c r="M468" s="14"/>
       <x:c r="N468" s="14"/>
       <x:c r="O468" s="14"/>
-      <x:c r="P468" s="14"/>
+      <x:c r="P468" s="31"/>
       <x:c r="Q468" s="14"/>
       <x:c r="R468" s="14"/>
       <x:c r="S468" s="14"/>
@@ -10964,7 +11176,7 @@
       <x:c r="M469" s="14"/>
       <x:c r="N469" s="14"/>
       <x:c r="O469" s="14"/>
-      <x:c r="P469" s="14"/>
+      <x:c r="P469" s="31"/>
       <x:c r="Q469" s="14"/>
       <x:c r="R469" s="14"/>
       <x:c r="S469" s="14"/>
@@ -10985,7 +11197,7 @@
       <x:c r="M470" s="14"/>
       <x:c r="N470" s="14"/>
       <x:c r="O470" s="14"/>
-      <x:c r="P470" s="14"/>
+      <x:c r="P470" s="31"/>
       <x:c r="Q470" s="14"/>
       <x:c r="R470" s="14"/>
       <x:c r="S470" s="14"/>
@@ -11006,7 +11218,7 @@
       <x:c r="M471" s="14"/>
       <x:c r="N471" s="14"/>
       <x:c r="O471" s="14"/>
-      <x:c r="P471" s="14"/>
+      <x:c r="P471" s="31"/>
       <x:c r="Q471" s="14"/>
       <x:c r="R471" s="14"/>
       <x:c r="S471" s="14"/>
@@ -11027,7 +11239,7 @@
       <x:c r="M472" s="14"/>
       <x:c r="N472" s="14"/>
       <x:c r="O472" s="14"/>
-      <x:c r="P472" s="14"/>
+      <x:c r="P472" s="31"/>
       <x:c r="Q472" s="14"/>
       <x:c r="R472" s="14"/>
       <x:c r="S472" s="14"/>
@@ -11048,7 +11260,7 @@
       <x:c r="M473" s="14"/>
       <x:c r="N473" s="14"/>
       <x:c r="O473" s="14"/>
-      <x:c r="P473" s="14"/>
+      <x:c r="P473" s="31"/>
       <x:c r="Q473" s="14"/>
       <x:c r="R473" s="14"/>
       <x:c r="S473" s="14"/>
@@ -11069,7 +11281,7 @@
       <x:c r="M474" s="14"/>
       <x:c r="N474" s="14"/>
       <x:c r="O474" s="14"/>
-      <x:c r="P474" s="14"/>
+      <x:c r="P474" s="31"/>
       <x:c r="Q474" s="14"/>
       <x:c r="R474" s="14"/>
       <x:c r="S474" s="14"/>
@@ -11090,7 +11302,7 @@
       <x:c r="M475" s="14"/>
       <x:c r="N475" s="14"/>
       <x:c r="O475" s="14"/>
-      <x:c r="P475" s="14"/>
+      <x:c r="P475" s="31"/>
       <x:c r="Q475" s="14"/>
       <x:c r="R475" s="14"/>
       <x:c r="S475" s="14"/>
@@ -11111,7 +11323,7 @@
       <x:c r="M476" s="14"/>
       <x:c r="N476" s="14"/>
       <x:c r="O476" s="14"/>
-      <x:c r="P476" s="14"/>
+      <x:c r="P476" s="31"/>
       <x:c r="Q476" s="14"/>
       <x:c r="R476" s="14"/>
       <x:c r="S476" s="14"/>
@@ -11132,7 +11344,7 @@
       <x:c r="M477" s="14"/>
       <x:c r="N477" s="14"/>
       <x:c r="O477" s="14"/>
-      <x:c r="P477" s="14"/>
+      <x:c r="P477" s="31"/>
       <x:c r="Q477" s="14"/>
       <x:c r="R477" s="14"/>
       <x:c r="S477" s="14"/>
@@ -11153,7 +11365,7 @@
       <x:c r="M478" s="14"/>
       <x:c r="N478" s="14"/>
       <x:c r="O478" s="14"/>
-      <x:c r="P478" s="14"/>
+      <x:c r="P478" s="31"/>
       <x:c r="Q478" s="14"/>
       <x:c r="R478" s="14"/>
       <x:c r="S478" s="14"/>
@@ -11174,7 +11386,7 @@
       <x:c r="M479" s="14"/>
       <x:c r="N479" s="14"/>
       <x:c r="O479" s="14"/>
-      <x:c r="P479" s="14"/>
+      <x:c r="P479" s="31"/>
       <x:c r="Q479" s="14"/>
       <x:c r="R479" s="14"/>
       <x:c r="S479" s="14"/>
@@ -11195,7 +11407,7 @@
       <x:c r="M480" s="14"/>
       <x:c r="N480" s="14"/>
       <x:c r="O480" s="14"/>
-      <x:c r="P480" s="14"/>
+      <x:c r="P480" s="31"/>
       <x:c r="Q480" s="14"/>
       <x:c r="R480" s="14"/>
       <x:c r="S480" s="14"/>
@@ -11216,7 +11428,7 @@
       <x:c r="M481" s="14"/>
       <x:c r="N481" s="14"/>
       <x:c r="O481" s="14"/>
-      <x:c r="P481" s="14"/>
+      <x:c r="P481" s="31"/>
       <x:c r="Q481" s="14"/>
       <x:c r="R481" s="14"/>
       <x:c r="S481" s="14"/>
@@ -11237,7 +11449,7 @@
       <x:c r="M482" s="14"/>
       <x:c r="N482" s="14"/>
       <x:c r="O482" s="14"/>
-      <x:c r="P482" s="14"/>
+      <x:c r="P482" s="31"/>
       <x:c r="Q482" s="14"/>
       <x:c r="R482" s="14"/>
       <x:c r="S482" s="14"/>
@@ -11258,7 +11470,7 @@
       <x:c r="M483" s="14"/>
       <x:c r="N483" s="14"/>
       <x:c r="O483" s="14"/>
-      <x:c r="P483" s="14"/>
+      <x:c r="P483" s="31"/>
       <x:c r="Q483" s="14"/>
       <x:c r="R483" s="14"/>
       <x:c r="S483" s="14"/>
@@ -11279,7 +11491,7 @@
       <x:c r="M484" s="14"/>
       <x:c r="N484" s="14"/>
       <x:c r="O484" s="14"/>
-      <x:c r="P484" s="14"/>
+      <x:c r="P484" s="31"/>
       <x:c r="Q484" s="14"/>
       <x:c r="R484" s="14"/>
       <x:c r="S484" s="14"/>
@@ -11300,7 +11512,7 @@
       <x:c r="M485" s="14"/>
       <x:c r="N485" s="14"/>
       <x:c r="O485" s="14"/>
-      <x:c r="P485" s="14"/>
+      <x:c r="P485" s="31"/>
       <x:c r="Q485" s="14"/>
       <x:c r="R485" s="14"/>
       <x:c r="S485" s="14"/>
@@ -11321,7 +11533,7 @@
       <x:c r="M486" s="14"/>
       <x:c r="N486" s="14"/>
       <x:c r="O486" s="14"/>
-      <x:c r="P486" s="14"/>
+      <x:c r="P486" s="31"/>
       <x:c r="Q486" s="14"/>
       <x:c r="R486" s="14"/>
       <x:c r="S486" s="14"/>
@@ -11342,7 +11554,7 @@
       <x:c r="M487" s="14"/>
       <x:c r="N487" s="14"/>
       <x:c r="O487" s="14"/>
-      <x:c r="P487" s="14"/>
+      <x:c r="P487" s="31"/>
       <x:c r="Q487" s="14"/>
       <x:c r="R487" s="14"/>
       <x:c r="S487" s="14"/>
@@ -11363,7 +11575,7 @@
       <x:c r="M488" s="14"/>
       <x:c r="N488" s="14"/>
       <x:c r="O488" s="14"/>
-      <x:c r="P488" s="14"/>
+      <x:c r="P488" s="31"/>
       <x:c r="Q488" s="14"/>
       <x:c r="R488" s="14"/>
       <x:c r="S488" s="14"/>
@@ -11384,7 +11596,7 @@
       <x:c r="M489" s="14"/>
       <x:c r="N489" s="14"/>
       <x:c r="O489" s="14"/>
-      <x:c r="P489" s="14"/>
+      <x:c r="P489" s="31"/>
       <x:c r="Q489" s="14"/>
       <x:c r="R489" s="14"/>
       <x:c r="S489" s="14"/>
@@ -11405,7 +11617,7 @@
       <x:c r="M490" s="14"/>
       <x:c r="N490" s="14"/>
       <x:c r="O490" s="14"/>
-      <x:c r="P490" s="14"/>
+      <x:c r="P490" s="31"/>
       <x:c r="Q490" s="14"/>
       <x:c r="R490" s="14"/>
       <x:c r="S490" s="14"/>
@@ -11426,7 +11638,7 @@
       <x:c r="M491" s="14"/>
       <x:c r="N491" s="14"/>
       <x:c r="O491" s="14"/>
-      <x:c r="P491" s="14"/>
+      <x:c r="P491" s="31"/>
       <x:c r="Q491" s="14"/>
       <x:c r="R491" s="14"/>
       <x:c r="S491" s="14"/>
@@ -11447,7 +11659,7 @@
       <x:c r="M492" s="14"/>
       <x:c r="N492" s="14"/>
       <x:c r="O492" s="14"/>
-      <x:c r="P492" s="14"/>
+      <x:c r="P492" s="31"/>
       <x:c r="Q492" s="14"/>
       <x:c r="R492" s="14"/>
       <x:c r="S492" s="14"/>
@@ -11468,7 +11680,7 @@
       <x:c r="M493" s="14"/>
       <x:c r="N493" s="14"/>
       <x:c r="O493" s="14"/>
-      <x:c r="P493" s="14"/>
+      <x:c r="P493" s="31"/>
       <x:c r="Q493" s="14"/>
       <x:c r="R493" s="14"/>
       <x:c r="S493" s="14"/>
@@ -11489,7 +11701,7 @@
       <x:c r="M494" s="14"/>
       <x:c r="N494" s="14"/>
       <x:c r="O494" s="14"/>
-      <x:c r="P494" s="14"/>
+      <x:c r="P494" s="31"/>
       <x:c r="Q494" s="14"/>
       <x:c r="R494" s="14"/>
       <x:c r="S494" s="14"/>
@@ -11510,7 +11722,7 @@
       <x:c r="M495" s="14"/>
       <x:c r="N495" s="14"/>
       <x:c r="O495" s="14"/>
-      <x:c r="P495" s="14"/>
+      <x:c r="P495" s="31"/>
       <x:c r="Q495" s="14"/>
       <x:c r="R495" s="14"/>
       <x:c r="S495" s="14"/>
@@ -11531,7 +11743,7 @@
       <x:c r="M496" s="14"/>
       <x:c r="N496" s="14"/>
       <x:c r="O496" s="14"/>
-      <x:c r="P496" s="14"/>
+      <x:c r="P496" s="31"/>
       <x:c r="Q496" s="14"/>
       <x:c r="R496" s="14"/>
       <x:c r="S496" s="14"/>
@@ -11552,7 +11764,7 @@
       <x:c r="M497" s="14"/>
       <x:c r="N497" s="14"/>
       <x:c r="O497" s="14"/>
-      <x:c r="P497" s="14"/>
+      <x:c r="P497" s="31"/>
       <x:c r="Q497" s="14"/>
       <x:c r="R497" s="14"/>
       <x:c r="S497" s="14"/>
@@ -11573,7 +11785,7 @@
       <x:c r="M498" s="14"/>
       <x:c r="N498" s="14"/>
       <x:c r="O498" s="14"/>
-      <x:c r="P498" s="14"/>
+      <x:c r="P498" s="31"/>
       <x:c r="Q498" s="14"/>
       <x:c r="R498" s="14"/>
       <x:c r="S498" s="14"/>
@@ -11594,7 +11806,7 @@
       <x:c r="M499" s="14"/>
       <x:c r="N499" s="14"/>
       <x:c r="O499" s="14"/>
-      <x:c r="P499" s="14"/>
+      <x:c r="P499" s="31"/>
       <x:c r="Q499" s="14"/>
       <x:c r="R499" s="14"/>
       <x:c r="S499" s="14"/>
@@ -11615,7 +11827,7 @@
       <x:c r="M500" s="14"/>
       <x:c r="N500" s="14"/>
       <x:c r="O500" s="14"/>
-      <x:c r="P500" s="14"/>
+      <x:c r="P500" s="31"/>
       <x:c r="Q500" s="14"/>
       <x:c r="R500" s="14"/>
       <x:c r="S500" s="14"/>
@@ -11671,7 +11883,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec27079765044452"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6d9f050570748e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12136,10 +12348,498 @@
         <x:v>The World's Hardest Game / Arrows/stick move. A is explicitly neutralized so it cannot click.</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>Bejeweled 2</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>bejeweled-2.profile</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>bejeweled2|bejeweled-2-deluxe|bejeweled2deluxe|bejeweled-2-action</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>click</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>a</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>Click</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N11" s="14" t="str">
+        <x:v>Mouse-only. Right stick moves the cursor; A clicks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>Minecraft Tower Defense</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>minecrafttowerdefense.profile</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>minecraft-tower-defense|minecraft-tower-defence|minecrafttowerdefence|minecraft-td|minecraft-tower-defense-1</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>click</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>a</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Click</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N12" s="14" t="str">
+        <x:v>Mouse-only. Right stick moves the cursor; A digs, builds and selects.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>Final Fantasy Sonic X5</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>final-fantasy-sonic-x5.profile</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>finalfantasysonicx5|final-fantasy-sonic-x-5|final-fantasy-sonic-x-episode-5|final-fantasy-sonic-x5-episode-5|ffsx5</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>click</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>a</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Click</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N13" s="14" t="str">
+        <x:v>Mouse-only RPG. Right stick moves the cursor; A selects.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>We Dancing Online</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>we-dancing-online.profile</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>we-dancing-online|wedancingonline</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>unused</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>r1</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>Space</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>Enter</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="str">
+        <x:v>Esc</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="str">
+        <x:v>Shift</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N14" s="14" t="str">
+        <x:v>D-pad = arrows; B = Space; X = X; Y = C; Start = Enter; Select = Esc; L1 = Shift; R1 = click.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>Ultimate Flash Sonic</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>ultimate-flash-sonic.profile</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>ultimateflashsonic|ultimate-sonic-flash|ultimate-sonic|ufs</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>keyboard</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>r1</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>Space</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="str">
+        <x:v>Enter</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L15" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N15" s="14" t="str">
+        <x:v>Arrows move; A = jump/Spin Dash; Start = pause; R1 = menu click.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>Super Smash Flash 2</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>ssf2.profile</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>super-smash-flash-2|supersmashflash2|ssf-2|ssf2-v0-8|ssf2-v0-8b|ssf2-v0-9|ssf2-v0-9b|super-smash-flash-2-v0-8|super-smash-flash-2-v0-9</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>keyboard</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>r1</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
+        <x:v>P</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str">
+        <x:v>U</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="str">
+        <x:v>Space</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="str">
+        <x:v>Backspace</x:v>
+      </x:c>
+      <x:c r="L16" s="14" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N16" s="14" t="str">
+        <x:v>P1: D-pad = WASD; A attack; B special; X grab; Y shield; Start start; Select pause; L1 taunt; R1 menu click.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14"/>
+      <x:c r="B17" s="14"/>
+      <x:c r="C17" s="14"/>
+      <x:c r="D17" s="14"/>
+      <x:c r="E17" s="14"/>
+      <x:c r="F17" s="14"/>
+      <x:c r="G17" s="14"/>
+      <x:c r="H17" s="14"/>
+      <x:c r="I17" s="14"/>
+      <x:c r="J17" s="14"/>
+      <x:c r="K17" s="14"/>
+      <x:c r="L17" s="14"/>
+      <x:c r="M17" s="14"/>
+      <x:c r="N17" s="14"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14"/>
+      <x:c r="B18" s="14"/>
+      <x:c r="C18" s="14"/>
+      <x:c r="D18" s="14"/>
+      <x:c r="E18" s="14"/>
+      <x:c r="F18" s="14"/>
+      <x:c r="G18" s="14"/>
+      <x:c r="H18" s="14"/>
+      <x:c r="I18" s="14"/>
+      <x:c r="J18" s="14"/>
+      <x:c r="K18" s="14"/>
+      <x:c r="L18" s="14"/>
+      <x:c r="M18" s="14"/>
+      <x:c r="N18" s="14"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14"/>
+      <x:c r="B19" s="14"/>
+      <x:c r="C19" s="14"/>
+      <x:c r="D19" s="14"/>
+      <x:c r="E19" s="14"/>
+      <x:c r="F19" s="14"/>
+      <x:c r="G19" s="14"/>
+      <x:c r="H19" s="14"/>
+      <x:c r="I19" s="14"/>
+      <x:c r="J19" s="14"/>
+      <x:c r="K19" s="14"/>
+      <x:c r="L19" s="14"/>
+      <x:c r="M19" s="14"/>
+      <x:c r="N19" s="14"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14"/>
+      <x:c r="B20" s="14"/>
+      <x:c r="C20" s="14"/>
+      <x:c r="D20" s="14"/>
+      <x:c r="E20" s="14"/>
+      <x:c r="F20" s="14"/>
+      <x:c r="G20" s="14"/>
+      <x:c r="H20" s="14"/>
+      <x:c r="I20" s="14"/>
+      <x:c r="J20" s="14"/>
+      <x:c r="K20" s="14"/>
+      <x:c r="L20" s="14"/>
+      <x:c r="M20" s="14"/>
+      <x:c r="N20" s="14"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14"/>
+      <x:c r="B21" s="14"/>
+      <x:c r="C21" s="14"/>
+      <x:c r="D21" s="14"/>
+      <x:c r="E21" s="14"/>
+      <x:c r="F21" s="14"/>
+      <x:c r="G21" s="14"/>
+      <x:c r="H21" s="14"/>
+      <x:c r="I21" s="14"/>
+      <x:c r="J21" s="14"/>
+      <x:c r="K21" s="14"/>
+      <x:c r="L21" s="14"/>
+      <x:c r="M21" s="14"/>
+      <x:c r="N21" s="14"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14"/>
+      <x:c r="B22" s="14"/>
+      <x:c r="C22" s="14"/>
+      <x:c r="D22" s="14"/>
+      <x:c r="E22" s="14"/>
+      <x:c r="F22" s="14"/>
+      <x:c r="G22" s="14"/>
+      <x:c r="H22" s="14"/>
+      <x:c r="I22" s="14"/>
+      <x:c r="J22" s="14"/>
+      <x:c r="K22" s="14"/>
+      <x:c r="L22" s="14"/>
+      <x:c r="M22" s="14"/>
+      <x:c r="N22" s="14"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14"/>
+      <x:c r="B23" s="14"/>
+      <x:c r="C23" s="14"/>
+      <x:c r="D23" s="14"/>
+      <x:c r="E23" s="14"/>
+      <x:c r="F23" s="14"/>
+      <x:c r="G23" s="14"/>
+      <x:c r="H23" s="14"/>
+      <x:c r="I23" s="14"/>
+      <x:c r="J23" s="14"/>
+      <x:c r="K23" s="14"/>
+      <x:c r="L23" s="14"/>
+      <x:c r="M23" s="14"/>
+      <x:c r="N23" s="14"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14"/>
+      <x:c r="B24" s="14"/>
+      <x:c r="C24" s="14"/>
+      <x:c r="D24" s="14"/>
+      <x:c r="E24" s="14"/>
+      <x:c r="F24" s="14"/>
+      <x:c r="G24" s="14"/>
+      <x:c r="H24" s="14"/>
+      <x:c r="I24" s="14"/>
+      <x:c r="J24" s="14"/>
+      <x:c r="K24" s="14"/>
+      <x:c r="L24" s="14"/>
+      <x:c r="M24" s="14"/>
+      <x:c r="N24" s="14"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14"/>
+      <x:c r="B25" s="14"/>
+      <x:c r="C25" s="14"/>
+      <x:c r="D25" s="14"/>
+      <x:c r="E25" s="14"/>
+      <x:c r="F25" s="14"/>
+      <x:c r="G25" s="14"/>
+      <x:c r="H25" s="14"/>
+      <x:c r="I25" s="14"/>
+      <x:c r="J25" s="14"/>
+      <x:c r="K25" s="14"/>
+      <x:c r="L25" s="14"/>
+      <x:c r="M25" s="14"/>
+      <x:c r="N25" s="14"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14"/>
+      <x:c r="B26" s="14"/>
+      <x:c r="C26" s="14"/>
+      <x:c r="D26" s="14"/>
+      <x:c r="E26" s="14"/>
+      <x:c r="F26" s="14"/>
+      <x:c r="G26" s="14"/>
+      <x:c r="H26" s="14"/>
+      <x:c r="I26" s="14"/>
+      <x:c r="J26" s="14"/>
+      <x:c r="K26" s="14"/>
+      <x:c r="L26" s="14"/>
+      <x:c r="M26" s="14"/>
+      <x:c r="N26" s="14"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14"/>
+      <x:c r="B27" s="14"/>
+      <x:c r="C27" s="14"/>
+      <x:c r="D27" s="14"/>
+      <x:c r="E27" s="14"/>
+      <x:c r="F27" s="14"/>
+      <x:c r="G27" s="14"/>
+      <x:c r="H27" s="14"/>
+      <x:c r="I27" s="14"/>
+      <x:c r="J27" s="14"/>
+      <x:c r="K27" s="14"/>
+      <x:c r="L27" s="14"/>
+      <x:c r="M27" s="14"/>
+      <x:c r="N27" s="14"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14"/>
+      <x:c r="B28" s="14"/>
+      <x:c r="C28" s="14"/>
+      <x:c r="D28" s="14"/>
+      <x:c r="E28" s="14"/>
+      <x:c r="F28" s="14"/>
+      <x:c r="G28" s="14"/>
+      <x:c r="H28" s="14"/>
+      <x:c r="I28" s="14"/>
+      <x:c r="J28" s="14"/>
+      <x:c r="K28" s="14"/>
+      <x:c r="L28" s="14"/>
+      <x:c r="M28" s="14"/>
+      <x:c r="N28" s="14"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14"/>
+      <x:c r="B29" s="14"/>
+      <x:c r="C29" s="14"/>
+      <x:c r="D29" s="14"/>
+      <x:c r="E29" s="14"/>
+      <x:c r="F29" s="14"/>
+      <x:c r="G29" s="14"/>
+      <x:c r="H29" s="14"/>
+      <x:c r="I29" s="14"/>
+      <x:c r="J29" s="14"/>
+      <x:c r="K29" s="14"/>
+      <x:c r="L29" s="14"/>
+      <x:c r="M29" s="14"/>
+      <x:c r="N29" s="14"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14"/>
+      <x:c r="B30" s="14"/>
+      <x:c r="C30" s="14"/>
+      <x:c r="D30" s="14"/>
+      <x:c r="E30" s="14"/>
+      <x:c r="F30" s="14"/>
+      <x:c r="G30" s="14"/>
+      <x:c r="H30" s="14"/>
+      <x:c r="I30" s="14"/>
+      <x:c r="J30" s="14"/>
+      <x:c r="K30" s="14"/>
+      <x:c r="L30" s="14"/>
+      <x:c r="M30" s="14"/>
+      <x:c r="N30" s="14"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68f5482decb04657"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a1b77b9fde43ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12189,7 +12889,7 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTA(Compatibility!A2:A500)</x:f>
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="28"/>
       <x:c r="E4" s="28"/>
@@ -12203,7 +12903,7 @@
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF(Compatibility!C2:C500,"Perfect")+COUNTIF(Compatibility!C2:C500,"Playable")</x:f>
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="28"/>
       <x:c r="E5" s="28"/>
@@ -12216,8 +12916,8 @@
         <x:v>Needs attention</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:f>COUNTIF(Compatibility!C2:C500,"Partial")+COUNTIF(Compatibility!C2:C500,"Boots")+COUNTIF(Compatibility!C2:C500,"Doesn't open")+COUNTIF(Compatibility!C2:C500,"Black screen")+COUNTIF(Compatibility!C2:C500,"Crash")+COUNTIF(Compatibility!C2:C500,"Needs assets")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIF(Compatibility!C2:C500,"Partial")+COUNTIF(Compatibility!C2:C500,"Boots")+COUNTIF(Compatibility!C2:C500,"Doesn't open")+COUNTIF(Compatibility!C2:C500,"Black screen")+COUNTIF(Compatibility!C2:C500,"White screen")+COUNTIF(Compatibility!C2:C500,"Crash")+COUNTIF(Compatibility!C2:C500,"Needs assets")</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="28"/>
       <x:c r="E6" s="28"/>
@@ -12231,7 +12931,7 @@
       </x:c>
       <x:c r="B7" t="n">
         <x:f>COUNTA('Control Profiles'!A2:A200)</x:f>
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="28"/>
       <x:c r="E7" s="28"/>
@@ -12244,7 +12944,7 @@
         <x:v>Current preview</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>0.8.2</x:v>
+        <x:v>0.8.21</x:v>
       </x:c>
       <x:c r="D8" s="28"/>
       <x:c r="E8" s="28"/>
@@ -12275,7 +12975,7 @@
       </x:c>
       <x:c r="B12" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A12)</x:f>
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -12329,7 +13029,7 @@
       </x:c>
       <x:c r="B18" t="n">
         <x:f>COUNTIF(Compatibility!$C$2:$C$500,A18)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -12356,6 +13056,6 @@
     <x:mergeCell ref="D3:H8"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re30770dc5c9a4ae8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c3d0fb66d804e63"/>
 </x:worksheet>
 </file>